--- a/Week1.xlsx
+++ b/Week1.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y90"/>
+  <dimension ref="A1:Y79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sun, Mar 24</t>
+          <t>Sun, Mar 31</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -427,7 +427,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Mon, Mar 25</t>
+          <t>Mon, Apr 1</t>
         </is>
       </c>
       <c r="F1" t="inlineStr"/>
@@ -435,7 +435,7 @@
       <c r="H1" t="inlineStr"/>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Tue, Mar 26</t>
+          <t>Tue, Apr 2</t>
         </is>
       </c>
       <c r="J1" t="inlineStr"/>
@@ -443,7 +443,7 @@
       <c r="L1" t="inlineStr"/>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Wed, Mar 27</t>
+          <t>Wed, Apr 3</t>
         </is>
       </c>
       <c r="N1" t="inlineStr"/>
@@ -451,7 +451,7 @@
       <c r="P1" t="inlineStr"/>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Thu, Mar 28</t>
+          <t>Thu, Apr 4</t>
         </is>
       </c>
       <c r="R1" t="inlineStr"/>
@@ -459,7 +459,7 @@
       <c r="T1" t="inlineStr"/>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Fri, Mar 29</t>
+          <t>Fri, Apr 5</t>
         </is>
       </c>
       <c r="V1" t="inlineStr"/>
@@ -467,7 +467,7 @@
       <c r="X1" t="inlineStr"/>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Sat, Mar 30</t>
+          <t>Sat, Apr 6</t>
         </is>
       </c>
     </row>
@@ -535,64 +535,24 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DJ </t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Bag 1, SB 11</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lashaun </t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Bag 5</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DJ </t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Bag 1, SB 11</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kim </t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Bag 8</t>
-        </is>
-      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ian </t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Bag 4</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
     </row>
@@ -606,56 +566,24 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Katherine </t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Bag 8</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ian </t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Bag 4</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Katherine </t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bag 7 </t>
-        </is>
-      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kim </t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Bag 8</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
     </row>
@@ -733,7 +661,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5:30 AM MEET WATERTOWN PLANK</t>
+          <t>5:00 AM START</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -741,7 +669,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6:30 AM START</t>
+          <t>5:30 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -749,7 +677,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>6:00 AM MEET AT THE OFFICE</t>
+          <t>4:30 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -757,7 +685,7 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>5:00 AM MEET WATERTOWN PLANK</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -765,7 +693,7 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>5:15 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>4:30 AM MEET BAYSHORE</t>
         </is>
       </c>
       <c r="W8" t="inlineStr"/>
@@ -780,7 +708,7 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -788,7 +716,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -796,7 +724,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -804,7 +732,7 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>6:30 AM START</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
@@ -827,7 +755,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
+          <t>OUTPOST NATURAL FOODS, BAY VIEW</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -835,7 +763,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>OPEN PANTRY #605, BAYSIDE</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -843,7 +771,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -851,7 +779,7 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1050, ST FRANCIS</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
@@ -859,7 +787,7 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
@@ -874,7 +802,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>KOHN'S FILLING STATION, KEWASKUM</t>
+          <t>2826 S KINNICKINNC AVE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -882,7 +810,8 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>501 W BROWN DEER RD</t>
+          <t>PICK #856, RACINE-
+MT PLEASANT</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -890,7 +819,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>OPEN PANTRY #493, RACINE</t>
+          <t>MARIANO'S #522 +RX, CHICAGO-EDGEWATER</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -898,7 +827,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2000 E LAYTON AVENUE SUITE 150</t>
+          <t>FESTIVAL #2732, APPLETON - NORTHLAND - LIFO</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -906,7 +835,7 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>ROTE OIL #14 TREVOR (CITGO)</t>
+          <t>PICK #408, TWO RIVERS</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
@@ -921,7 +850,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>890 FOND DU LAC AVE</t>
+          <t>https://goo.gl/maps/5hiyyxywjiH2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -929,7 +858,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/pQaSRAn88Vh6DAQ58</t>
+          <t>1202  N GREENBAY RD</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -937,7 +866,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>3441 SPRING ST</t>
+          <t>5201 N SHERIDAN RD</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -945,7 +874,7 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/saDijnsPM7S2</t>
+          <t>1200 W NORTHLAND AVE</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -953,7 +882,7 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>12617 ANTIOCH RD</t>
+          <t>1010 22ND STREET</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
@@ -968,7 +897,7 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/CJnRNDyortw</t>
+          <t>EVERYONE PLEASE CHECK IN W/ METCALFES AFTER</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -976,7 +905,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>https://goo.gl/maps/gCMavYTDGoo</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -984,19 +913,23 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/8i7XHemjTpL2</t>
+          <t>https://goo.gl/maps/9eaE3Q6o8jF2</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/eRWs6b1N24m</t>
+        </is>
+      </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/xA9YMzPGc6Vhxi5r8</t>
+          <t>https://maps.app.goo.gl/5jsT8sqpo6yELUmX9</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
@@ -1009,49 +942,29 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>TO FOLLOW</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
+          <t>SET UP ON REG #1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>TO FOLLOW</t>
-        </is>
-      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>Kim G</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>Sante Fe available, Equip</t>
-        </is>
-      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>DJ and Mai will start here, Aurora is 10 min away, 7:30 Start</t>
         </is>
       </c>
       <c r="W14" t="inlineStr"/>
@@ -1063,50 +976,66 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Camry available, Equip</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>OPEN PANTRY #612, BROOKFIELD</t>
+          <t>*Kim - Lincoln - Sonia meet at the office @ 4:45 am</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Mai</t>
+          <t>Jeremiah</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>Until 12:00</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>ROTE OIL #13 TREVOR (BP)</t>
+          <t>Ian's car to pick up Carlie on the way north @ Grafton</t>
         </is>
       </c>
       <c r="W15" t="inlineStr"/>
@@ -1118,40 +1047,53 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>KOHN'S FILLING STATION 259, CAMPBELLSPORT</t>
+          <t>Curt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>17235 W BLUEMOUND RD</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>OPEN PANTRY #9570, RACINE</t>
+          <t>Carlie</t>
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Driver,
+Optima</t>
+        </is>
+      </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>12511 ANTIOCH RD</t>
-        </is>
-      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
@@ -1161,41 +1103,80 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>259 N FOND DU LAC AVE</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/awRYbmypZ4H2</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>Kim G</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>*Driver
+Sante Fe, Equip</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2731 DURAND AVE</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Driver,
+Altima</t>
+        </is>
+      </c>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/iu3xzNwgJ32esP5RA</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr"/>
+          <t>Kim G</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>@ Store,
+Sante Fe, Equip</t>
+        </is>
+      </c>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
     </row>
@@ -1204,41 +1185,74 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/WCsZpx5SMsA2</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/boUkpED44a62</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Driver,
+Altima</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>5:00 AM MEET AT THE OFFICE</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>@ Grafton</t>
+        </is>
+      </c>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
     </row>
@@ -1251,42 +1265,59 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Driver,
+Sante Fe,
+Rx</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>Katherine</t>
         </is>
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Driver,
-Sante Fe, Equip</t>
-        </is>
-      </c>
+          <t>Curt</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
     </row>
@@ -1295,34 +1326,29 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Kim G</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Driver,
-Sante Fe, Equip</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>OPEN PANTRY #614, MILWAUKEE</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>Jerry D</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>3rd week</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1330,31 +1356,36 @@
           <t>Katherine</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>Kim G</t>
         </is>
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>w/ Mai
+Aurora @ 7:30</t>
+        </is>
+      </c>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
     </row>
@@ -1363,54 +1394,75 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>5:00 AM START</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>3100 S 76TH ST</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>Kim C</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>3rd scan, work w/ Evelin</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Sue</t>
+          <t>Kim C</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Driver,
-Camry</t>
+          <t>3rd week</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>ROTE OIL #1 PADDOCK LAKE- BRASS BALL</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Driver,
+Camry
+(Grafton)</t>
+        </is>
+      </c>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
     </row>
@@ -1420,31 +1472,69 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/fpg1rAd58h22</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>25406 75TH ST</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
@@ -1455,29 +1545,65 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>OUTPOST NATURAL FOODS, MEQUON</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Early office meet</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Monica</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/LTa4ckcczx5qc8269</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr"/>
+          <t>Annette</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="W23" t="inlineStr"/>
@@ -1492,50 +1618,67 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>5:30 AM MEET OFFICE</t>
+          <t>7590 W MEQUON RD</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Camry available, Equip</t>
-        </is>
-      </c>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>5:30 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr"/>
+          <t>Heather</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr"/>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
     </row>
@@ -1547,46 +1690,71 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>https://goo.gl/maps/do2xmdVUL8z</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Early office meet</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr"/>
+          <t>Jerry S</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1062, WEST ALLIS</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr"/>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>w/ DJ
+Aurora @ 7:30</t>
+        </is>
+      </c>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
     </row>
@@ -1598,43 +1766,63 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>EVERYONE PLEASE CHECK IN W/ METCALFES AFTER</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>Stephanie</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>ROTE OIL #2 PADDOCK LAKE- 75TH ST</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr"/>
+          <t>Laurie</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>6609 W GREENFIELD AVE</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="W26" t="inlineStr"/>
@@ -1647,37 +1835,66 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>AURORA OUTPATIENT RX #1053, SLINGER</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>@ Store,
+Trainer</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1115 UNION GROVE</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>25555 75TH ST</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr"/>
+          <t>Marcia</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/dX5u7g5chT1DCwZVA</t>
+          <t>Stephanie</t>
         </is>
       </c>
       <c r="W27" t="inlineStr"/>
@@ -1689,33 +1906,70 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1061 EAST COMMERCE BOULEVARD SUITE</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>Jeremiah</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>4310 67TH DRIVE</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr"/>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>@ Store,
+Supv Rx</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/5UyWWXXbzXMaVnv99</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr"/>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
@@ -1728,49 +1982,61 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/7iYLLr5ukoS2</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>3 Stepladders</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>5:30 AM START</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>15)</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/T7d8P5BJ5vQyPjos7</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>15)</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Nagui</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Kim G</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
     </row>
@@ -1779,48 +2045,52 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>APPROX 8:00/9:00 AM START</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>Alyssa H</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>@ Store, Trainer</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>16)</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>NEED THE 4208 SCANNERS DUE TO THE LIGHTING IN THE STORE.  ALSO SCANNER HOODS.</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr"/>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>7:30 AM START</t>
+        </is>
+      </c>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
@@ -1830,45 +2100,56 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>Ethan</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>@ Store, work w/ Alyssa H</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>ROTE OIL #6 HUBERTUS</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>17)</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Michael N</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>Driver,
-Camry</t>
-        </is>
-      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
@@ -1878,38 +2159,33 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>GAUGERT'S BUSS STOP, SULLIVAN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>Heather</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@ Store  </t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1306 HWY 175</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Driver,
-Equip</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
@@ -1918,7 +2194,7 @@
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
-          <t>8:00 AM START</t>
+          <t>AURORA OUTPATIENT RX #1041, TWO RIVERS</t>
         </is>
       </c>
       <c r="W32" t="inlineStr"/>
@@ -1931,31 +2207,19 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>141 MAIN ST</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/SZRuQ4FHA1cX2ZmC8</t>
+          <t>DISCOUNT LIQUOR INC, MILWAUKEE</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Carlie</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
@@ -1965,7 +2229,7 @@
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
+          <t>5300 MEMORIAL DRIVE, SUITE 103</t>
         </is>
       </c>
       <c r="W33" t="inlineStr"/>
@@ -1978,45 +2242,33 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/TEUfEX2J1AE2</t>
-        </is>
-      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>5031 W OKLAHOMA AVE</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>Milwaukee Office</t>
         </is>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>4:45 AM MEET SOUTH RACINE COURT (HWY 43 &amp; Y)</t>
-        </is>
-      </c>
+      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
-          <t>SMITH BEER &amp; LIQUOR, MILWAUKEE</t>
+          <t>https://goo.gl/maps/7zzPH72TWHs</t>
         </is>
       </c>
       <c r="W34" t="inlineStr"/>
@@ -2029,33 +2281,37 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>5:00 AM START</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>https://goo.gl/maps/hfa57ctXcvNrGJ4NA</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Kim G</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
-          <t>1413 E BRADY STREET</t>
+          <t>Help at Pick n Save after if needed</t>
         </is>
       </c>
       <c r="W35" t="inlineStr"/>
@@ -2067,49 +2323,32 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Driver,
-Equip</t>
-        </is>
-      </c>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>ROTE OIL #7 MILWAUKEE</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/X1WJEhe6hdQ2</t>
-        </is>
-      </c>
+      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
@@ -2119,45 +2358,55 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>OUTPOST NATURAL FOODS, MILWAUKEE</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>5931 N 91ST ST</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5:30 AM START </t>
-        </is>
-      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>SULLIVAN'S FOODS #242, MARENGO</t>
-        </is>
-      </c>
+      <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Start at 
+Pick n Save,
+Equip</t>
+        </is>
+      </c>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
     </row>
@@ -2167,46 +2416,51 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>100 E CAPITOL DR</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/cw58s7atAhTAGHNd7</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Until 12:00</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>202 LINDOW LANE</t>
-        </is>
-      </c>
+      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>Mai</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>Start at 
+Pick n Save</t>
         </is>
       </c>
       <c r="X38" t="inlineStr"/>
@@ -2218,43 +2472,39 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/n94xpFtHzvE2</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Until 12:00</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>ROTE OIL #10 MUKWONAGO - ROCHESTER</t>
-        </is>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/GrPtfaDKMT2RotRb9</t>
-        </is>
-      </c>
+      <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
@@ -2264,32 +2514,28 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>5:00 AM MEET OFFICE</t>
+          <t>EVERYONE PLEASE CHECK IN W/ METCALFES AFTER</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>1060 N ROCHESTER ST</t>
-        </is>
-      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
@@ -2307,52 +2553,28 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>ROTE OIL #8 ELM GROVE</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/dmvR5bTHLs1Cbjcr5</t>
-        </is>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
@@ -2362,50 +2584,38 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>13395 WATERTOWN PLANK RD</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TO FOLLOW   </t>
-        </is>
-      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>3rd week</t>
-        </is>
-      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
-          <t>6:15 AM OFFICE LEAVE TIME</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="W42" t="inlineStr"/>
@@ -2417,10 +2627,14 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>ROTE OIL #03 TWIN LAKES</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -2428,35 +2642,23 @@
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/5zXAKpcRHDmA17UK9</t>
+          <t>6:30 AM MEET WATERTOWN PLANK</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
+          <t>PICK #366 +RX, HALES CORNERS</t>
         </is>
       </c>
       <c r="W43" t="inlineStr"/>
@@ -2468,10 +2670,14 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>475 N LAKE AVE</t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -2479,40 +2685,23 @@
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>7:00 AM START</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>ROTE OIL #12 MUKWONAGO - (AMOCO) GREENWALD</t>
-        </is>
-      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>Driver,
-Altima</t>
-        </is>
-      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
+          <t>5800 S 108TH ST</t>
         </is>
       </c>
       <c r="W44" t="inlineStr"/>
@@ -2524,10 +2713,14 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/jNgJR8hii6jJGZQP7</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -2535,40 +2728,23 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>FINANCIAL</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>909 GREENWALD CT</t>
-        </is>
-      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
-          <t>RAPID MART HARTFORD</t>
+          <t>https://goo.gl/maps/zX1XvNMo8SU2</t>
         </is>
       </c>
       <c r="W45" t="inlineStr"/>
@@ -2580,10 +2756,14 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">TO FOLLOW   </t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -2591,37 +2771,21 @@
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>ROTE OIL #09 GREENFIELD</t>
+          <t>EAST SIDE MART, JACKSON</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/ejQSLoz2D8EmzKVq6</t>
-        </is>
-      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>Monica</t>
-        </is>
-      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>2712 E SUMNER ST</t>
-        </is>
-      </c>
+      <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
@@ -2632,48 +2796,40 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>12345 W LAYTON AVE</t>
+          <t>N168 W1940 MAIN ST</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TO FOLLOW   </t>
-        </is>
-      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/5dpExsTUAgz</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr"/>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
     </row>
@@ -2683,43 +2839,35 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>ROTE OIL #04 GENOA CITY</t>
-        </is>
-      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/TSgMUriHbJPX9hGE7</t>
+          <t>https://goo.gl/maps/hgxGLx2srCs</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DC5-FINANCIAL </t>
-        </is>
-      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>Sonia</t>
-        </is>
-      </c>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Aaron</t>
+        </is>
+      </c>
       <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
@@ -2732,7 +2880,7 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">100 ELIZABETH LANE    </t>
+          <t>5:00 AM START</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -2742,11 +2890,7 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>ROTE OIL  #11 MUKWONAGO - (BP) ARROWHEAD</t>
-        </is>
-      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
@@ -2755,19 +2899,15 @@
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Camry, Equip</t>
-        </is>
-      </c>
+          <t>Casey</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
     </row>
@@ -2779,7 +2919,7 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/DitGJzEvTVhJPxkJ8</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -2791,21 +2931,19 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Sante Fe available, Equip</t>
+          <t>Driver,
+Camry,
+Equip</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>122 ARROWHEAD DR</t>
-        </is>
-      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
@@ -2814,17 +2952,17 @@
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>Jerry D</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>3rd week</t>
         </is>
       </c>
       <c r="X50" t="inlineStr"/>
@@ -2838,7 +2976,7 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">TO FOLLOW   </t>
+          <t>OUTPOST NATURAL FOODS, WAUWATOSA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -2850,30 +2988,34 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/7XkTFZtDFDgGBctz7</t>
-        </is>
-      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>4:45 AM MEET OFFICE</t>
-        </is>
-      </c>
+      <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Kim C</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>3rd week</t>
+        </is>
+      </c>
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
     </row>
@@ -2885,45 +3027,33 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>7000 W STATE ST</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Until 11</t>
-        </is>
-      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Monica</t>
+        </is>
+      </c>
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
@@ -2936,7 +3066,7 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ROTE OIL #05  LAKE GENEVA</t>
+          <t>https://goo.gl/maps/9Apjjj8M6672</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -2945,37 +3075,29 @@
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>4:15 AM MEET SOUTH RACINE COURT (HWY 43 &amp; Y)</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr"/>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
     </row>
@@ -2987,7 +3109,7 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>300 PELLER RD</t>
+          <t>**Help at Metcalfe after**</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -2996,33 +3118,29 @@
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>WILLY STREET COOP, MIDDLETON</t>
-        </is>
-      </c>
+      <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr"/>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
     </row>
@@ -3032,19 +3150,11 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/6fegzT1PbyY5VkDR6</t>
-        </is>
-      </c>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>7:00 AM START</t>
-        </is>
-      </c>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
@@ -3052,20 +3162,24 @@
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>6825 UNIVERSITY AVE</t>
-        </is>
-      </c>
+      <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr"/>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
     </row>
@@ -3074,16 +3188,24 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>EXCEL FINANCIAL</t>
-        </is>
-      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
@@ -3091,20 +3213,24 @@
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/in4JiZtePA62</t>
-        </is>
-      </c>
+      <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>SULLIVAN'S FOODS #241, LENA</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr"/>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
     </row>
@@ -3115,47 +3241,43 @@
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+          <t>Cynthia</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>CONCORD GENERAL STORE, OCONOMOWOC</t>
-        </is>
-      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>4:15 AM MEET SOUTH RACINE COURT (HWY 43 &amp; Y)</t>
-        </is>
-      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>201 DODDS DRIVE</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr"/>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
     </row>
@@ -3166,59 +3288,43 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Driver, Camry</t>
-        </is>
-      </c>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>N6485 COUNTY RD F</t>
-        </is>
-      </c>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/82qhta5RyXsUSC2u9</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr"/>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
     </row>
@@ -3227,46 +3333,45 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Nick</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/X4xEoL3zCRA2</t>
-        </is>
-      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>Driver,
-Optima, Trainer</t>
-        </is>
-      </c>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
-      <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
     </row>
@@ -3275,8 +3380,16 @@
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Sonia</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
@@ -3284,38 +3397,27 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>SULLIVAN'S FOODS #225, FREEPORT</t>
-        </is>
-      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>Curt</t>
-        </is>
-      </c>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>Ashley P</t>
+          <t>Lori</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>@ Store, Equip</t>
+          <t>@ Store,
+Rx</t>
         </is>
       </c>
       <c r="X60" t="inlineStr"/>
@@ -3326,68 +3428,35 @@
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>6:30 AM START</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>2002 W GALENA AVE</t>
-        </is>
-      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>Ian</t>
-        </is>
-      </c>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Nate</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>Driver,
-Red Van</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="X61" t="inlineStr"/>
@@ -3399,60 +3468,37 @@
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>MODAS</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>FULL STORE</t>
-        </is>
-      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Carlie</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/YcFP9FTjTEs94iQh7</t>
-        </is>
-      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>16)</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>Mai</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr"/>
+          <t>Qiana</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>@ Store,
+Supv Rx</t>
+        </is>
+      </c>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
     </row>
@@ -3464,7 +3510,7 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ONEIDA #2022 ONE STOP E &amp; EE, DEPERE</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -3477,33 +3523,25 @@
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>Kim C</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>2nd scan, work w/ Ashley</t>
-        </is>
-      </c>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>17)</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr"/>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr"/>
     </row>
@@ -3515,7 +3553,7 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>790 COUNTY RD EE</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -3524,47 +3562,22 @@
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>@ Store,
-Trainer</t>
-        </is>
-      </c>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>18)</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>Brianna</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
@@ -3583,66 +3596,26 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/VLR8RdvzGgF2</t>
+          <t>METCALFE'S MARKET #560, WAUWATOSA</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>Milwaukee Office</t>
-        </is>
-      </c>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>3rd week</t>
-        </is>
-      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>Elijah</t>
-        </is>
-      </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Elijah</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
       <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr"/>
     </row>
@@ -3654,62 +3627,26 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>6700 W STATE ST</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>Kim G</t>
-        </is>
-      </c>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>Curt</t>
-        </is>
-      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
       <c r="X66" t="inlineStr"/>
       <c r="Y66" t="inlineStr"/>
     </row>
@@ -3721,7 +3658,7 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>MODAS</t>
+          <t>https://goo.gl/maps/hbUxBiCRdt72</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -3730,49 +3667,21 @@
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
+      <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr">
         <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>5:15 AM OFFICE LEAVE TIME</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr"/>
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr"/>
     </row>
@@ -3782,51 +3691,27 @@
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>ONEIDA #2021 ONE STOP 54, ONEIDA</t>
-        </is>
-      </c>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>2nd week</t>
-        </is>
-      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
-      <c r="R68" t="inlineStr">
-        <is>
-          <t>Michelle S</t>
-        </is>
-      </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>@ Store, 1st Day, work w/ Carlie</t>
-        </is>
-      </c>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr"/>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="W68" t="inlineStr"/>
       <c r="X68" t="inlineStr"/>
       <c r="Y68" t="inlineStr"/>
@@ -3836,53 +3721,40 @@
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>W180 HWY 54</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
+          <t>Kim G</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Sante Fe available, Equip</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>Kim G</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>Driver, 
-Sante Fe</t>
-        </is>
-      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
-      <c r="V69" t="inlineStr"/>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="W69" t="inlineStr"/>
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
@@ -3892,41 +3764,40 @@
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/kMzccLLaPd22</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr"/>
+          <t>Casey</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>After Outpost</t>
+        </is>
+      </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr"/>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>PIGGLY WIGGLY #145, KEWASKUM</t>
+        </is>
+      </c>
       <c r="W70" t="inlineStr"/>
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
@@ -3936,24 +3807,28 @@
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Jerry D</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>1st Financial, work w/ Evelin</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>Monica</t>
-        </is>
-      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr"/>
@@ -3961,7 +3836,11 @@
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr"/>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>890 FOND DU LAC AVE</t>
+        </is>
+      </c>
       <c r="W71" t="inlineStr"/>
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
@@ -3973,34 +3852,22 @@
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Jerry S</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>Nick</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>Sonia</t>
-        </is>
-      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
@@ -4008,7 +3875,11 @@
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
-      <c r="V72" t="inlineStr"/>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/iZr1X51Jf9U2</t>
+        </is>
+      </c>
       <c r="W72" t="inlineStr"/>
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
@@ -4020,17 +3891,17 @@
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>Eva</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Optima, Trainer</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
@@ -4038,21 +3909,9 @@
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>Brittany</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
@@ -4071,17 +3930,18 @@
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Annette</t>
+          <t>Evelin</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">@ Store  </t>
+          <t>@ Store,
+Trainer</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -4089,29 +3949,29 @@
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
-      <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr"/>
-      <c r="W74" t="inlineStr"/>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jerry S</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
     </row>
@@ -4122,17 +3982,17 @@
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Heather</t>
+          <t>Jerry S</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">@ Store  </t>
+          <t>@ Store, Until 12:45</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
@@ -4148,8 +4008,16 @@
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
-      <c r="U75" t="inlineStr"/>
-      <c r="V75" t="inlineStr"/>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Nick</t>
+        </is>
+      </c>
       <c r="W75" t="inlineStr"/>
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr"/>
@@ -4161,17 +4029,17 @@
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Katie C</t>
+          <t>Marcia</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>@ Store, 1st Oneidas, work w/ Carlie</t>
+          <t>@ Store, Until 12:45</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
@@ -4187,9 +4055,21 @@
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
-      <c r="U76" t="inlineStr"/>
-      <c r="V76" t="inlineStr"/>
-      <c r="W76" t="inlineStr"/>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Alyssa H</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr"/>
     </row>
@@ -4198,9 +4078,21 @@
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Nagui</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>@ Store, Until 12:45</t>
+        </is>
+      </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
@@ -4214,9 +4106,21 @@
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
-      <c r="U77" t="inlineStr"/>
-      <c r="V77" t="inlineStr"/>
-      <c r="W77" t="inlineStr"/>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Marcia</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
     </row>
@@ -4241,9 +4145,21 @@
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
-      <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr"/>
-      <c r="W78" t="inlineStr"/>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
     </row>
@@ -4253,11 +4169,7 @@
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>5:00 AM MEET SOUTH RACINE COURT (HWY 43 &amp; Y)</t>
-        </is>
-      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
@@ -4272,385 +4184,23 @@
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr"/>
-      <c r="U79" t="inlineStr"/>
-      <c r="V79" t="inlineStr"/>
-      <c r="W79" t="inlineStr"/>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Nagui</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>@ Store, 2nd Pig, work w/ Marcia</t>
+        </is>
+      </c>
       <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr"/>
-      <c r="B80" t="inlineStr"/>
-      <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>6:30 AM START</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr"/>
-      <c r="T80" t="inlineStr"/>
-      <c r="U80" t="inlineStr"/>
-      <c r="V80" t="inlineStr"/>
-      <c r="W80" t="inlineStr"/>
-      <c r="X80" t="inlineStr"/>
-      <c r="Y80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>MODAS</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="inlineStr"/>
-      <c r="T81" t="inlineStr"/>
-      <c r="U81" t="inlineStr"/>
-      <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr"/>
-      <c r="X81" t="inlineStr"/>
-      <c r="Y81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr"/>
-      <c r="B82" t="inlineStr"/>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>KELLEY #58, TYLER CREEK MOBIL, HAMPSHIRE</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr"/>
-      <c r="T82" t="inlineStr"/>
-      <c r="U82" t="inlineStr"/>
-      <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
-      <c r="X82" t="inlineStr"/>
-      <c r="Y82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr"/>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>15N341 RTE 47</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr"/>
-      <c r="S83" t="inlineStr"/>
-      <c r="T83" t="inlineStr"/>
-      <c r="U83" t="inlineStr"/>
-      <c r="V83" t="inlineStr"/>
-      <c r="W83" t="inlineStr"/>
-      <c r="X83" t="inlineStr"/>
-      <c r="Y83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr"/>
-      <c r="B84" t="inlineStr"/>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/SW6S8XqhdGcLz6W2A</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="inlineStr"/>
-      <c r="T84" t="inlineStr"/>
-      <c r="U84" t="inlineStr"/>
-      <c r="V84" t="inlineStr"/>
-      <c r="W84" t="inlineStr"/>
-      <c r="X84" t="inlineStr"/>
-      <c r="Y84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr"/>
-      <c r="B85" t="inlineStr"/>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr"/>
-      <c r="T85" t="inlineStr"/>
-      <c r="U85" t="inlineStr"/>
-      <c r="V85" t="inlineStr"/>
-      <c r="W85" t="inlineStr"/>
-      <c r="X85" t="inlineStr"/>
-      <c r="Y85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr"/>
-      <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Mike G</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="inlineStr"/>
-      <c r="T86" t="inlineStr"/>
-      <c r="U86" t="inlineStr"/>
-      <c r="V86" t="inlineStr"/>
-      <c r="W86" t="inlineStr"/>
-      <c r="X86" t="inlineStr"/>
-      <c r="Y86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr"/>
-      <c r="B87" t="inlineStr"/>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="inlineStr"/>
-      <c r="T87" t="inlineStr"/>
-      <c r="U87" t="inlineStr"/>
-      <c r="V87" t="inlineStr"/>
-      <c r="W87" t="inlineStr"/>
-      <c r="X87" t="inlineStr"/>
-      <c r="Y87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr"/>
-      <c r="B88" t="inlineStr"/>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr"/>
-      <c r="S88" t="inlineStr"/>
-      <c r="T88" t="inlineStr"/>
-      <c r="U88" t="inlineStr"/>
-      <c r="V88" t="inlineStr"/>
-      <c r="W88" t="inlineStr"/>
-      <c r="X88" t="inlineStr"/>
-      <c r="Y88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr"/>
-      <c r="B89" t="inlineStr"/>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
-      <c r="S89" t="inlineStr"/>
-      <c r="T89" t="inlineStr"/>
-      <c r="U89" t="inlineStr"/>
-      <c r="V89" t="inlineStr"/>
-      <c r="W89" t="inlineStr"/>
-      <c r="X89" t="inlineStr"/>
-      <c r="Y89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr"/>
-      <c r="B90" t="inlineStr"/>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Qiana</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr"/>
-      <c r="S90" t="inlineStr"/>
-      <c r="T90" t="inlineStr"/>
-      <c r="U90" t="inlineStr"/>
-      <c r="V90" t="inlineStr"/>
-      <c r="W90" t="inlineStr"/>
-      <c r="X90" t="inlineStr"/>
-      <c r="Y90" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Week1.xlsx
+++ b/Week1.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y79"/>
+  <dimension ref="A1:Y82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sun, Mar 31</t>
+          <t>Sun, Apr 7</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -427,7 +427,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Mon, Apr 1</t>
+          <t>Mon, Apr 8</t>
         </is>
       </c>
       <c r="F1" t="inlineStr"/>
@@ -435,7 +435,7 @@
       <c r="H1" t="inlineStr"/>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Tue, Apr 2</t>
+          <t>Tue, Apr 9</t>
         </is>
       </c>
       <c r="J1" t="inlineStr"/>
@@ -443,7 +443,7 @@
       <c r="L1" t="inlineStr"/>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Wed, Apr 3</t>
+          <t>Wed, Apr 10</t>
         </is>
       </c>
       <c r="N1" t="inlineStr"/>
@@ -451,7 +451,7 @@
       <c r="P1" t="inlineStr"/>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Thu, Apr 4</t>
+          <t>Thu, Apr 11</t>
         </is>
       </c>
       <c r="R1" t="inlineStr"/>
@@ -459,7 +459,7 @@
       <c r="T1" t="inlineStr"/>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Fri, Apr 5</t>
+          <t>Fri, Apr 12</t>
         </is>
       </c>
       <c r="V1" t="inlineStr"/>
@@ -467,7 +467,7 @@
       <c r="X1" t="inlineStr"/>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Sat, Apr 6</t>
+          <t>Sat, Apr 13</t>
         </is>
       </c>
     </row>
@@ -535,23 +535,43 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kim </t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DJ </t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kim </t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Katherine </t>
+        </is>
+      </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DJ </t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
@@ -566,19 +586,35 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Katherine </t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kim </t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Katherine </t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DJ </t>
+        </is>
+      </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
@@ -601,7 +637,11 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Katherine </t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
@@ -661,7 +701,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5:00 AM START</t>
+          <t>5:15 AM MEET BAYSHORE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -669,7 +709,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5:30 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>4:30 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -685,7 +725,7 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>5:00 AM MEET WATERTOWN PLANK</t>
+          <t>5:00 AM MEET AT THE OFFICE</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -693,7 +733,7 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>4:30 AM MEET BAYSHORE</t>
+          <t>5:00 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="W8" t="inlineStr"/>
@@ -708,7 +748,7 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>6:30 AM START</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -732,7 +772,7 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>6:30 AM START</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
@@ -755,7 +795,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>OUTPOST NATURAL FOODS, BAY VIEW</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -779,7 +819,7 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
@@ -802,7 +842,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2826 S KINNICKINNC AVE</t>
+          <t>FESTIVAL #2702, MANITOWOC - LIFO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -810,8 +850,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>PICK #856, RACINE-
-MT PLEASANT</t>
+          <t>MARIANO'S #520 +RX, CHICAGO-BRIDGEPORT</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -819,7 +858,8 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>MARIANO'S #522 +RX, CHICAGO-EDGEWATER</t>
+          <t>MARIANO'S #534 +RX, 
+NEW CITY</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -827,7 +867,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>FESTIVAL #2732, APPLETON - NORTHLAND - LIFO</t>
+          <t>AURORA OUTPATIENT RX #1174 WALWORTH</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -835,7 +875,7 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>PICK #408, TWO RIVERS</t>
+          <t>MARIANO'S #532 +RX, GLENVIEW</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
@@ -850,7 +890,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/5hiyyxywjiH2</t>
+          <t>2151 S 42ND ST</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -858,7 +898,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1202  N GREENBAY RD</t>
+          <t>3145 S ASHLAND AVE</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -866,7 +906,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>5201 N SHERIDAN RD</t>
+          <t>1500 N CLYBOURN AVE</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -874,7 +914,7 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1200 W NORTHLAND AVE</t>
+          <t>525 KENOSHA ST, SUITE C</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -882,7 +922,7 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>1010 22ND STREET</t>
+          <t>2323 CAPITAL DR</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
@@ -897,7 +937,7 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>EVERYONE PLEASE CHECK IN W/ METCALFES AFTER</t>
+          <t>https://goo.gl/maps/ynTuKFekbGQ2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -905,7 +945,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/gCMavYTDGoo</t>
+          <t>https://goo.gl/maps/8Wt7uwiJSHJ2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -913,7 +953,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/9eaE3Q6o8jF2</t>
+          <t>https://goo.gl/maps/jSfCth27mhJ2</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -921,7 +961,7 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/eRWs6b1N24m</t>
+          <t>https://goo.gl/maps/HYXAm9E8G2X4pAUGA</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
@@ -929,7 +969,7 @@
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/5jsT8sqpo6yELUmX9</t>
+          <t>https://goo.gl/maps/ut53mE2zZpL2</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
@@ -954,7 +994,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>SET UP ON REG #7</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
@@ -964,7 +1008,7 @@
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>DJ and Mai will start here, Aurora is 10 min away, 7:30 Start</t>
+          <t>SET UP ON REG #2</t>
         </is>
       </c>
       <c r="W14" t="inlineStr"/>
@@ -983,38 +1027,27 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Katherine</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Camry available, Equip</t>
+          <t>@ Store,
+Sante Fe, Equip</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>*Kim - Lincoln - Sonia meet at the office @ 4:45 am</t>
+          <t xml:space="preserve">NEW FROZEN DRS, BUT NO MAJOR PRODUCT CHANGES PER PAUL </t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
         <is>
@@ -1023,21 +1056,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Jeremiah</t>
+          <t>Katherine</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Equip</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Ian's car to pick up Carlie on the way north @ Grafton</t>
-        </is>
-      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
@@ -1054,10 +1083,15 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Curt</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>@ Store,
+Optima</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
@@ -1065,15 +1099,19 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
@@ -1082,19 +1120,31 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>Driver,
-Optima</t>
+Camry</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
     </row>
@@ -1110,7 +1160,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1122,61 +1172,47 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Kim G</t>
+          <t>Nate</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>*Driver
-Sante Fe, Equip</t>
+          <t>@ Store, Equip</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>Driver,
-Altima</t>
-        </is>
-      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Kim G</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>@ Store,
-Sante Fe, Equip</t>
-        </is>
-      </c>
+          <t>Curt</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
     </row>
@@ -1192,7 +1228,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1204,53 +1240,41 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Driver,
-Altima</t>
-        </is>
-      </c>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>Ian</t>
-        </is>
-      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>@ Grafton</t>
+          <t>Driver,
+Camry</t>
         </is>
       </c>
       <c r="X18" t="inlineStr"/>
@@ -1261,9 +1285,22 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Driver,
+Altima</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
@@ -1272,52 +1309,56 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van,
+Supv Rx</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Driver,
-Sante Fe,
-Rx</t>
+          <t>Rx</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Katherine</t>
+          <t>4:30 AM MEET AT THE OFFICE</t>
         </is>
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Curt</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Supv Rx</t>
+        </is>
+      </c>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
     </row>
@@ -1326,9 +1367,22 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
@@ -1337,53 +1391,45 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>3rd week</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Katherine</t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Kim G</t>
+          <t>6:30 AM START</t>
         </is>
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>w/ Mai
-Aurora @ 7:30</t>
+          <t>Driver,
+Sante Fe</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
@@ -1394,13 +1440,21 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>5:00 AM START</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>Jerry D</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>3rd Financial</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
@@ -1409,60 +1463,50 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Kim C</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>3rd scan, work w/ Evelin</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Kim C</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>3rd week</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Driver,
-Camry
-(Grafton)</t>
-        </is>
-      </c>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
     </row>
@@ -1471,10 +1515,14 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1486,56 +1534,54 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>Anisha</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Driver,
-Red Van</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Anisha</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Driver,
-Red Van</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>FESTIVAL #2735, MAUSTON - LIFO</t>
         </is>
       </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr"/>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
     </row>
@@ -1544,10 +1590,14 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>OUTPOST NATURAL FOODS, MEQUON</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1559,54 +1609,56 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Ashley P</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Early office meet</t>
+          <t>@ Store,
+Rx</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>@ Store,
+Supv Rx</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Annette</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>750 N UNION ST</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr"/>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
     </row>
@@ -1615,10 +1667,14 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>7590 W MEQUON RD</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -1630,53 +1686,52 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
+          <t>Brittany</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Heather</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/8fV8TwF5DKH2</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Brianna</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Driver,
-Red Van</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="X24" t="inlineStr"/>
@@ -1687,10 +1742,14 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/do2xmdVUL8z</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1702,57 +1761,48 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>Brittany</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Early office meet</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>Jerry S</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Mai</t>
+          <t>Elijah</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>w/ DJ
-Aurora @ 7:30</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="X25" t="inlineStr"/>
@@ -1764,11 +1814,7 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>EVERYONE PLEASE CHECK IN W/ METCALFES AFTER</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
@@ -1778,7 +1824,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Eva</t>
+          <t>Elijah</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1789,43 +1835,51 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Laurie</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store, Equip</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr"/>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
     </row>
@@ -1845,24 +1899,23 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Evelin</t>
+          <t>Eva</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>@ Store,
-Trainer</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Anisha</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -1873,31 +1926,31 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Marcia</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr"/>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
     </row>
@@ -1906,21 +1959,13 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jeremiah</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>6:00 AM OFFICE LEAVE TIME</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
@@ -1929,7 +1974,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1940,40 +1985,47 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Ashley P</t>
+          <t>Michael N</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>@ Store,
-Supv Rx</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Michelle</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
+          <t>Curt</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
     </row>
@@ -1982,34 +2034,38 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>3 Stepladders</t>
-        </is>
-      </c>
+          <t>7:00 AM START</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Michael N</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>15)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Eva</t>
+          <t>Nate</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2020,23 +2076,37 @@
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>15)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Nagui</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Driver 1/2
+Red Van</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Qiana</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>@ Store,
+Rx</t>
+        </is>
+      </c>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
     </row>
@@ -2045,34 +2115,38 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Alyssa H</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>@ Store, Trainer</t>
-        </is>
-      </c>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>16)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Qiana</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2081,17 +2155,38 @@
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Driver 1/2
+Red Van</t>
+        </is>
+      </c>
       <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>15)</t>
+        </is>
+      </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>7:30 AM START</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr"/>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
     </row>
@@ -2100,38 +2195,26 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ethan</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>@ Store, work w/ Alyssa H</t>
-        </is>
-      </c>
+          <t>AURORA OUTPATIENT RX #1108, LOMIRA</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>17)</t>
+          <t>16)</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Michael N</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2140,16 +2223,20 @@
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
@@ -2159,44 +2246,36 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Heather</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">@ Store  </t>
-        </is>
-      </c>
+          <t>375 EAST AVENUE, SUITE 1</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Sonia</t>
+        </is>
+      </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>AURORA OUTPATIENT RX #1041, TWO RIVERS</t>
-        </is>
-      </c>
+      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
@@ -2207,13 +2286,17 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/HZvTzhm2zfv</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>DISCOUNT LIQUOR INC, MILWAUKEE</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2222,14 +2305,26 @@
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
-          <t>5300 MEMORIAL DRIVE, SUITE 103</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="W33" t="inlineStr"/>
@@ -2248,7 +2343,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>5031 W OKLAHOMA AVE</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2256,19 +2351,31 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Milwaukee Office</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/7zzPH72TWHs</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="W34" t="inlineStr"/>
@@ -2280,18 +2387,26 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>5:00 AM START</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Camry, Equip</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/hfa57ctXcvNrGJ4NA</t>
+          <t>PICK #308, WAUKESHA - SUNSET EAST</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2299,19 +2414,32 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Kim G</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
-          <t>Help at Pick n Save after if needed</t>
+          <t>PICK #431, FRANKLIN -
+S LOVERS LANE RD</t>
         </is>
       </c>
       <c r="W35" t="inlineStr"/>
@@ -2324,31 +2452,47 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>220 E SUNSET DR</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>PICK #857 +RX, ST FRANCIS - WHITNALL</t>
         </is>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Brittany</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>7780 S LOVERS LANE ROAD</t>
+        </is>
+      </c>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
@@ -2359,54 +2503,48 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>OUTPOST NATURAL FOODS, MILWAUKEE</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/jn6VPu5yR4C2</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>4698 S WHITNALL</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Start at 
-Pick n Save,
-Equip</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/vq4QCMAV1rj</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
     </row>
@@ -2416,53 +2554,48 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>100 E CAPITOL DR</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Until 12:00</t>
-        </is>
-      </c>
+          <t>SET UP ON REG #5</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/fxhnBtwx5642</t>
+        </is>
+      </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
-          <t>Mai</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Start at 
-Pick n Save</t>
-        </is>
-      </c>
+          <t>SET UP ON REG CLOSEST TOWARDS RESTROOMS</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
     </row>
@@ -2472,39 +2605,39 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/n94xpFtHzvE2</t>
-        </is>
-      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Mai</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Until 12:00</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>SMALL RESETS-REMAPPED</t>
+        </is>
+      </c>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
@@ -2515,32 +2648,56 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>EVERYONE PLEASE CHECK IN W/ METCALFES AFTER</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Sante Fe available, Equip</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>15)</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr"/>
@@ -2557,25 +2714,69 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>After Aurora</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Rx</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>16)</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
     </row>
@@ -2584,38 +2785,58 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Cynthia</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Casey</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>17)</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="W42" t="inlineStr"/>
@@ -2627,41 +2848,57 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>6:30 AM MEET WATERTOWN PLANK</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>After Aurora</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Cynthia</t>
+        </is>
+      </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>PICK #366 +RX, HALES CORNERS</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr"/>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
     </row>
@@ -2670,38 +2907,50 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>After Aurora</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>5800 S 108TH ST</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="W44" t="inlineStr"/>
@@ -2713,38 +2962,54 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Until noon, Trainer</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Jerry D</t>
+        </is>
+      </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>4:45 AM MEET WATERTOWN PLANK</t>
+        </is>
+      </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/zX1XvNMo8SU2</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="W45" t="inlineStr"/>
@@ -2756,36 +3021,52 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Sue</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>EAST SIDE MART, JACKSON</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Monica</t>
+        </is>
+      </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
@@ -2799,37 +3080,49 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>N168 W1940 MAIN ST</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
     </row>
@@ -2842,30 +3135,50 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/hgxGLx2srCs</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Until 11:00, Trainer</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Sonia</t>
+        </is>
+      </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>PIGGLY WIGGLY #238, WAUPUN</t>
+        </is>
+      </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Stephanie</t>
         </is>
       </c>
       <c r="W48" t="inlineStr"/>
@@ -2878,36 +3191,64 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>5:00 AM START</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Jeri</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>@ Store, work w/ Stephanie</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>100 GATEWAY DR</t>
+        </is>
+      </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>Casey</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr"/>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
     </row>
@@ -2917,52 +3258,62 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>Josie</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Driver,
-Camry,
-Equip</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Jeri</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/aYPh6GWi7S4ZA8VX6</t>
+        </is>
+      </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>Jerry D</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>3rd week</t>
+          <t>@ Store, 3rd DC5 Scan, work, w/ Carlie</t>
         </is>
       </c>
       <c r="X50" t="inlineStr"/>
@@ -2974,48 +3325,48 @@
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>OUTPOST NATURAL FOODS, WAUWATOSA</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Kim C</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>3rd week</t>
-        </is>
-      </c>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
     </row>
@@ -3025,35 +3376,61 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>7000 W STATE ST</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>@ Store,
+Supv Rx</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Driver,
+Altima, Equip</t>
+        </is>
+      </c>
       <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Monica</t>
-        </is>
-      </c>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
@@ -3064,40 +3441,56 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/9Apjjj8M6672</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>@ Store, 1st DC5 Scan, work w/ Mai</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Savannah</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Cynthia</t>
+        </is>
+      </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
     </row>
@@ -3107,40 +3500,44 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>**Help at Metcalfe after**</t>
-        </is>
-      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>15)</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>@ Store, 2nd DC5 Scan, work w/ Stephanie</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Jerry D</t>
+        </is>
+      </c>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
     </row>
@@ -3161,25 +3558,26 @@
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Driver, 
+Sante Fe</t>
+        </is>
+      </c>
       <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
     </row>
@@ -3188,49 +3586,37 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>COURTESY MEET</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Monica</t>
+        </is>
+      </c>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Elijah</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
     </row>
@@ -3239,45 +3625,41 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>5:30 AM MEET WATERTOWN PLANK</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6:00 AM START </t>
+        </is>
+      </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
     </row>
@@ -3286,45 +3668,45 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Ian</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
     </row>
@@ -3333,45 +3715,33 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Nick</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>AURORA OUTPATIENT RX #1012, CUDAHY</t>
+        </is>
+      </c>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
     </row>
@@ -3380,46 +3750,33 @@
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Sonia</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>AURORA OUTPATIENT RX #1122, HUBERTUS</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>5900 S LAKE DRIVE</t>
+        </is>
+      </c>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>@ Store,
-Rx</t>
-        </is>
-      </c>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
     </row>
@@ -3433,32 +3790,32 @@
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>1303 HIGHWAY 175</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/gJd9TeY5Upy</t>
+        </is>
+      </c>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Milwaukee Office</t>
+        </is>
+      </c>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>15)</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr"/>
     </row>
@@ -3472,7 +3829,11 @@
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/4Vge5Fbx2R4sNroN8</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
@@ -3480,25 +3841,16 @@
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>16)</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Qiana</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>@ Store,
-Supv Rx</t>
-        </is>
-      </c>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
     </row>
@@ -3508,40 +3860,36 @@
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Camry available, Equip</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>17)</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Sarah</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
       <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr"/>
     </row>
@@ -3551,16 +3899,25 @@
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Driver,
+Sante Fe, Equip</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
@@ -3570,21 +3927,9 @@
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>18)</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
       <c r="X64" t="inlineStr"/>
       <c r="Y64" t="inlineStr"/>
     </row>
@@ -3594,16 +3939,24 @@
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>METCALFE'S MARKET #560, WAUWATOSA</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
@@ -3625,15 +3978,19 @@
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>6700 W STATE ST</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
@@ -3656,11 +4013,7 @@
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/hbUxBiCRdt72</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
@@ -3676,11 +4029,7 @@
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>5:15 AM OFFICE LEAVE TIME</t>
-        </is>
-      </c>
+      <c r="V67" t="inlineStr"/>
       <c r="W67" t="inlineStr"/>
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr"/>
@@ -3707,11 +4056,7 @@
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="V68" t="inlineStr"/>
       <c r="W68" t="inlineStr"/>
       <c r="X68" t="inlineStr"/>
       <c r="Y68" t="inlineStr"/>
@@ -3721,24 +4066,16 @@
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Kim G</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Sante Fe available, Equip</t>
-        </is>
-      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>5:00 AM OFFICE LEAVE TIME</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
@@ -3750,11 +4087,7 @@
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="V69" t="inlineStr"/>
       <c r="W69" t="inlineStr"/>
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
@@ -3764,24 +4097,16 @@
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>After Outpost</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>7:00 AM START</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
@@ -3793,11 +4118,7 @@
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>PIGGLY WIGGLY #145, KEWASKUM</t>
-        </is>
-      </c>
+      <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr"/>
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
@@ -3807,24 +4128,16 @@
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>1st Financial, work w/ Evelin</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
@@ -3836,11 +4149,7 @@
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>890 FOND DU LAC AVE</t>
-        </is>
-      </c>
+      <c r="V71" t="inlineStr"/>
       <c r="W71" t="inlineStr"/>
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
@@ -3850,20 +4159,16 @@
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Nick</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>CONDON OIL #230, WAUTOMA</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
@@ -3875,11 +4180,7 @@
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/iZr1X51Jf9U2</t>
-        </is>
-      </c>
+      <c r="V72" t="inlineStr"/>
       <c r="W72" t="inlineStr"/>
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
@@ -3889,24 +4190,16 @@
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>W7711 STATE RD 21</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
@@ -3928,25 +4221,16 @@
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>@ Store,
-Trainer</t>
-        </is>
-      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/Todd4ZTFuYD2</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
@@ -3957,21 +4241,9 @@
       <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Jerry S</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr"/>
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
     </row>
@@ -3980,24 +4252,16 @@
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Jerry S</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>@ Store, Until 12:45</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
@@ -4008,16 +4272,8 @@
       <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>Nick</t>
-        </is>
-      </c>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
       <c r="W75" t="inlineStr"/>
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr"/>
@@ -4027,24 +4283,16 @@
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Marcia</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>@ Store, Until 12:45</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
@@ -4055,21 +4303,9 @@
       <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>Alyssa H</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr"/>
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr"/>
     </row>
@@ -4078,24 +4314,16 @@
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Nagui</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>@ Store, Until 12:45</t>
-        </is>
-      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>CONDON OIL #180, REDGRANITE</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
@@ -4106,21 +4334,9 @@
       <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>Marcia</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
     </row>
@@ -4134,7 +4350,11 @@
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>900 BANNERMAN ST</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
@@ -4145,21 +4365,9 @@
       <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>Michelle</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
     </row>
@@ -4173,7 +4381,11 @@
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/D4tbL8dtjiM2</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
@@ -4184,23 +4396,117 @@
       <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr"/>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>Nagui</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>@ Store, 2nd Pig, work w/ Marcia</t>
-        </is>
-      </c>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr"/>
       <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Driver,
+Camry</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="inlineStr"/>
+      <c r="Y82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Week1.xlsx
+++ b/Week1.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y82"/>
+  <dimension ref="A1:AA81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sun, Apr 7</t>
+          <t>Sun, Apr 14</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -427,7 +427,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Mon, Apr 8</t>
+          <t>Mon, Apr 15</t>
         </is>
       </c>
       <c r="F1" t="inlineStr"/>
@@ -435,7 +435,7 @@
       <c r="H1" t="inlineStr"/>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Tue, Apr 9</t>
+          <t>Tue, Apr 16</t>
         </is>
       </c>
       <c r="J1" t="inlineStr"/>
@@ -443,7 +443,7 @@
       <c r="L1" t="inlineStr"/>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Wed, Apr 10</t>
+          <t>Wed, Apr 17</t>
         </is>
       </c>
       <c r="N1" t="inlineStr"/>
@@ -451,7 +451,7 @@
       <c r="P1" t="inlineStr"/>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Thu, Apr 11</t>
+          <t>Thu, Apr 18</t>
         </is>
       </c>
       <c r="R1" t="inlineStr"/>
@@ -459,7 +459,7 @@
       <c r="T1" t="inlineStr"/>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Fri, Apr 12</t>
+          <t>Fri, Apr 19</t>
         </is>
       </c>
       <c r="V1" t="inlineStr"/>
@@ -467,9 +467,11 @@
       <c r="X1" t="inlineStr"/>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Sat, Apr 13</t>
-        </is>
-      </c>
+          <t>Sat, Apr 20</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr"/>
+      <c r="AA1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -497,6 +499,8 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -524,11 +528,21 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kim </t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bags </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
@@ -537,26 +551,38 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim </t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t xml:space="preserve">DJ </t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Bags 1,2</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DJ </t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t xml:space="preserve">Katherine </t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Bag 4</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim </t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+          <t xml:space="preserve">DJ </t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Bags 1-4</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -564,7 +590,11 @@
           <t xml:space="preserve">Katherine </t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Bag 8,, SB 11</t>
+        </is>
+      </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
@@ -572,9 +602,15 @@
           <t xml:space="preserve">DJ </t>
         </is>
       </c>
-      <c r="W4" t="inlineStr"/>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bags 1-4</t>
+        </is>
+      </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -586,20 +622,20 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Katherine </t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim </t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t xml:space="preserve">DJ </t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Bag 1 SB 11</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
@@ -607,7 +643,11 @@
           <t xml:space="preserve">Katherine </t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Bag 8, SB 11</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -615,13 +655,19 @@
           <t xml:space="preserve">DJ </t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Bags 1,2</t>
+        </is>
+      </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -639,10 +685,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katherine </t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t xml:space="preserve">Kim </t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Bags 5-8</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -657,6 +707,8 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -688,20 +740,22 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5:15 AM MEET BAYSHORE</t>
+          <t>4:15 AM MEET WATERTOWN PLANK</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -709,7 +763,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4:30 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>4:15 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -725,7 +779,7 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>5:00 AM MEET AT THE OFFICE</t>
+          <t>4:45 AM MEET RACINE COURT (HWYY 43 &amp; Y)</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -733,22 +787,32 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>5:00 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>4:30 AM MEET AT THE OFFICE</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>6:30 AM START</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -780,16 +844,26 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PIGGLY WIGGLY #364, MENOMONEE FALLS</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -827,22 +901,32 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>PICK #880 +RX, GLENDALE-SILVER SPRING</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>N81 W15182 APPLETON AVE</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FESTIVAL #2702, MANITOWOC - LIFO</t>
+          <t>PIGGLY WIGGLY #385, KAUKAUNA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -850,7 +934,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>MARIANO'S #520 +RX, CHICAGO-BRIDGEPORT</t>
+          <t>MARIANO'S #535 +RX,ORLAND PARK</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -858,8 +942,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>MARIANO'S #534 +RX, 
-NEW CITY</t>
+          <t>MARIANO'S #536 +FUEL CENTER-RX, WESTMONT</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -867,7 +950,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1174 WALWORTH</t>
+          <t>MARIANO'S #544 +FUEL CENTER-RX, CRYSTAL LAKE</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -875,22 +958,32 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>MARIANO'S #532 +RX, GLENVIEW</t>
+          <t>1735 W SILVER SPRING</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>MILLER &amp; SONS SUPERMARKET, VERONA</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/gqjVNncxKSq</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2151 S 42ND ST</t>
+          <t>300 E ANN ST</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -898,7 +991,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3145 S ASHLAND AVE</t>
+          <t>9504 142ND ST</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -906,7 +999,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1500 N CLYBOURN AVE</t>
+          <t>150 W 63RD ST</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -914,7 +1007,7 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>525 KENOSHA ST, SUITE C</t>
+          <t>105 NORTHWEST HWY</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -922,22 +1015,32 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2323 CAPITAL DR</t>
+          <t>https://goo.gl/maps/SUc4yjc7BVT2</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>210 S MAIN ST</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>FROZEN RESET-REMAPPED</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/ynTuKFekbGQ2</t>
+          <t>https://goo.gl/maps/bhYPnHyrPcz</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -945,7 +1048,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/8Wt7uwiJSHJ2</t>
+          <t>https://goo.gl/maps/x3S76RraqQ82</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -953,7 +1056,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/jSfCth27mhJ2</t>
+          <t>https://goo.gl/maps/9cugGMSRw3F2</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -961,7 +1064,7 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/HYXAm9E8G2X4pAUGA</t>
+          <t>https://goo.gl/maps/PTcufZmqU332</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
@@ -969,12 +1072,18 @@
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/ut53mE2zZpL2</t>
+          <t>SET UP ON REG #1</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/bBRpVEnzkgivH6R69</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -982,13 +1091,17 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>LIQUOR RESET-REMAPPED</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>SET UP ON REG #1</t>
+          <t>SET UP ON REG 1 OR 2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -996,234 +1109,302 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>SET UP ON REG #7</t>
+          <t>SET UP ON REG #1</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>SET UP ON LAST REG BY STORE DIRECTORS OFFICE</t>
+        </is>
+      </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>SET UP ON REG #2</t>
-        </is>
-      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Sante Fe available, Equip</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>@ Store,
-Sante Fe, Equip</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NEW FROZEN DRS, BUT NO MAJOR PRODUCT CHANGES PER PAUL </t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Katherine, Carlie, and Sue will start at Mariano's</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
         <is>
           <t>1)</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>Equip</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>Jeremiah</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>@ Store,
-Optima</t>
+          <t>@ Store, Equip</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Sue</t>
+          <t>Nate</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>Driver,
-Camry</t>
+          <t>@ Store, Equip</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>Aaron</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Curt</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Stephanie</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Casey</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>Casey</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>2)</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Casey</t>
+        </is>
+      </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Curt</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr"/>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Until 11:00</t>
+        </is>
+      </c>
       <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1235,59 +1416,98 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Supv Rx</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Driver,
+Optima</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>3)</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Curt</t>
+        </is>
+      </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
+          <t>Casey</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
         <is>
           <t>Driver,
-Camry</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
+Red Van</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Brittany</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1304,72 +1524,84 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van,
-Supv Rx</t>
-        </is>
-      </c>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Cynthia</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>4)</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Rx</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
-          <t>4:30 AM MEET AT THE OFFICE</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Supv Rx</t>
-        </is>
-      </c>
+          <t>Cynthia</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1377,138 +1609,186 @@
           <t>Ian</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van
+Rx</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Driver,
+Camry,
+Rx</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>5)</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
-          <t>6:30 AM START</t>
+          <t>Jerry D</t>
         </is>
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Driver,
-Sante Fe</t>
-        </is>
-      </c>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Qiana</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jerry D</t>
+          <t>Kailee</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>3rd Financial</t>
+          <t>1st Pig, work w/ Lincoln</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Kailee</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>3rd DC5 Scan, work w/ Stephanie</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>6)</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr"/>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Driver,
+Sante Fe,
+Rx</t>
+        </is>
+      </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Mai</t>
+          <t>Jerry D</t>
         </is>
       </c>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
@@ -1517,7 +1797,7 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1525,65 +1805,86 @@
           <t>Lincoln</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van,
+Trainer</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>w/ Carlie</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
           <t>7)</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
-          <t>FESTIVAL #2735, MAUSTON - LIFO</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr"/>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
+          <t>Kailee</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
@@ -1592,7 +1893,7 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1604,63 +1905,81 @@
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Ashley P</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>@ Store,
-Rx</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van,
+Supv Rx</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
           <t>8)</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>@ Store,
-Supv Rx</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
-          <t>750 N UNION ST</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Anisha</t>
+          <t>Katherine</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
+          <t>Supv Rx</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
@@ -1669,24 +1988,24 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Brianna</t>
+          <t>Anisha</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1697,45 +2016,55 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
           <t>9)</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Brittany</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/8fV8TwF5DKH2</t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
           <t>Brianna</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
@@ -1744,24 +2073,24 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Brittany</t>
+          <t>Ashley P</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1772,54 +2101,89 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
           <t>10)</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Elijah</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
+          <t>Rx</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>Brittany</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Xenia</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1st Pig,
+work w/ Carlie</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1835,53 +2199,60 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Ashley P</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>@ Store, Equip</t>
+          <t>@ Store,
+Supv Rx</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
@@ -1894,7 +2265,7 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1910,49 +2281,63 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Stephanie</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Trainer</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr"/>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
@@ -1960,16 +2345,12 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>6:00 AM OFFICE LEAVE TIME</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1985,49 +2366,51 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Michael N</t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>w/ Carlie</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Curt</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr"/>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
@@ -2035,21 +2418,17 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>7:00 AM START</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Michael N</t>
+          <t>Qiana</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2060,12 +2439,12 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Nate</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2076,39 +2455,27 @@
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Driver 1/2
-Red Van</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Qiana</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>@ Store,
-Rx</t>
-        </is>
-      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
@@ -2116,16 +2483,12 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2141,12 +2504,12 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>15)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Qiana</t>
+          <t>Anisha</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2157,38 +2520,27 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Driver 1/2
-Red Van</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>15)</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
@@ -2196,11 +2548,7 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>AURORA OUTPATIENT RX #1108, LOMIRA</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -2209,12 +2557,12 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>16)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Eva</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2223,23 +2571,21 @@
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>Mai</t>
-        </is>
-      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
@@ -2247,38 +2593,44 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>375 EAST AVENUE, SUITE 1</t>
-        </is>
-      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>16)</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>Sonia</t>
-        </is>
-      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
@@ -2286,11 +2638,7 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/HZvTzhm2zfv</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
@@ -2301,35 +2649,41 @@
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>17)</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>5:00 AM MEET WATERTOWN PLANK</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>PIGGLY WIGGLY #328, FOND DU LAC</t>
         </is>
       </c>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
@@ -2348,103 +2702,94 @@
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>18)</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr"/>
+          <t>Michael N</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>6:30 AM START</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>131 UNIVERSITY AVE</t>
         </is>
       </c>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Camry, Equip</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>PICK #308, WAUKESHA - SUNSET EAST</t>
+          <t>PICK #368 +RX, BROOKFIELD CAL-CAP</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>19)</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr"/>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
-          <t>PICK #431, FRANKLIN -
-S LOVERS LANE RD</t>
+          <t>https://goo.gl/maps/QmMfhkkrDpNxyhyC8</t>
         </is>
       </c>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
@@ -2458,44 +2803,35 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>220 E SUNSET DR</t>
+          <t>17295 WEST CAPITOL DR</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>PICK #857 +RX, ST FRANCIS - WHITNALL</t>
-        </is>
-      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Brittany</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>FESTIVAL #2725, MENASHA -LIFO</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
-          <t>7780 S LOVERS LANE ROAD</t>
+          <t>Trevor to meet with Michelle 
+@ St Pt Target @ 4:30 AM</t>
         </is>
       </c>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
@@ -2509,44 +2845,30 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/jn6VPu5yR4C2</t>
+          <t>https://goo.gl/maps/33rm1Fc6q4o</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>4698 S WHITNALL</t>
-        </is>
-      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Elijah</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>1355 ONEIDA ST</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/vq4QCMAV1rj</t>
-        </is>
-      </c>
+      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
@@ -2560,7 +2882,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>SET UP ON REG #5</t>
+          <t>SET UP REG #1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2568,36 +2890,38 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/fxhnBtwx5642</t>
+          <t>*Crew will start at Marianos - Aurora is 15 min away</t>
         </is>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/i2zDN3asp132</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>SET UP ON REG CLOSEST TOWARDS RESTROOMS</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr"/>
+          <t>Jerry S</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
@@ -2609,38 +2933,44 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>SMALL RESETS-REMAPPED</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>8:00 AM START</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>SMALL RESETS-REMAPPED</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr"/>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Driver, Gold Camry</t>
+        </is>
+      </c>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
@@ -2651,59 +2981,49 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>Sante Fe available, Equip</t>
-        </is>
-      </c>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>15)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Jeremiah</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store, Equip</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Trevor</t>
+        </is>
+      </c>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
@@ -2716,69 +3036,66 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>After Aurora</t>
+          <t>Sante Fe available, Equip</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>Rx</t>
-        </is>
-      </c>
+          <t>AURORA RX #1511, 
+DOWNERS GROVE, ILLINOIS</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>16)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Nate</t>
+          <t>Carlie</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Driver,
+Optima,
+Trainer</t>
         </is>
       </c>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>Heather</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
@@ -2791,7 +3108,7 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2801,47 +3118,50 @@
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>3825 HIGHLAND AVE</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>17)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>DJ</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Driver,
+Altima</t>
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>Aaron</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr"/>
+          <t>Jeremiah</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
@@ -2854,12 +3174,12 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>DJ</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2868,39 +3188,45 @@
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>https://maps.app.goo.gl/tmCsuu4e9oddvAzVA</t>
         </is>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>Marcia</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>Trainer</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
@@ -2913,49 +3239,60 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>After Aurora</t>
-        </is>
-      </c>
+          <t>Jerry D</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>*Park in parking lot B - No charge for parking in that lot</t>
         </is>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>@ Store,
+After Aurora</t>
+        </is>
+      </c>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>Casey</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr"/>
+          <t>Nagui</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
@@ -2968,7 +3305,7 @@
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -2978,43 +3315,38 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Until noon, Trainer</t>
+          <t>Until 12:00,
+Trainer</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Jerry D</t>
+          <t>*Go in main door for physcian office building and go to the right</t>
         </is>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>4:45 AM MEET WATERTOWN PLANK</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
@@ -3027,7 +3359,7 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3037,39 +3369,29 @@
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Monica</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
@@ -3082,49 +3404,59 @@
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Until 11:00, Trainer</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
+        <is>
           <t>8)</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
+      <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Office</t>
         </is>
       </c>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
@@ -3137,53 +3469,60 @@
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Stephanie</t>
+          <t>Xenia</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Until 11:00, Trainer</t>
+          <t>2nd Scan,
+work w/ Mai</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>Carlie</t>
         </is>
       </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>PIGGLY WIGGLY #238, WAUPUN</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr"/>
+          <t>Xenia</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>3rd Festival, work w/ Carlie</t>
+        </is>
+      </c>
       <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
+      <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
-          <t>Stephanie</t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
@@ -3196,61 +3535,55 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Jeri</t>
+          <t>Brittany</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>@ Store, work w/ Stephanie</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
+        <is>
           <t>10)</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>Trainer</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
-          <t>100 GATEWAY DR</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr"/>
+          <t>Annette</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@ Store </t>
+        </is>
+      </c>
       <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
@@ -3263,61 +3596,47 @@
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
+          <t>10)</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
+        <is>
           <t>11)</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Josie</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>Jeri</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/aYPh6GWi7S4ZA8VX6</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr"/>
+          <t>Courtney</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@ Store </t>
+        </is>
+      </c>
       <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
-      <c r="V50" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>@ Store, 3rd DC5 Scan, work, w/ Carlie</t>
-        </is>
-      </c>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
@@ -3330,45 +3649,47 @@
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Jeri</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>@ Store, work w/ Stephanie</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr">
+        <is>
           <t>12)</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@ Store </t>
+        </is>
+      </c>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
@@ -3381,12 +3702,12 @@
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Josie</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3395,37 +3716,27 @@
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Sarah</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>@ Store,
-Supv Rx</t>
-        </is>
-      </c>
+          <t>LEAVE OFFICE @ 5:15 AM</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>Nagui</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>Driver,
-Altima, Equip</t>
+          <t xml:space="preserve">@ Store </t>
         </is>
       </c>
       <c r="T52" t="inlineStr"/>
@@ -3434,6 +3745,8 @@
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
@@ -3446,46 +3759,31 @@
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Lori</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>@ Store, 1st DC5 Scan, work w/ Mai</t>
+          <t>@ Store,
+Rx</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Savannah</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>7:30 AM START</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
@@ -3493,6 +3791,8 @@
       <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
@@ -3503,36 +3803,32 @@
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Michael N</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>@ Store, Trainer</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>15)</t>
-        </is>
-      </c>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>@ Store, 2nd DC5 Scan, work w/ Stephanie</t>
-        </is>
-      </c>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
@@ -3540,6 +3836,8 @@
       <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
@@ -3550,36 +3848,46 @@
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>15)</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>@ Store,
+Supv Rx</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>DENNY'S SUPERVALU, ALGOMA - LIFO</t>
+        </is>
+      </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr">
         <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>Driver, 
-Sante Fe</t>
-        </is>
-      </c>
+          <t>LEAVE OFFICE @ 4:30 AM</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
@@ -3590,26 +3898,34 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>16)</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>COURTESY MEET</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>@ Store, 3rd DC5 Scan, work w/ Michael</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>510 5TH ST</t>
+        </is>
+      </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="S56" t="inlineStr"/>
@@ -3619,6 +3935,8 @@
       <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
@@ -3630,29 +3948,21 @@
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>5:30 AM MEET WATERTOWN PLANK</t>
-        </is>
-      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t xml:space="preserve">6:00 AM START </t>
+          <t>https://goo.gl/maps/LicUiiuHyA9zibVc8</t>
         </is>
       </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="S57" t="inlineStr"/>
@@ -3662,6 +3972,8 @@
       <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
@@ -3673,42 +3985,28 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
+      <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>AURORA OUTPATIENT RX #1030, OSHKOSH</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
@@ -3722,21 +4020,33 @@
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1012, CUDAHY</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr"/>
+          <t>Jerry S</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>414 DOCTORS COURT SUITE 100</t>
+        </is>
+      </c>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
@@ -3744,6 +4054,8 @@
       <c r="W59" t="inlineStr"/>
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
@@ -3757,21 +4069,33 @@
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1122, HUBERTUS</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>5900 S LAKE DRIVE</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr"/>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Sante Fe</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/7jsxtRm7nJ82</t>
+        </is>
+      </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
@@ -3779,6 +4103,8 @@
       <c r="W60" t="inlineStr"/>
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
@@ -3792,25 +4118,29 @@
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>1303 HIGHWAY 175</t>
+          <t>AURORA OUTPATIENT RX #1260, WAUWATOSA</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/gJd9TeY5Upy</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr"/>
+          <t>Annette</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>Milwaukee Office</t>
-        </is>
-      </c>
+      <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
@@ -3818,6 +4148,8 @@
       <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
@@ -3831,28 +4163,51 @@
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/4Vge5Fbx2R4sNroN8</t>
+          <t>1055 NORTH MAYFAIR RD SUITE 100</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Courtney</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="S62" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Driver,
+Camry, Equip</t>
+        </is>
+      </c>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="inlineStr"/>
       <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
@@ -3864,22 +4219,26 @@
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/NV3ZZdgjMJXbNG4s7</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Katherine</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Camry available, Equip</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="P63" t="inlineStr"/>
@@ -3892,6 +4251,8 @@
       <c r="W63" t="inlineStr"/>
       <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
@@ -3902,26 +4263,25 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Driver,
-Sante Fe, Equip</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Heather</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
@@ -3932,6 +4292,8 @@
       <c r="W64" t="inlineStr"/>
       <c r="X64" t="inlineStr"/>
       <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
@@ -3944,23 +4306,35 @@
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>DJ</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
+          <t>Equip</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Marcia</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
@@ -3971,6 +4345,8 @@
       <c r="W65" t="inlineStr"/>
       <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
@@ -3981,16 +4357,8 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>Ian</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
@@ -4006,6 +4374,8 @@
       <c r="W66" t="inlineStr"/>
       <c r="X66" t="inlineStr"/>
       <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
@@ -4033,6 +4403,8 @@
       <c r="W67" t="inlineStr"/>
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
@@ -4044,11 +4416,19 @@
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LEAVE OFFICE @ 5:30 AM </t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
@@ -4060,6 +4440,8 @@
       <c r="W68" t="inlineStr"/>
       <c r="X68" t="inlineStr"/>
       <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
@@ -4073,13 +4455,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
-          <t>5:00 AM OFFICE LEAVE TIME</t>
+          <t>7:00 AM START</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
@@ -4091,6 +4477,8 @@
       <c r="W69" t="inlineStr"/>
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
@@ -4104,7 +4492,7 @@
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4122,6 +4510,8 @@
       <c r="W70" t="inlineStr"/>
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
@@ -4135,7 +4525,7 @@
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>CONDON OIL #150, KIEL</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4153,6 +4543,8 @@
       <c r="W71" t="inlineStr"/>
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
@@ -4166,7 +4558,7 @@
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
-          <t>CONDON OIL #230, WAUTOMA</t>
+          <t>84 E PARK AVE</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4184,6 +4576,8 @@
       <c r="W72" t="inlineStr"/>
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
@@ -4197,7 +4591,7 @@
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
-          <t>W7711 STATE RD 21</t>
+          <t>https://goo.gl/maps/HE1oXp7RZPP2</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4215,6 +4609,8 @@
       <c r="W73" t="inlineStr"/>
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
@@ -4228,7 +4624,7 @@
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/Todd4ZTFuYD2</t>
+          <t>TO FOLLOW</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4246,6 +4642,8 @@
       <c r="W74" t="inlineStr"/>
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
@@ -4259,7 +4657,7 @@
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -4277,6 +4675,8 @@
       <c r="W75" t="inlineStr"/>
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
+      <c r="AA75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
@@ -4290,7 +4690,7 @@
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>CONDON OIL #165, CHILTON</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -4308,6 +4708,8 @@
       <c r="W76" t="inlineStr"/>
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr"/>
+      <c r="AA76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
@@ -4321,7 +4723,7 @@
       <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
-          <t>CONDON OIL #180, REDGRANITE</t>
+          <t>613 N MADISON ST</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -4339,6 +4741,8 @@
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr"/>
+      <c r="AA77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
@@ -4352,7 +4756,7 @@
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
-          <t>900 BANNERMAN ST</t>
+          <t>https://goo.gl/maps/idhDxXsWdCT2</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -4370,6 +4774,8 @@
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr"/>
+      <c r="AA78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
@@ -4381,11 +4787,7 @@
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/D4tbL8dtjiM2</t>
-        </is>
-      </c>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
@@ -4401,6 +4803,8 @@
       <c r="W79" t="inlineStr"/>
       <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
@@ -4411,9 +4815,21 @@
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Camry, Equip</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
@@ -4428,6 +4844,8 @@
       <c r="W80" t="inlineStr"/>
       <c r="X80" t="inlineStr"/>
       <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
@@ -4440,17 +4858,17 @@
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Katherine</t>
+          <t>Michelle</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>@ Store, Until 11:15</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -4467,46 +4885,8 @@
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr"/>
-      <c r="B82" t="inlineStr"/>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>Driver,
-Camry</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr"/>
-      <c r="T82" t="inlineStr"/>
-      <c r="U82" t="inlineStr"/>
-      <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
-      <c r="X82" t="inlineStr"/>
-      <c r="Y82" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Week1.xlsx
+++ b/Week1.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA81"/>
+  <dimension ref="A1:Y88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sun, Apr 14</t>
+          <t>Sun, Apr 21</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -427,7 +427,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Mon, Apr 15</t>
+          <t>Mon, Apr 22</t>
         </is>
       </c>
       <c r="F1" t="inlineStr"/>
@@ -435,7 +435,7 @@
       <c r="H1" t="inlineStr"/>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Tue, Apr 16</t>
+          <t>Tue, Apr 23</t>
         </is>
       </c>
       <c r="J1" t="inlineStr"/>
@@ -443,7 +443,7 @@
       <c r="L1" t="inlineStr"/>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Wed, Apr 17</t>
+          <t>Wed, Apr 24</t>
         </is>
       </c>
       <c r="N1" t="inlineStr"/>
@@ -451,7 +451,7 @@
       <c r="P1" t="inlineStr"/>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Thu, Apr 18</t>
+          <t>Thu, Apr 25</t>
         </is>
       </c>
       <c r="R1" t="inlineStr"/>
@@ -459,7 +459,7 @@
       <c r="T1" t="inlineStr"/>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Fri, Apr 19</t>
+          <t>Fri, Apr 26</t>
         </is>
       </c>
       <c r="V1" t="inlineStr"/>
@@ -467,11 +467,9 @@
       <c r="X1" t="inlineStr"/>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Sat, Apr 20</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr"/>
-      <c r="AA1" t="inlineStr"/>
+          <t>Sat, Apr 27</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -499,8 +497,6 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -528,21 +524,11 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kim </t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bags </t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
@@ -551,12 +537,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DJ </t>
+          <t xml:space="preserve">Kim </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bags 1,2</t>
+          <t>Bags 5-7</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -568,19 +554,19 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Bag 4</t>
+          <t>Bag 8</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DJ </t>
+          <t xml:space="preserve">Katherine </t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Bags 1-4</t>
+          <t>Bag 8</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -592,25 +578,23 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Bag 8,, SB 11</t>
+          <t xml:space="preserve">Bag 8 </t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DJ </t>
+          <t xml:space="preserve">Katherine </t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Bags 1-4</t>
+          <t>Bag 8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -622,42 +606,50 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Katherine </t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bag 2</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DJ </t>
+          <t xml:space="preserve">Kim </t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Bag 1 SB 11</t>
+          <t>Bag 5, SB 11</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katherine </t>
+          <t xml:space="preserve">Kim </t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Bag 8, SB 11</t>
+          <t>Bag 5, SB 11</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DJ </t>
+          <t xml:space="preserve">Kim </t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Bags 1,2</t>
+          <t>Bag 5, SB 11</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -666,8 +658,6 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -685,12 +675,12 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim </t>
+          <t xml:space="preserve">DJ </t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Bags 5-8</t>
+          <t>Bags 1-3</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -699,16 +689,22 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DJ </t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Bags 1-3</t>
+        </is>
+      </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -740,22 +736,24 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>4:30 AM MEET OFFICE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4:15 AM MEET WATERTOWN PLANK</t>
+          <t>5:00 AM MEET OFFICE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -763,7 +761,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4:15 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>5:30 AM START</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -771,7 +769,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4:30 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t xml:space="preserve">5:30 AM START </t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -779,7 +777,7 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>4:45 AM MEET RACINE COURT (HWYY 43 &amp; Y)</t>
+          <t>5:00 AM MEET OFFICE</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -787,29 +785,27 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>5:00 AM MEET OFFICE</t>
         </is>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>4:30 AM MEET AT THE OFFICE</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>6:00 AM START</t>
@@ -820,7 +816,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -828,7 +824,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -844,24 +840,18 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PIGGLY WIGGLY #364, MENOMONEE FALLS</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -877,7 +867,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>ROTE OIL #6 HUBERTUS</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -885,7 +875,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>ROTE OIL #10 MUKWONAGO - ROCHESTER</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -893,7 +883,7 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
@@ -901,24 +891,18 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>PICK #880 +RX, GLENDALE-SILVER SPRING</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>N81 W15182 APPLETON AVE</t>
+          <t>MILLER &amp; SONS SUPERMARKET, MT HOREB</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -926,7 +910,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PIGGLY WIGGLY #385, KAUKAUNA</t>
+          <t>ROTE OIL #03 TWIN LAKES</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -934,7 +918,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>MARIANO'S #535 +RX,ORLAND PARK</t>
+          <t>1306 HWY 175</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -942,7 +926,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>MARIANO'S #536 +FUEL CENTER-RX, WESTMONT</t>
+          <t>1060 N ROCHESTER ST</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -950,7 +934,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>MARIANO'S #544 +FUEL CENTER-RX, CRYSTAL LAKE</t>
+          <t>ROTE OIL #1 PADDOCK LAKE- BRASS BALL</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -958,24 +942,18 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>1735 W SILVER SPRING</t>
+          <t>ROTE OIL #14 TREVOR (CITGO)</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>MILLER &amp; SONS SUPERMARKET, VERONA</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/gqjVNncxKSq</t>
+          <t>1845 SPRINGDALE ST</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -983,7 +961,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>300 E ANN ST</t>
+          <t>475 N LAKE AVE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -991,7 +969,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>9504 142ND ST</t>
+          <t>https://goo.gl/maps/SZRuQ4FHA1cX2ZmC8</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -999,7 +977,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>150 W 63RD ST</t>
+          <t>https://goo.gl/maps/dmvR5bTHLs1Cbjcr5</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -1007,7 +985,7 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>105 NORTHWEST HWY</t>
+          <t>25406 75TH ST</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -1015,24 +993,18 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/SUc4yjc7BVT2</t>
+          <t>12617 ANTIOCH RD</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>210 S MAIN ST</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FROZEN RESET-REMAPPED</t>
+          <t>https://goo.gl/maps/zSVBPqJx7dR2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -1040,7 +1012,7 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/bhYPnHyrPcz</t>
+          <t>https://goo.gl/maps/jNgJR8hii6jJGZQP7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1048,7 +1020,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/x3S76RraqQ82</t>
+          <t>TO FOLLOW</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1056,7 +1028,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/9cugGMSRw3F2</t>
+          <t xml:space="preserve">TO FOLLOW   </t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -1064,7 +1036,7 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/PTcufZmqU332</t>
+          <t>https://goo.gl/maps/LTa4ckcczx5qc8269</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
@@ -1072,18 +1044,12 @@
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>SET UP ON REG #1</t>
+          <t>https://goo.gl/maps/xA9YMzPGc6Vhxi5r8</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>https://maps.app.goo.gl/bBRpVEnzkgivH6R69</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -1093,7 +1059,7 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>LIQUOR RESET-REMAPPED</t>
+          <t xml:space="preserve">TO FOLLOW   </t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1101,7 +1067,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>SET UP ON REG 1 OR 2</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1109,7 +1075,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>SET UP ON REG #1</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -1117,18 +1083,20 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>SET UP ON LAST REG BY STORE DIRECTORS OFFICE</t>
+          <t>TO FOLLOW</t>
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1138,66 +1106,56 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sante Fe available, Equip</t>
+          <t>@ Store, Equip</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ROTE OIL #7 MILWAUKEE</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Katherine, Carlie, and Sue will start at Mariano's</t>
+          <t>ROTE OIL #12 MUKWONAGO - (AMOCO) GREENWALD</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+          <t>ROTE OIL #13 TREVOR (BP)</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1207,86 +1165,52 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mai</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jeremiah</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>ROTE OIL #04 GENOA CITY</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>5931 N 91ST ST</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>909 GREENWALD CT</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>ROTE OIL #2 PADDOCK LAKE- 75TH ST</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>12511 ANTIOCH RD</t>
         </is>
       </c>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Curt</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1296,94 +1220,57 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Trainer</t>
-        </is>
-      </c>
+          <t xml:space="preserve">100 ELIZABETH LANE    </t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>https://goo.gl/maps/cw58s7atAhTAGHNd7</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/ejQSLoz2D8EmzKVq6</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>25555 75TH ST</t>
         </is>
       </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Until 11:00</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/iu3xzNwgJ32esP5RA</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1393,100 +1280,48 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>https://goo.gl/maps/DitGJzEvTVhJPxkJ8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Supv Rx</t>
-        </is>
-      </c>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Driver,
-Optima</t>
-        </is>
-      </c>
+          <t xml:space="preserve">TO FOLLOW   </t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Curt</t>
+          <t>https://goo.gl/maps/5UyWWXXbzXMaVnv99</t>
         </is>
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+      <c r="Y18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1496,91 +1331,56 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Brittany</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Driver,
-Altima</t>
-        </is>
-      </c>
+          <t xml:space="preserve">TO FOLLOW   </t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>EXCEL FINANCIAL</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t xml:space="preserve">DC5-FINANCIAL </t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1590,7 +1390,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Evelin</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1599,89 +1399,64 @@
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van
-Rx</t>
-        </is>
-      </c>
+          <t>ROTE OIL #8 ELM GROVE</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Driver,
-Camry,
-Rx</t>
-        </is>
-      </c>
+          <t>ROTE OIL  #11 MUKWONAGO - (BP) ARROWHEAD</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Driver,
+Altima</t>
+        </is>
+      </c>
       <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1691,7 +1466,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Qiana</t>
+          <t>Ashley P</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1700,408 +1475,262 @@
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kailee</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>1st Pig, work w/ Lincoln</t>
-        </is>
-      </c>
+          <t>ROTE OIL #05  LAKE GENEVA</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>13395 WATERTOWN PLANK RD</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Kailee</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>3rd DC5 Scan, work w/ Stephanie</t>
-        </is>
-      </c>
+          <t>122 ARROWHEAD DR</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
           <t>Driver,
-Sante Fe,
-Rx</t>
+Camry</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
+      <c r="Y21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van,
-Trainer</t>
-        </is>
-      </c>
+          <t>300 PELLER RD</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>https://goo.gl/maps/5zXAKpcRHDmA17UK9</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>w/ Carlie</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/7XkTFZtDFDgGBctz7</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Kailee</t>
-        </is>
-      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
+      <c r="Y22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Brittany</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>https://goo.gl/maps/6fegzT1PbyY5VkDR6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van,
-Supv Rx</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>Monica</t>
-        </is>
-      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
+      <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Supv Rx</t>
-        </is>
-      </c>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
+      <c r="Y23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Sonia</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Sue</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
+      <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
+      <c r="Y24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Qiana</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>ROTE OIL #09 GREENFIELD</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2111,53 +1740,23 @@
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
+      <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Rx</t>
-        </is>
-      </c>
+          <t>AURORA OUTPATIENT RX #1360 PLEASANT PRAIRIE</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>Brittany</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
@@ -2166,93 +1765,49 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Xenia</t>
+          <t>DJ</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1st Pig,
-work w/ Carlie</t>
+          <t>Driver, Altima</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Elijah</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>12345 W LAYTON AVE</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Sonia</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>@ Store,
-Supv Rx</t>
-        </is>
-      </c>
+          <t>AURORA OUTPATIENT RX #1263 MENOMONEE FALLS</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
+      <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Mai</t>
+          <t>12500 AURORA DR,  SUITE 1000</t>
         </is>
       </c>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
@@ -2263,81 +1818,35 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/TSgMUriHbJPX9hGE7</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Trainer</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Elijah</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>N84 W16889 MENOMONEE AVE, STE 140</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
+      <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>https://goo.gl/maps/cBS6XeGsHAkpmwWFA</t>
         </is>
       </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>Sarah</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
@@ -2348,69 +1857,31 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>w/ Carlie</t>
-        </is>
-      </c>
+          <t>5:30 AM MEET COLLEGE (SOUTHWEST)</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://maps.app.goo.gl/oLhxTANtiQDoDPgy5</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
@@ -2418,64 +1889,58 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>4:30 AM MEET WATERTOWN PLANK</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Qiana</t>
+          <t>Katherine</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Camry available, Equip</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sante Fe available, Equip</t>
+        </is>
+      </c>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
@@ -2483,54 +1948,46 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>15)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Sante Fe available, Equip</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -2539,8 +1996,6 @@
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
@@ -2548,44 +2003,46 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Until 12:00</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>15)</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>AURORA OUTPATIENT RX #1150, KENOSHA</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
@@ -2593,28 +2050,24 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>PIGGLY WIGGLY #387, WINNECONNE</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>16)</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>10400 75TH ST</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
@@ -2623,14 +2076,12 @@
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>6:00 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
@@ -2638,37 +2089,29 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>910 E MAIN ST</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>17)</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/K5ZSZyLo7jH2</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
-          <t>5:00 AM MEET WATERTOWN PLANK</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="S33" t="inlineStr"/>
@@ -2676,14 +2119,12 @@
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
-          <t>PIGGLY WIGGLY #328, FOND DU LAC</t>
+          <t>6:30 AM START</t>
         </is>
       </c>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
@@ -2691,37 +2132,33 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/yDNLLcepRYT2</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>5:15 AM MEET SOUTH RACINE COURT (HWY 43 &amp; Y)</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>18)</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Michael N</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>ENTER BY URGENT CARE</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
-          <t>6:30 AM START</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
@@ -2729,14 +2166,12 @@
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
-          <t>131 UNIVERSITY AVE</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
@@ -2750,31 +2185,19 @@
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>PICK #368 +RX, BROOKFIELD CAL-CAP</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>19)</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>PICK #862 +RX, OAK CREEK - MEGA MALL</t>
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
@@ -2782,40 +2205,64 @@
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/QmMfhkkrDpNxyhyC8</t>
+          <t>FESTIVAL #2710, MT PLEASANT - LIFO</t>
         </is>
       </c>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Driver,
+Sante Fe, Equip</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>17295 WEST CAPITOL DR</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Driver,
+Sante Fe, Equip</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
-          <t>FESTIVAL #2725, MENASHA -LIFO</t>
+          <t>8770 S HOWELL AVE</t>
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
@@ -2823,162 +2270,195 @@
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
-          <t>Trevor to meet with Michelle 
-@ St Pt Target @ 4:30 AM</t>
+          <t>5740 WASHINGTON AVE</t>
         </is>
       </c>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Driver,
+Optima,
+Trainer</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/33rm1Fc6q4o</t>
+          <t>AURORA OUTPATIENT RX #1178 LAKE GENEVA</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1355 ONEIDA ST</t>
+          <t>https://goo.gl/maps/whvAchGPZWU2</t>
         </is>
       </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/PRSb1wjmEbn</t>
+        </is>
+      </c>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Jerry D</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Work w/ Carlie</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>SET UP REG #1</t>
+          <t>146 E GENEVA SQ</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>*Crew will start at Marianos - Aurora is 15 min away</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/i2zDN3asp132</t>
-        </is>
-      </c>
+      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Jerry S</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Lincoln</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>SMALL RESETS-REMAPPED</t>
+          <t>https://goo.gl/maps/7Ady9a9f1nnktk6MA</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>8:00 AM START</t>
-        </is>
-      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t>Brianna</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Driver, Gold Camry</t>
+          <t>@ Store, Equip</t>
         </is>
       </c>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Sonia</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -2988,50 +2468,56 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>5:00 AM MEET OFFICE</t>
         </is>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Jeremiah</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>Cynthia</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>Trevor</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr"/>
+          <t>Aaron</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>@ Store, Until 12:00</t>
+        </is>
+      </c>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Sue</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
@@ -3046,56 +2532,48 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Sante Fe available, Equip</t>
+          <t>Driver,
+Sante Fe, Equip</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>AURORA RX #1511, 
-DOWNERS GROVE, ILLINOIS</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>Mai</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>Driver,
-Optima,
-Trainer</t>
+          <t>Until 12:00</t>
         </is>
       </c>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>Heather</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Casey</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
@@ -3113,7 +2591,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3121,47 +2599,36 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>3825 HIGHLAND AVE</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>Driver,
-Altima</t>
-        </is>
-      </c>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>Jeremiah</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Curt</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
@@ -3172,61 +2639,47 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>After Aurora</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/tmCsuu4e9oddvAzVA</t>
+          <t>PICK #178 +RX, MADISON-SHOPKO DR</t>
         </is>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr"/>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Until 11:00</t>
+        </is>
+      </c>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>Marcia</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Cynthia</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
@@ -3237,62 +2690,52 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>*Park in parking lot B - No charge for parking in that lot</t>
+          <t>2502 SHOPKO DRIVE</t>
         </is>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Katherine</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>@ Store,
-After Aurora</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>Nagui</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Driver,
+Red Van</t>
         </is>
       </c>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
@@ -3303,50 +2746,56 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Mai</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Until 12:00,
-Trainer</t>
-        </is>
-      </c>
+          <t>5:15 AM MEET WATERTOWN PLANK</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>*Go in main door for physcian office building and go to the right</t>
+          <t>https://goo.gl/maps/mzSRZ7wKTvq</t>
         </is>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
           <t>Lincoln</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Driver,
+Optima</t>
+        </is>
+      </c>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
-      <c r="Z45" t="inlineStr"/>
-      <c r="AA45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
@@ -3357,41 +2806,52 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>6:30 AM START</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RESET-REMAPPED </t>
+        </is>
+      </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr"/>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>@ Store,
+Supv Rx</t>
+        </is>
+      </c>
       <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
-      <c r="AA46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
@@ -3402,61 +2862,47 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Until 11:00, Trainer</t>
-        </is>
-      </c>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr"/>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr"/>
-      <c r="AA47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
@@ -3467,62 +2913,59 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Xenia</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>2nd Scan,
-work w/ Mai</t>
-        </is>
-      </c>
+          <t>FESTIVAL #2708, OSHKOSH - LIFO</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr"/>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Xenia</t>
+          <t>Elijah</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>3rd Festival, work w/ Carlie</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr"/>
-      <c r="AA48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
@@ -3533,57 +2976,55 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Brittany</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>2415 WESTOWNE AVE</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Sue</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Annette</t>
+          <t>Eva</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t xml:space="preserve">@ Store </t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Sonia</t>
+        </is>
+      </c>
       <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
-      <c r="Z49" t="inlineStr"/>
-      <c r="AA49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
@@ -3594,39 +3035,39 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/SYenrFArvdC2</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Curt</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Courtney</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t xml:space="preserve">@ Store </t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T50" t="inlineStr"/>
@@ -3635,8 +3076,6 @@
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr"/>
-      <c r="AA50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
@@ -3647,39 +3086,40 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Jeri</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>@ Store, work w/ Stephanie</t>
-        </is>
-      </c>
+          <t>LIQUOR RESET-REMAPPED</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Cynthia</t>
+        </is>
+      </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t>Makeda</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t xml:space="preserve">@ Store </t>
+          <t>@ Store,
+4th Scan</t>
         </is>
       </c>
       <c r="T51" t="inlineStr"/>
@@ -3688,8 +3128,6 @@
       <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
-      <c r="AA51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
@@ -3700,53 +3138,58 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Josie</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>*Carlie to drop off the Optima at the office</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>LEAVE OFFICE @ 5:15 AM</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van,
+Supv Rx</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Nagui</t>
+          <t>Michael N</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t xml:space="preserve">@ Store </t>
+          <t>@ Store,
+Trainer</t>
         </is>
       </c>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>7:00 AM START</t>
+        </is>
+      </c>
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr"/>
-      <c r="AA52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
@@ -3757,42 +3200,48 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Jerry D</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>15)</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Qiana</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
         <is>
           <t>@ Store,
 Rx</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>7:30 AM START</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>MODAS / WINTAKES</t>
+        </is>
+      </c>
       <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr"/>
-      <c r="AA53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
@@ -3805,39 +3254,57 @@
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Michael N</t>
+          <t>Jeremiah</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>@ Store, Trainer</t>
+          <t>@ Store, Equip</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>16)</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>SCHIERL #59, WESTON - CTY RD J</t>
+        </is>
+      </c>
       <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr"/>
-      <c r="AA54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
@@ -3850,44 +3317,63 @@
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>15)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Carlie</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>@ Store,
-Supv Rx</t>
+          <t>*drop Optima, Trainer</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>DENNY'S SUPERVALU, ALGOMA - LIFO</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr"/>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Driver,
+Camry,
+Rx</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>17)</t>
+        </is>
+      </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>LEAVE OFFICE @ 4:30 AM</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr"/>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>6606 COUNTY RD J</t>
+        </is>
+      </c>
       <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
-      <c r="AA55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
@@ -3900,43 +3386,62 @@
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>16)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>18)</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
           <t>Victoria</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>@ Store, 3rd DC5 Scan, work w/ Michael</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>510 5TH ST</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr"/>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/sr7sZYxNPHacNdrP8</t>
+        </is>
+      </c>
       <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
-      <c r="AA56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
@@ -3947,24 +3452,36 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/LicUiiuHyA9zibVc8</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr"/>
+          <t>Jeri</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
@@ -3972,8 +3489,6 @@
       <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
-      <c r="AA57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
@@ -3984,29 +3499,55 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>AURORA OUTPATIENT RX #1030, OSHKOSH</t>
-        </is>
-      </c>
+      <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jeremiah</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr"/>
-      <c r="AA58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
@@ -4017,45 +3558,60 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Jerry S</t>
+          <t>Makeda</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>@ Store, Equip</t>
+          <t>@ Store,
+3rd Scan</t>
         </is>
       </c>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr">
         <is>
-          <t>414 DOCTORS COURT SUITE 100</t>
+          <t>5:00 AM MEET WATERTOWN PLANK</t>
         </is>
       </c>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
-      <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Annette</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@ Store  </t>
+        </is>
+      </c>
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="inlineStr"/>
-      <c r="AA59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
@@ -4066,45 +3622,60 @@
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>Nate</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Sante Fe</t>
+          <t>@ Store,
+Trainer</t>
         </is>
       </c>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/7jsxtRm7nJ82</t>
+          <t>6:30 AM START</t>
         </is>
       </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jacqui</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
-      <c r="Z60" t="inlineStr"/>
-      <c r="AA60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
@@ -4115,22 +3686,30 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1260, WAUWATOSA</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
+          <t>Courtney</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Annette</t>
+          <t>Savannah</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -4140,16 +3719,30 @@
       </c>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Driver, Dark Grey Camry</t>
+        </is>
+      </c>
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr"/>
-      <c r="AA61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
@@ -4160,22 +3753,30 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>1055 NORTH MAYFAIR RD SUITE 100</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
+          <t>Ethan</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Courtney</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -4184,30 +3785,31 @@
         </is>
       </c>
       <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>Driver,
-Camry, Equip</t>
-        </is>
-      </c>
+          <t>FESTIVAL #2716, APPLETON - DARBOY - LIFO</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Trevor</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>meet Michelle 6:15 AM @ Point Target</t>
+        </is>
+      </c>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr"/>
-      <c r="AA62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
@@ -4218,22 +3820,30 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/NV3ZZdgjMJXbNG4s7</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
+          <t>Jerry S</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>16)</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -4243,7 +3853,11 @@
       </c>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>W3195 VAN ROY RD</t>
+        </is>
+      </c>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
@@ -4251,8 +3865,6 @@
       <c r="W63" t="inlineStr"/>
       <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr"/>
-      <c r="Z63" t="inlineStr"/>
-      <c r="AA63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
@@ -4263,28 +3875,32 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Marcia</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>Heather</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/57s41PSXiLJ2</t>
+        </is>
+      </c>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
@@ -4292,8 +3908,6 @@
       <c r="W64" t="inlineStr"/>
       <c r="X64" t="inlineStr"/>
       <c r="Y64" t="inlineStr"/>
-      <c r="Z64" t="inlineStr"/>
-      <c r="AA64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
@@ -4306,47 +3920,41 @@
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>Michelle</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>@ Store, Until 11:30</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>Marcia</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RESET-REMAPPED </t>
+        </is>
+      </c>
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Milwaukee Office</t>
+        </is>
+      </c>
       <c r="W65" t="inlineStr"/>
       <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr"/>
-      <c r="Z65" t="inlineStr"/>
-      <c r="AA65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
@@ -4357,9 +3965,21 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Nagui</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>@ Store, Until 2</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
@@ -4370,12 +3990,14 @@
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
       <c r="W66" t="inlineStr"/>
       <c r="X66" t="inlineStr"/>
       <c r="Y66" t="inlineStr"/>
-      <c r="Z66" t="inlineStr"/>
-      <c r="AA66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
@@ -4386,25 +4008,51 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Pang</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>@ Store, 2nd Festival, work w/ Carlie, Until 2</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>4:45 AM MEET AT BAYSHORE</t>
+        </is>
+      </c>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Jeremiah</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
       <c r="W67" t="inlineStr"/>
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr"/>
-      <c r="Z67" t="inlineStr"/>
-      <c r="AA67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
@@ -4416,23 +4064,27 @@
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LEAVE OFFICE @ 5:30 AM </t>
-        </is>
-      </c>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>6:30 AM START</t>
         </is>
       </c>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Casey</t>
+        </is>
+      </c>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
@@ -4440,8 +4092,6 @@
       <c r="W68" t="inlineStr"/>
       <c r="X68" t="inlineStr"/>
       <c r="Y68" t="inlineStr"/>
-      <c r="Z68" t="inlineStr"/>
-      <c r="AA68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
@@ -4453,32 +4103,43 @@
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>7:00 AM START</t>
-        </is>
-      </c>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr"/>
+          <t>MODAS</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>TOB ONLY</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Driver,
+Altima</t>
+        </is>
+      </c>
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
       <c r="V69" t="inlineStr"/>
       <c r="W69" t="inlineStr"/>
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
-      <c r="Z69" t="inlineStr"/>
-      <c r="AA69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
@@ -4492,26 +4153,41 @@
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>Office</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>ONEIDA #2022 ONE STOP E &amp; EE, DEPERE</t>
+        </is>
+      </c>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
       <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr"/>
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
-      <c r="Z70" t="inlineStr"/>
-      <c r="AA70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
@@ -4525,26 +4201,40 @@
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
-          <t>CONDON OIL #150, KIEL</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>790 COUNTY RD EE</t>
+        </is>
+      </c>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>Jerry D</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>work w/ Lincoln</t>
+        </is>
+      </c>
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
       <c r="V71" t="inlineStr"/>
       <c r="W71" t="inlineStr"/>
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
-      <c r="Z71" t="inlineStr"/>
-      <c r="AA71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
@@ -4556,19 +4246,27 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>84 E PARK AVE</t>
-        </is>
-      </c>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/VLR8RdvzGgF2</t>
+        </is>
+      </c>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
@@ -4576,8 +4274,6 @@
       <c r="W72" t="inlineStr"/>
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
-      <c r="Z72" t="inlineStr"/>
-      <c r="AA72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
@@ -4589,28 +4285,38 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/HE1oXp7RZPP2</t>
-        </is>
-      </c>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TO FOLLOW  </t>
+        </is>
+      </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>Trainer</t>
+        </is>
+      </c>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
       <c r="V73" t="inlineStr"/>
       <c r="W73" t="inlineStr"/>
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
-      <c r="Z73" t="inlineStr"/>
-      <c r="AA73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
@@ -4622,19 +4328,27 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>TO FOLLOW</t>
-        </is>
-      </c>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>MODAS</t>
+        </is>
+      </c>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
@@ -4642,8 +4356,6 @@
       <c r="W74" t="inlineStr"/>
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
-      <c r="Z74" t="inlineStr"/>
-      <c r="AA74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
@@ -4655,19 +4367,27 @@
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>ONEIDA #2021 ONE STOP 54, ONEIDA</t>
+        </is>
+      </c>
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Sonia</t>
+        </is>
+      </c>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr"/>
@@ -4675,8 +4395,6 @@
       <c r="W75" t="inlineStr"/>
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr"/>
-      <c r="Z75" t="inlineStr"/>
-      <c r="AA75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
@@ -4688,28 +4406,38 @@
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>CONDON OIL #165, CHILTON</t>
-        </is>
-      </c>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>W180 HWY 54</t>
+        </is>
+      </c>
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr"/>
       <c r="V76" t="inlineStr"/>
       <c r="W76" t="inlineStr"/>
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr"/>
-      <c r="Z76" t="inlineStr"/>
-      <c r="AA76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
@@ -4721,28 +4449,38 @@
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>613 N MADISON ST</t>
-        </is>
-      </c>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/kMzccLLaPd22</t>
+        </is>
+      </c>
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>Nagui</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr"/>
       <c r="V77" t="inlineStr"/>
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
-      <c r="Z77" t="inlineStr"/>
-      <c r="AA77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
@@ -4754,28 +4492,38 @@
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/idhDxXsWdCT2</t>
-        </is>
-      </c>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TO FOLLOW  </t>
+        </is>
+      </c>
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>Pang</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>@ Store, 2nd Festival, work w/ Lincoln</t>
+        </is>
+      </c>
       <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr"/>
       <c r="V78" t="inlineStr"/>
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
-      <c r="Z78" t="inlineStr"/>
-      <c r="AA78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
@@ -4791,7 +4539,11 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>MODAS</t>
+        </is>
+      </c>
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr"/>
@@ -4803,8 +4555,6 @@
       <c r="W79" t="inlineStr"/>
       <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr"/>
-      <c r="Z79" t="inlineStr"/>
-      <c r="AA79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
@@ -4815,24 +4565,16 @@
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>Camry, Equip</t>
-        </is>
-      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>ONEIDA #2024 TRAVEL CENTER, PULASKI</t>
+        </is>
+      </c>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
@@ -4844,8 +4586,6 @@
       <c r="W80" t="inlineStr"/>
       <c r="X80" t="inlineStr"/>
       <c r="Y80" t="inlineStr"/>
-      <c r="Z80" t="inlineStr"/>
-      <c r="AA80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
@@ -4856,24 +4596,16 @@
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>Michelle</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>@ Store, Until 11:15</t>
-        </is>
-      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>5939 OLD 29 DRIVE</t>
+        </is>
+      </c>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
@@ -4885,8 +4617,256 @@
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr"/>
-      <c r="Z81" t="inlineStr"/>
-      <c r="AA81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/P7gcbpqmHRw</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="inlineStr"/>
+      <c r="Y82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="inlineStr"/>
+      <c r="X83" t="inlineStr"/>
+      <c r="Y83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Jerry S</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr"/>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
+      <c r="W84" t="inlineStr"/>
+      <c r="X84" t="inlineStr"/>
+      <c r="Y84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Driver,
+Optima</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
+      <c r="W85" t="inlineStr"/>
+      <c r="X85" t="inlineStr"/>
+      <c r="Y85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>1st Modas</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
+      <c r="W86" t="inlineStr"/>
+      <c r="X86" t="inlineStr"/>
+      <c r="Y86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
+      <c r="W87" t="inlineStr"/>
+      <c r="X87" t="inlineStr"/>
+      <c r="Y87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Heather</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="inlineStr"/>
+      <c r="X88" t="inlineStr"/>
+      <c r="Y88" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Week1.xlsx
+++ b/Week1.xlsx
@@ -3949,7 +3949,7 @@
       <c r="U65" t="inlineStr"/>
       <c r="V65" t="inlineStr">
         <is>
-          <t>Milwaukee Office</t>
+          <t>Madison Office</t>
         </is>
       </c>
       <c r="W65" t="inlineStr"/>

--- a/Week1.xlsx
+++ b/Week1.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y88"/>
+  <dimension ref="A1:Y74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sun, Apr 21</t>
+          <t>Sun, Apr 28</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -427,7 +427,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Mon, Apr 22</t>
+          <t>Mon, Apr 29</t>
         </is>
       </c>
       <c r="F1" t="inlineStr"/>
@@ -435,7 +435,7 @@
       <c r="H1" t="inlineStr"/>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Tue, Apr 23</t>
+          <t>Tue, Apr 30</t>
         </is>
       </c>
       <c r="J1" t="inlineStr"/>
@@ -443,7 +443,7 @@
       <c r="L1" t="inlineStr"/>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Wed, Apr 24</t>
+          <t>Wed, May 1</t>
         </is>
       </c>
       <c r="N1" t="inlineStr"/>
@@ -451,7 +451,7 @@
       <c r="P1" t="inlineStr"/>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Thu, Apr 25</t>
+          <t>Thu, May 2</t>
         </is>
       </c>
       <c r="R1" t="inlineStr"/>
@@ -459,7 +459,7 @@
       <c r="T1" t="inlineStr"/>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Fri, Apr 26</t>
+          <t>Fri, May 3</t>
         </is>
       </c>
       <c r="V1" t="inlineStr"/>
@@ -467,7 +467,7 @@
       <c r="X1" t="inlineStr"/>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Sat, Apr 27</t>
+          <t>Sat, May 4</t>
         </is>
       </c>
     </row>
@@ -549,19 +549,19 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katherine </t>
+          <t xml:space="preserve">DJ </t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Bag 8</t>
+          <t>Bags 2-3</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katherine </t>
+          <t xml:space="preserve">Ian </t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -573,24 +573,24 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katherine </t>
+          <t xml:space="preserve">Kim </t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bag 8 </t>
+          <t>Bags 5-8</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katherine </t>
+          <t xml:space="preserve">DJ </t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Bag 8</t>
+          <t>Bags 2-4</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -608,54 +608,54 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katherine </t>
+          <t xml:space="preserve">DJ </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bag 2</t>
+          <t>Bag 1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim </t>
+          <t xml:space="preserve">Katherine </t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Bag 5, SB 11</t>
+          <t>Bag 1, SB 11</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kim </t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Bag 5, SB 11</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim </t>
+          <t xml:space="preserve">Katherine </t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Bag 5, SB 11</t>
+          <t>Bags 1-3</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Katherine </t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bag 1, SB 11</t>
+        </is>
+      </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
     </row>
@@ -664,23 +664,27 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ian </t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bag 8</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DJ </t>
+          <t xml:space="preserve">Kim </t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Bags 1-3</t>
+          <t>Bag 7, SB 10</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -689,20 +693,20 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DJ </t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>Bags 1-3</t>
-        </is>
-      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kim </t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bag 8, SB 10</t>
+        </is>
+      </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
     </row>
@@ -720,15 +724,27 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ian </t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Bag 8</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Altima service being done this day</t>
+        </is>
+      </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
@@ -739,11 +755,7 @@
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4:30 AM MEET OFFICE</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
@@ -751,54 +763,30 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>5:00 AM MEET OFFICE</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>5:30 AM START</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5:30 AM START </t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>5:00 AM MEET OFFICE</t>
-        </is>
-      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>5:00 AM MEET OFFICE</t>
-        </is>
-      </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
@@ -808,7 +796,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>4:30 AM MEET WATERTOWN PLANK</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -816,7 +804,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>5:45 AM MEET WATERTOWN PLANK</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -824,7 +812,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>4:15 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -832,7 +820,7 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>4:45 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
@@ -840,7 +828,7 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>5:15 AM MEET BAYSHORE</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
@@ -849,17 +837,13 @@
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -867,7 +851,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>ROTE OIL #6 HUBERTUS</t>
+          <t>6:30 AM START</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -875,7 +859,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>ROTE OIL #10 MUKWONAGO - ROCHESTER</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -883,7 +867,7 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
@@ -891,7 +875,7 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
@@ -900,17 +884,13 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>MILLER &amp; SONS SUPERMARKET, MT HOREB</t>
-        </is>
-      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ROTE OIL #03 TWIN LAKES</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -918,7 +898,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1306 HWY 175</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -926,7 +906,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1060 N ROCHESTER ST</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -934,7 +914,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>ROTE OIL #1 PADDOCK LAKE- BRASS BALL</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -942,7 +922,7 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>ROTE OIL #14 TREVOR (CITGO)</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
@@ -951,17 +931,13 @@
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1845 SPRINGDALE ST</t>
-        </is>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>475 N LAKE AVE</t>
+          <t>WEBSTER'S MARKETPLACE, RIPON</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -969,7 +945,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/SZRuQ4FHA1cX2ZmC8</t>
+          <t>FESTIVAL #2696, HARTFORD - LIFO</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -977,7 +953,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/dmvR5bTHLs1Cbjcr5</t>
+          <t>MARIANO'S #503, CHICAGO - LAKESHORE EAST</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -985,7 +961,7 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>25406 75TH ST</t>
+          <t>MARIANO'S #510 +RX, HARWOOD HEIGHTS</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -993,7 +969,7 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>12617 ANTIOCH RD</t>
+          <t>PICK #343, PLYMOUTH</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
@@ -1002,17 +978,13 @@
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/zSVBPqJx7dR2</t>
-        </is>
-      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/jNgJR8hii6jJGZQP7</t>
+          <t>1188 W FOND DU LAC STREET</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1020,7 +992,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>1275 BELL AVE</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1028,7 +1000,8 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t xml:space="preserve">TO FOLLOW   </t>
+          <t>333 EAST BENTON PL, 
+SUITE 206</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -1036,7 +1009,7 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/LTa4ckcczx5qc8269</t>
+          <t>7401 WEST LAWRENCE AVENUE</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
@@ -1044,7 +1017,7 @@
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/xA9YMzPGc6Vhxi5r8</t>
+          <t>2643 EASTERN AVE</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
@@ -1059,7 +1032,7 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">TO FOLLOW   </t>
+          <t>https://goo.gl/maps/EWZS96J1G93UVQgi7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1067,7 +1040,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>https://goo.gl/maps/PUKTG8ru54xUWw7d9</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1075,7 +1048,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>https://goo.gl/maps/Gwa8pwADYxr</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -1083,7 +1056,7 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>https://goo.gl/maps/Nv5frfdAopr</t>
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
@@ -1091,7 +1064,7 @@
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>https://goo.gl/maps/uM51wiLfFCA2</t>
         </is>
       </c>
       <c r="W14" t="inlineStr"/>
@@ -1099,42 +1072,26 @@
       <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Sarah</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>SMALL RESET-REMAPPED</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>ROTE OIL #7 MILWAUKEE</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>ROTE OIL #12 MUKWONAGO - (AMOCO) GREENWALD</t>
+          <t>NEED TO PAY FOR PARKING AT THIS SITE!</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
@@ -1142,7 +1099,7 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>SET UP ON REG #5</t>
         </is>
       </c>
       <c r="S15" t="inlineStr"/>
@@ -1150,7 +1107,7 @@
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>ROTE OIL #13 TREVOR (BP)</t>
+          <t>**Car swap happening with Jeremiah and Ian</t>
         </is>
       </c>
       <c r="W15" t="inlineStr"/>
@@ -1158,529 +1115,663 @@
       <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ROTE OIL #04 GENOA CITY</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>5931 N 91ST ST</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>909 GREENWALD CT</t>
-        </is>
-      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>ROTE OIL #2 PADDOCK LAKE- 75TH ST</t>
-        </is>
-      </c>
+      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>12511 ANTIOCH RD</t>
-        </is>
-      </c>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">100 ELIZABETH LANE    </t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>@ Store,
+Sante Fe, Equip</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/cw58s7atAhTAGHNd7</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/ejQSLoz2D8EmzKVq6</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>25555 75TH ST</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr"/>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>@ Store,
+Sante Fe, Equip</t>
+        </is>
+      </c>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/iu3xzNwgJ32esP5RA</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/DitGJzEvTVhJPxkJ8</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t xml:space="preserve">TO FOLLOW   </t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/5UyWWXXbzXMaVnv99</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Casey</t>
+        </is>
+      </c>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">TO FOLLOW   </t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>*After Aurora</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC5-FINANCIAL </t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Cynthia</t>
+        </is>
+      </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Katherine</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>After Aurora</t>
         </is>
       </c>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>ROTE OIL #8 ELM GROVE</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>ROTE OIL  #11 MUKWONAGO - (BP) ARROWHEAD</t>
+          <t>Jerry D</t>
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Katherine</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>Driver,
+Red Van</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
           <t>Driver,
-Altima</t>
+Red Van**</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ROTE OIL #05  LAKE GENEVA</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>13395 WATERTOWN PLANK RD</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>122 ARROWHEAD DR</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>Driver,
-Camry</t>
-        </is>
-      </c>
+          <t>Jerry D</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jerry D</t>
+        </is>
+      </c>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>300 PELLER RD</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/5zXAKpcRHDmA17UK9</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/7XkTFZtDFDgGBctz7</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Driver,
+Camry</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>After Aurora</t>
+        </is>
+      </c>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Brittany</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/6fegzT1PbyY5VkDR6</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Monica</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Sonia</t>
+        </is>
+      </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr"/>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>After Aurora</t>
+        </is>
+      </c>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>@ Store,
+Help Kim</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr"/>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>Mai</t>
         </is>
       </c>
       <c r="W24" t="inlineStr"/>
@@ -1688,73 +1779,85 @@
       <c r="Y24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Qiana</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Katherine</t>
+          <t>Eva</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>ROTE OIL #09 GREENFIELD</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr"/>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1360 PLEASANT PRAIRIE</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr"/>
+          <t>Heather</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>@ Store, Until 1:15</t>
+        </is>
+      </c>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
     </row>
@@ -1765,47 +1868,79 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>Evelin</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Driver, Altima</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>12345 W LAYTON AVE</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Stephanie</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1263 MENOMONEE FALLS</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr"/>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>12500 AURORA DR,  SUITE 1000</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr"/>
+          <t>Jeremiah</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>@ Store, Until 1:15</t>
+        </is>
+      </c>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
     </row>
@@ -1814,37 +1949,81 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/TSgMUriHbJPX9hGE7</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Sue</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>N84 W16889 MENOMONEE AVE, STE 140</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr"/>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/cBS6XeGsHAkpmwWFA</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr"/>
+          <t>Marcia</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>@ Store, Until 1:15</t>
+        </is>
+      </c>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
     </row>
@@ -1853,33 +2032,85 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Makeda</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>@ Store, work w/ Michael</t>
+        </is>
+      </c>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>5:30 AM MEET COLLEGE (SOUTHWEST)</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr"/>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/oLhxTANtiQDoDPgy5</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr"/>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Nagui</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>@ Store, Until 1:15</t>
+        </is>
+      </c>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
     </row>
@@ -1888,57 +2119,73 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>4:30 AM MEET WATERTOWN PLANK</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>Michael N</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>@ Store, Trainer</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Katherine</t>
+          <t>Makeda</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Camry available, Equip</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Sante Fe available, Equip</t>
-        </is>
-      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
     </row>
@@ -1947,47 +2194,67 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>Qiana</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>Michael N</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr"/>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Makeda</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Sante Fe available, Equip</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -2002,44 +2269,65 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>15)</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>@ Store, work w/ Michael</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>16)</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Mai</t>
+          <t>Qiana</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Until 12:00</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>AURORA OUTPATIENT RX #1150, KENOSHA</t>
-        </is>
-      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15) </t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Michael N</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>@ Store,
+Rx</t>
+        </is>
+      </c>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>5:15 AM MEET BAYSHORE</t>
+        </is>
+      </c>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
@@ -2050,11 +2338,7 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>PIGGLY WIGGLY #387, WINNECONNE</t>
-        </is>
-      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -2062,21 +2346,29 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>10400 75TH ST</t>
-        </is>
-      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16) </t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
-          <t>6:00 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="W32" t="inlineStr"/>
@@ -2089,11 +2381,7 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>910 E MAIN ST</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
@@ -2103,23 +2391,33 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/K5ZSZyLo7jH2</t>
+          <t>6:30 AM RACINE COURT 
+(HWY 43 &amp; Y)</t>
         </is>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17) </t>
+        </is>
+      </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr"/>
+          <t>Qiana</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>@ Store,
+Supv Rx</t>
+        </is>
+      </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
-          <t>6:30 AM START</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="W33" t="inlineStr"/>
@@ -2134,7 +2432,7 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/yDNLLcepRYT2</t>
+          <t>5:30 AM MEET WATERTOWN PLANK</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -2142,7 +2440,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>5:15 AM MEET SOUTH RACINE COURT (HWY 43 &amp; Y)</t>
+          <t>5:15 AM OFFICE LEAVE TIME</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2150,23 +2448,31 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>ENTER BY URGENT CARE</t>
+          <t>7:00 AM START</t>
         </is>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>18)</t>
+        </is>
+      </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr"/>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>AURORA OUTPATIENT RX #1227, PLYMOUTH</t>
         </is>
       </c>
       <c r="W34" t="inlineStr"/>
@@ -2179,7 +2485,11 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
@@ -2191,21 +2501,21 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>EXCEL FINANCIAL</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>PICK #862 +RX, OAK CREEK - MEGA MALL</t>
-        </is>
-      </c>
+      <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
-          <t>FESTIVAL #2710, MT PLEASANT - LIFO</t>
+          <t>2600 KILEY WAY, SUITE 100</t>
         </is>
       </c>
       <c r="W35" t="inlineStr"/>
@@ -2217,22 +2527,13 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Driver,
-Sante Fe, Equip</t>
-        </is>
-      </c>
+          <t>EXCEL FINANCIAL</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
@@ -2242,35 +2543,22 @@
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>Driver,
-Sante Fe, Equip</t>
-        </is>
-      </c>
+          <t>KANSASVILLE CITGO QUICK MART</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>8770 S HOWELL AVE</t>
-        </is>
-      </c>
+      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
-          <t>5740 WASHINGTON AVE</t>
+          <t>https://goo.gl/maps/oK3no3iSD5kXaRa59</t>
         </is>
       </c>
       <c r="W36" t="inlineStr"/>
@@ -2282,40 +2570,26 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Driver,
-Optima,
-Trainer</t>
-        </is>
-      </c>
+          <t>KOHN'S FILLING STATION, KEWASKUM</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1178 LAKE GENEVA</t>
+          <t>AURORA OUTPATIENT RX #1102, HARTFORD</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>23010 DURAND AVE</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
@@ -2323,17 +2597,13 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/whvAchGPZWU2</t>
+          <t>5:30 AM REQUIRED MEET AT GARFIELD AVE PICK N SAVE</t>
         </is>
       </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/PRSb1wjmEbn</t>
-        </is>
-      </c>
+      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
@@ -2343,41 +2613,54 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Work w/ Carlie</t>
-        </is>
-      </c>
+          <t>890 FOND DU LAC AVE</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>146 E GENEVA SQ</t>
+          <t>1640 E SUMNER ST, SUITE 100</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/QZs8ZSjv9eL2</t>
+        </is>
+      </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Pick n Save address is:
+1100 E Garfield Ave</t>
+        </is>
+      </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
     </row>
@@ -2386,14 +2669,10 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>https://goo.gl/maps/CJnRNDyortw</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -2401,46 +2680,38 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/7Ady9a9f1nnktk6MA</t>
+          <t>https://goo.gl/maps/umuyQZyC8FT2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>5:45 AM START</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>Cynthia</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
     </row>
@@ -2449,14 +2720,10 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t xml:space="preserve">TO FOLLOW </t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -2468,36 +2735,33 @@
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>5:00 AM MEET OFFICE</t>
+          <t>EXCEL FINANCIAL</t>
         </is>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>@ Store, Until 12:00</t>
+          <t>Driver,
+Optima</t>
         </is>
       </c>
       <c r="X40" t="inlineStr"/>
@@ -2508,14 +2772,10 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sue</t>
+          <t>EXCEL FINANCIAL</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -2527,50 +2787,33 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Katherine</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Driver,
-Sante Fe, Equip</t>
+          <t>Camry, Equip</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>TWIN LAKES CITGO, TWIN LAKES</t>
         </is>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Mai</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>Until 12:00</t>
-        </is>
-      </c>
+          <t>ASCENSION IP CSMM COLUMBIA ST MARY'S WOMEN'S MEDICAL CENTER</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
@@ -2581,51 +2824,35 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>KOHN'S FILLING STATION 259, CAMPBELLSPORT</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Monica</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>410 N LAKE AVE</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>2323 N LAKE DR</t>
         </is>
       </c>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>Curt</t>
-        </is>
-      </c>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
@@ -2636,7 +2863,11 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>259 N FOND DU LAC AVE</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
@@ -2646,35 +2877,23 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>PICK #178 +RX, MADISON-SHOPKO DR</t>
+          <t>https://goo.gl/maps/k9s2GwpMbH32</t>
         </is>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>Until 11:00</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/86sUJVyjHnUKr7tv8</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="W43" t="inlineStr"/>
@@ -2687,53 +2906,40 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/WCsZpx5SMsA2</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>6:15 AM OFFICE LEAVE TIME</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>2502 SHOPKO DRIVE</t>
-        </is>
-      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>In order for everyone to get to the site efficiently and avoid anyone</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
     </row>
@@ -2749,51 +2955,43 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>5:15 AM MEET WATERTOWN PLANK</t>
+          <t>7:00 AM START</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/mzSRZ7wKTvq</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Driver,
+Altima, Equip</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>getting confused on where to go, all must use the meet above</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
+      <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>Driver,
-Optima</t>
-        </is>
-      </c>
+          <t>PICK #416, WAUWATOSA - WALNUT</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
     </row>
@@ -2802,51 +3000,54 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>6:30 AM START</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t xml:space="preserve">RESET-REMAPPED </t>
+          <t>Katherine</t>
         </is>
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
+      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr">
         <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>@ Store,
-Supv Rx</t>
-        </is>
-      </c>
+          <t>DJ to drop off the Altima at Lutters in AM.  Use Camry until after Fri</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
+      <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
-          <t>Mai</t>
+          <t>1717 N MAYFAIR RD</t>
         </is>
       </c>
       <c r="W46" t="inlineStr"/>
@@ -2858,14 +3059,27 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Driver,
+Altima</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>AURORA OUTPATIENT RX #1750 ELKHORN</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -2874,30 +3088,14 @@
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
+      <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>https://goo.gl/maps/96AWc1YH6do</t>
         </is>
       </c>
       <c r="W47" t="inlineStr"/>
@@ -2916,51 +3114,35 @@
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>FESTIVAL #2708, OSHKOSH - LIFO</t>
+          <t>201 E MORRISSEY DRIVE, SUITE 100</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Elijah</t>
+          <t>Katherine</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Equip</t>
         </is>
       </c>
       <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
+      <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>SET UP ON REG #5</t>
         </is>
       </c>
       <c r="W48" t="inlineStr"/>
@@ -2979,49 +3161,33 @@
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2415 WESTOWNE AVE</t>
+          <t>https://goo.gl/maps/xYN7FT5gMzQk78dv6</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>5:15 AM OFFICE LEAVE TIME</t>
         </is>
       </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Curt</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>Sonia</t>
-        </is>
-      </c>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
@@ -3032,48 +3198,57 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>6:30 AM MEET OFFICE</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/SYenrFArvdC2</t>
-        </is>
-      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Curt</t>
+          <t>7:00 AM START</t>
         </is>
       </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>DJ</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Driver,
+Camry</t>
         </is>
       </c>
       <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
     </row>
@@ -3083,49 +3258,69 @@
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>7:00 AM START</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>LIQUOR RESET-REMAPPED</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Sante Fe, Equip</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Makeda</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>@ Store,
-4th Scan</t>
+          <t>Driver,
+Optima</t>
         </is>
       </c>
       <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Aaron</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Until 12:00</t>
+        </is>
+      </c>
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
     </row>
@@ -3135,56 +3330,49 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>*Carlie to drop off the Optima at the office</t>
-        </is>
-      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van,
-Supv Rx</t>
-        </is>
-      </c>
+          <t>CONDON OIL #120, PRINCETON</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Michael N</t>
+          <t>Lori</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>@ Store,
-Trainer</t>
+          <t>@ Garfield meet too!</t>
         </is>
       </c>
       <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
+          <t>Curt</t>
         </is>
       </c>
       <c r="W52" t="inlineStr"/>
@@ -3197,49 +3385,56 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>GAUGERT'S BUSS STOP, SULLIVAN</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Jerry D</t>
+          <t>811 OLD GREEN LAKE RD</t>
         </is>
       </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>15)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>Qiana</t>
+          <t>Mai</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>@ Store,
-Rx</t>
+          <t>Until 12:00</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>MODAS / WINTAKES</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr"/>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>After Aurora</t>
+        </is>
+      </c>
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
     </row>
@@ -3249,57 +3444,49 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>141 MAIN ST</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Jeremiah</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>6:30 AM MEET OFFICE</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>https://maps.app.goo.gl/b9UWz2Uc4DF9epFR8</t>
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>16)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>Sarah</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>SCHIERL #59, WESTON - CTY RD J</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="W54" t="inlineStr"/>
@@ -3312,63 +3499,49 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/TEUfEX2J1AE2</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>*drop Optima, Trainer</t>
-        </is>
-      </c>
+          <t>7:00 AM START</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>Driver,
-Camry,
-Rx</t>
-        </is>
-      </c>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>17)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>6606 COUNTY RD J</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="W55" t="inlineStr"/>
@@ -3381,65 +3554,48 @@
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>APPROX 10:00/11:00 AM START</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+          <t>EXCEL FINANCIAL</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>CONDON OIL #220, GREEN LAKE</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>18)</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/sr7sZYxNPHacNdrP8</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr"/>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Until 10:00</t>
+        </is>
+      </c>
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
     </row>
@@ -3449,44 +3605,48 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>CONCORD GENERAL STORE, OCONOMOWOC</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Jeri</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>514 MILL ST</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
     </row>
@@ -3496,54 +3656,50 @@
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>RON'S MARKET, HELENVILLE</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>N6485 COUNTY RD F</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://maps.app.goo.gl/9KFU2mUvQ1KBEVvg9</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>Jeremiah</t>
+          <t>Ashley P</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>@ Store, Equip</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="X58" t="inlineStr"/>
@@ -3555,59 +3711,46 @@
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>W3094 HWY 18</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>https://goo.gl/maps/X4xEoL3zCRA2</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>Makeda</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>@ Store,
-3rd Scan</t>
-        </is>
-      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr">
         <is>
-          <t>5:00 AM MEET WATERTOWN PLANK</t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>Annette</t>
+          <t>Elijah</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t xml:space="preserve">@ Store  </t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="X59" t="inlineStr"/>
@@ -3619,54 +3762,50 @@
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/pyYX7wkpwom</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>APPROX 10:00/10:30 AM START</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Nate</t>
+          <t>Michelle</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>@ Store,
-Trainer</t>
+          <t>@ Store, 
+PC Box</t>
         </is>
       </c>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>6:30 AM START</t>
-        </is>
-      </c>
+      <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>Jacqui</t>
+          <t>Eva</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -3686,30 +3825,22 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Courtney</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Savannah</t>
+          <t>Courtney</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -3719,26 +3850,22 @@
       </c>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t>Evelin</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>Driver, Dark Grey Camry</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="X61" t="inlineStr"/>
@@ -3749,63 +3876,66 @@
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Driver,
+Optima, Equip</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Ethan</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>CONDON OIL #195, THERESA</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>15)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Optima
+Help Michelle,
+Take DC5's</t>
         </is>
       </c>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>FESTIVAL #2716, APPLETON - DARBOY - LIFO</t>
-        </is>
-      </c>
+      <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>Trevor</t>
+          <t>Lori</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>meet Michelle 6:15 AM @ Point Target</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="X62" t="inlineStr"/>
@@ -3816,53 +3946,49 @@
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Jerry S</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>213 N MILWAUKEE</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>16)</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>W3195 VAN ROY RD</t>
-        </is>
-      </c>
+      <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr"/>
     </row>
@@ -3875,37 +4001,37 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Marcia</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/dBrycqMgUwF2</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/57s41PSXiLJ2</t>
-        </is>
-      </c>
+      <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr"/>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>15)</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X64" t="inlineStr"/>
       <c r="Y64" t="inlineStr"/>
     </row>
@@ -3918,41 +4044,37 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>Michelle</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>@ Store, Until 11:30</t>
-        </is>
-      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RESET-REMAPPED </t>
-        </is>
-      </c>
+      <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr"/>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>16)</t>
+        </is>
+      </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>Madison Office</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr"/>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr"/>
     </row>
@@ -3967,22 +4089,27 @@
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Nagui</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>@ Store, Until 2</t>
+          <t>Driver,
+Optima, Equip</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
@@ -3990,11 +4117,7 @@
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
+      <c r="V66" t="inlineStr"/>
       <c r="W66" t="inlineStr"/>
       <c r="X66" t="inlineStr"/>
       <c r="Y66" t="inlineStr"/>
@@ -4010,43 +4133,23 @@
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Pang</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>@ Store, 2nd Festival, work w/ Carlie, Until 2</t>
-        </is>
-      </c>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>4:45 AM MEET AT BAYSHORE</t>
-        </is>
-      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>Jeremiah</t>
-        </is>
-      </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
@@ -4068,27 +4171,19 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>6:30 AM START</t>
-        </is>
-      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="R68" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr"/>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="W68" t="inlineStr"/>
       <c r="X68" t="inlineStr"/>
       <c r="Y68" t="inlineStr"/>
@@ -4107,36 +4202,19 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>MODAS</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>TOB ONLY</t>
-        </is>
-      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>Driver,
-Altima</t>
-        </is>
-      </c>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
-      <c r="V69" t="inlineStr"/>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
       <c r="W69" t="inlineStr"/>
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
@@ -4151,40 +4229,23 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>ONEIDA #2022 ONE STOP E &amp; EE, DEPERE</t>
-        </is>
-      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr"/>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>AURORA OUTPATIENT RX #1017, WAUWATOSA</t>
+        </is>
+      </c>
       <c r="W70" t="inlineStr"/>
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
@@ -4199,39 +4260,23 @@
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Kim</t>
-        </is>
-      </c>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>790 COUNTY RD EE</t>
-        </is>
-      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="R71" t="inlineStr">
-        <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>work w/ Lincoln</t>
-        </is>
-      </c>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr"/>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>1220 DEWEY AVENUE</t>
+        </is>
+      </c>
       <c r="W71" t="inlineStr"/>
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
@@ -4250,27 +4295,19 @@
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/VLR8RdvzGgF2</t>
-        </is>
-      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="R72" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
-      <c r="V72" t="inlineStr"/>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/9FX8iZxiZbN2</t>
+        </is>
+      </c>
       <c r="W72" t="inlineStr"/>
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
@@ -4289,28 +4326,12 @@
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TO FOLLOW  </t>
-        </is>
-      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>Trainer</t>
-        </is>
-      </c>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
       <c r="V73" t="inlineStr"/>
@@ -4332,541 +4353,30 @@
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>MODAS</t>
-        </is>
-      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
-      <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr"/>
-      <c r="W74" t="inlineStr"/>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Sante Fe available, Equip</t>
+        </is>
+      </c>
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr"/>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>ONEIDA #2021 ONE STOP 54, ONEIDA</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="S75" t="inlineStr"/>
-      <c r="T75" t="inlineStr"/>
-      <c r="U75" t="inlineStr"/>
-      <c r="V75" t="inlineStr"/>
-      <c r="W75" t="inlineStr"/>
-      <c r="X75" t="inlineStr"/>
-      <c r="Y75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr"/>
-      <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>W180 HWY 54</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr">
-        <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="T76" t="inlineStr"/>
-      <c r="U76" t="inlineStr"/>
-      <c r="V76" t="inlineStr"/>
-      <c r="W76" t="inlineStr"/>
-      <c r="X76" t="inlineStr"/>
-      <c r="Y76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr"/>
-      <c r="B77" t="inlineStr"/>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/kMzccLLaPd22</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
-      <c r="R77" t="inlineStr">
-        <is>
-          <t>Nagui</t>
-        </is>
-      </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="T77" t="inlineStr"/>
-      <c r="U77" t="inlineStr"/>
-      <c r="V77" t="inlineStr"/>
-      <c r="W77" t="inlineStr"/>
-      <c r="X77" t="inlineStr"/>
-      <c r="Y77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr"/>
-      <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TO FOLLOW  </t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
-      <c r="R78" t="inlineStr">
-        <is>
-          <t>Pang</t>
-        </is>
-      </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>@ Store, 2nd Festival, work w/ Lincoln</t>
-        </is>
-      </c>
-      <c r="T78" t="inlineStr"/>
-      <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr"/>
-      <c r="W78" t="inlineStr"/>
-      <c r="X78" t="inlineStr"/>
-      <c r="Y78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr"/>
-      <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>MODAS</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="inlineStr"/>
-      <c r="T79" t="inlineStr"/>
-      <c r="U79" t="inlineStr"/>
-      <c r="V79" t="inlineStr"/>
-      <c r="W79" t="inlineStr"/>
-      <c r="X79" t="inlineStr"/>
-      <c r="Y79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr"/>
-      <c r="B80" t="inlineStr"/>
-      <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>ONEIDA #2024 TRAVEL CENTER, PULASKI</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr"/>
-      <c r="T80" t="inlineStr"/>
-      <c r="U80" t="inlineStr"/>
-      <c r="V80" t="inlineStr"/>
-      <c r="W80" t="inlineStr"/>
-      <c r="X80" t="inlineStr"/>
-      <c r="Y80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>5939 OLD 29 DRIVE</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="inlineStr"/>
-      <c r="T81" t="inlineStr"/>
-      <c r="U81" t="inlineStr"/>
-      <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr"/>
-      <c r="X81" t="inlineStr"/>
-      <c r="Y81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr"/>
-      <c r="B82" t="inlineStr"/>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/P7gcbpqmHRw</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr"/>
-      <c r="T82" t="inlineStr"/>
-      <c r="U82" t="inlineStr"/>
-      <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
-      <c r="X82" t="inlineStr"/>
-      <c r="Y82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr"/>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr"/>
-      <c r="S83" t="inlineStr"/>
-      <c r="T83" t="inlineStr"/>
-      <c r="U83" t="inlineStr"/>
-      <c r="V83" t="inlineStr"/>
-      <c r="W83" t="inlineStr"/>
-      <c r="X83" t="inlineStr"/>
-      <c r="Y83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr"/>
-      <c r="B84" t="inlineStr"/>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>Jerry S</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="inlineStr"/>
-      <c r="T84" t="inlineStr"/>
-      <c r="U84" t="inlineStr"/>
-      <c r="V84" t="inlineStr"/>
-      <c r="W84" t="inlineStr"/>
-      <c r="X84" t="inlineStr"/>
-      <c r="Y84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr"/>
-      <c r="B85" t="inlineStr"/>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>Driver,
-Optima</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr"/>
-      <c r="T85" t="inlineStr"/>
-      <c r="U85" t="inlineStr"/>
-      <c r="V85" t="inlineStr"/>
-      <c r="W85" t="inlineStr"/>
-      <c r="X85" t="inlineStr"/>
-      <c r="Y85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr"/>
-      <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>1st Modas</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="inlineStr"/>
-      <c r="T86" t="inlineStr"/>
-      <c r="U86" t="inlineStr"/>
-      <c r="V86" t="inlineStr"/>
-      <c r="W86" t="inlineStr"/>
-      <c r="X86" t="inlineStr"/>
-      <c r="Y86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr"/>
-      <c r="B87" t="inlineStr"/>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="inlineStr"/>
-      <c r="T87" t="inlineStr"/>
-      <c r="U87" t="inlineStr"/>
-      <c r="V87" t="inlineStr"/>
-      <c r="W87" t="inlineStr"/>
-      <c r="X87" t="inlineStr"/>
-      <c r="Y87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr"/>
-      <c r="B88" t="inlineStr"/>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>Heather</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr"/>
-      <c r="S88" t="inlineStr"/>
-      <c r="T88" t="inlineStr"/>
-      <c r="U88" t="inlineStr"/>
-      <c r="V88" t="inlineStr"/>
-      <c r="W88" t="inlineStr"/>
-      <c r="X88" t="inlineStr"/>
-      <c r="Y88" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Week1.xlsx
+++ b/Week1.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y74"/>
+  <dimension ref="A1:Y64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sun, Apr 28</t>
+          <t>Sun, May 5</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -427,7 +427,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Mon, Apr 29</t>
+          <t>Mon, May 6</t>
         </is>
       </c>
       <c r="F1" t="inlineStr"/>
@@ -435,7 +435,7 @@
       <c r="H1" t="inlineStr"/>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Tue, Apr 30</t>
+          <t>Tue, May 7</t>
         </is>
       </c>
       <c r="J1" t="inlineStr"/>
@@ -443,7 +443,7 @@
       <c r="L1" t="inlineStr"/>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Wed, May 1</t>
+          <t>Wed, May 8</t>
         </is>
       </c>
       <c r="N1" t="inlineStr"/>
@@ -451,7 +451,7 @@
       <c r="P1" t="inlineStr"/>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Thu, May 2</t>
+          <t>Thu, May 9</t>
         </is>
       </c>
       <c r="R1" t="inlineStr"/>
@@ -459,7 +459,7 @@
       <c r="T1" t="inlineStr"/>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Fri, May 3</t>
+          <t>Fri, May 10</t>
         </is>
       </c>
       <c r="V1" t="inlineStr"/>
@@ -467,7 +467,7 @@
       <c r="X1" t="inlineStr"/>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Sat, May 4</t>
+          <t>Sat, May 11</t>
         </is>
       </c>
     </row>
@@ -537,60 +537,60 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim </t>
+          <t xml:space="preserve">Katherine </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bags 5-7</t>
+          <t>Bag 5, SB 11</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DJ </t>
+          <t xml:space="preserve">Jeremiah </t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Bags 2-3</t>
+          <t>Bags 1-4</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ian </t>
+          <t xml:space="preserve">Katherine </t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Bag 8</t>
+          <t>Bag 5, SB 11</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim </t>
+          <t xml:space="preserve">DJ </t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Bags 5-8</t>
+          <t>Bags 1-3</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DJ </t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Bags 2-4</t>
+          <t>Bags 5,6</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -608,26 +608,18 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DJ </t>
+          <t xml:space="preserve">Kim </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bag 1</t>
+          <t>Bag 8, SB 10</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Katherine </t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Bag 1, SB 11</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -636,26 +628,18 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katherine </t>
+          <t xml:space="preserve">Kim </t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Bags 1-3</t>
+          <t>Bag 8, SB 11</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Katherine </t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Bag 1, SB 11</t>
-        </is>
-      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
     </row>
@@ -664,29 +648,17 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ian </t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Bag 8</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kim </t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Bag 7, SB 10</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -697,16 +669,8 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kim </t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Bag 8, SB 10</t>
-        </is>
-      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
     </row>
@@ -724,27 +688,15 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ian </t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Bag 8</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>Altima service being done this day</t>
-        </is>
-      </c>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
@@ -763,23 +715,43 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>7:00 AM START</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>4:30 AM MEET COLLEGE (SOUTHWEST)</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>5:00 AM MEET COLLEGE (SOUTHWEST)</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>5:15 AM MEET COLLEGE (SOUTHWEST)</t>
+        </is>
+      </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>THEY NOW HAVE SIGNS UP NO STREET PARKING</t>
+        </is>
+      </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
@@ -789,14 +761,10 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>4:30 AM MEET WATERTOWN PLANK</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -804,7 +772,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5:45 AM MEET WATERTOWN PLANK</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -812,7 +780,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>4:15 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -820,7 +788,7 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>4:45 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
@@ -828,7 +796,7 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>5:15 AM MEET BAYSHORE</t>
+          <t>11:45 AM REQUIRED MEET AT TIPP ST PARK N RIDE</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
@@ -843,7 +811,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>ASCENSION IP CSMO COLUMBIA ST MARY'S HOSP OZAUKEE CAMPUS, MEQUON</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -851,7 +819,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>6:30 AM START</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -859,7 +827,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -867,7 +835,7 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
@@ -875,7 +843,8 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>ADDRESS TO THE MEET:
+W156N9277 TIPP ST, MENOMONEE FALLS</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
@@ -890,7 +859,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>13111 N PORT WASHINGTON RD</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -898,7 +867,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>MARIANO'S #515 +RX, CHICAGO, RAVENSWOOD</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -906,7 +875,8 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>MARIANO'S #541 +FC-RX, 
+DES PLAINES</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -914,7 +884,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>MARIANO'S #523 +RX, GURNEE</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -922,7 +892,7 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>12:00 PM START</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
@@ -937,7 +907,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>WEBSTER'S MARKETPLACE, RIPON</t>
+          <t>https://goo.gl/maps/h68MdySxd6QHKPLu5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -945,7 +915,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>FESTIVAL #2696, HARTFORD - LIFO</t>
+          <t>1800 WEST LAWRENCE AVE</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -953,7 +923,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>MARIANO'S #503, CHICAGO - LAKESHORE EAST</t>
+          <t>10 E GOLF RD</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -961,7 +931,7 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>MARIANO'S #510 +RX, HARWOOD HEIGHTS</t>
+          <t>6655 GRAND AVE</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -969,7 +939,7 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>PICK #343, PLYMOUTH</t>
+          <t>MODAS</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
@@ -984,7 +954,7 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1188 W FOND DU LAC STREET</t>
+          <t>Need 2 supvs here and for each to bring a box</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -992,7 +962,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1275 BELL AVE</t>
+          <t>https://goo.gl/maps/fhp2WWuMFCQ2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1000,8 +970,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>333 EAST BENTON PL, 
-SUITE 206</t>
+          <t>https://goo.gl/maps/igRLR2wEyh22</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -1009,7 +978,7 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>7401 WEST LAWRENCE AVENUE</t>
+          <t>https://goo.gl/maps/SV1CeAGfq1s</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
@@ -1017,7 +986,7 @@
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2643 EASTERN AVE</t>
+          <t>AURORA OUTPATIENT RX #1119, MENOM FALLS</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
@@ -1030,17 +999,13 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/EWZS96J1G93UVQgi7</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/PUKTG8ru54xUWw7d9</t>
+          <t>SET UP ON REG #7</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1048,7 +1013,7 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/Gwa8pwADYxr</t>
+          <t>SET UP ON REG #3</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -1056,7 +1021,7 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/Nv5frfdAopr</t>
+          <t>RESET-REMAPPED</t>
         </is>
       </c>
       <c r="S14" t="inlineStr"/>
@@ -1064,7 +1029,7 @@
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/uM51wiLfFCA2</t>
+          <t xml:space="preserve">N93 W14575 WHITTAKER WAY </t>
         </is>
       </c>
       <c r="W14" t="inlineStr"/>
@@ -1076,13 +1041,21 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SMALL RESET-REMAPPED</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Camry available, Equip</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
@@ -1091,23 +1064,19 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>NEED TO PAY FOR PARKING AT THIS SITE!</t>
+          <t>RESET-REMAPPED</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>SET UP ON REG #5</t>
-        </is>
-      </c>
+      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>**Car swap happening with Jeremiah and Ian</t>
+          <t>https://goo.gl/maps/CLqauUgd2u12</t>
         </is>
       </c>
       <c r="W15" t="inlineStr"/>
@@ -1119,8 +1088,16 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Carlie</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
@@ -1130,7 +1107,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>Jeremiah</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1143,12 +1120,29 @@
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>@ Store,
+Equip</t>
+        </is>
+      </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Area tickets are used here, supervisor will need to arrive early to post them.</t>
+        </is>
+      </c>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
@@ -1160,18 +1154,17 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>DJ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>@ Store,
-Sante Fe, Equip</t>
+          <t>PC Box</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -1182,7 +1175,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>Carlie</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1205,36 +1198,23 @@
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>@ Store,
-Sante Fe, Equip</t>
-        </is>
-      </c>
+          <t>Casey</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Make sure to bring folders for both sites - *notes* - Items over $1,000 count as tenths - Count big dollar sections 1st for auditing. </t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
     </row>
@@ -1245,12 +1225,12 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1262,10 +1242,15 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>Casey</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Driver,
+Sante Fe</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
@@ -1274,31 +1259,32 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Casey</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Driver,
+Optima</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>Curt</t>
         </is>
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>Make sure to tag each location when completed. Try to start large Drawer sections early - they take a lot of time.</t>
         </is>
       </c>
       <c r="W18" t="inlineStr"/>
@@ -1310,16 +1296,8 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
@@ -1329,14 +1307,10 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>*After Aurora</t>
-        </is>
-      </c>
+          <t>Cynthia</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
@@ -1345,38 +1319,30 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>Jerry D</t>
         </is>
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>After Aurora</t>
-        </is>
-      </c>
+          <t>Meet in order to avoid parking issues at the location</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
     </row>
@@ -1385,22 +1351,9 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
@@ -1409,15 +1362,10 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+          <t>Jerry D</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
@@ -1426,44 +1374,30 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Jerry D</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van**</t>
-        </is>
-      </c>
+          <t>Only Milwwaukee crew will be at this meet up</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
     </row>
@@ -1472,21 +1406,13 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>6:00 AM MEET AT THE OFFICE</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
@@ -1495,10 +1421,14 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Supv Rx</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
@@ -1507,38 +1437,30 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+          <t>Jerry D</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr"/>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Driver,
+Camry</t>
+        </is>
+      </c>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
@@ -1548,21 +1470,13 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>7:00 AM START</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
@@ -1571,7 +1485,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1583,41 +1497,47 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
           <t>Driver,
-Camry</t>
+Red Van</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr"/>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van,
+Rx</t>
+        </is>
+      </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Katherine</t>
+          <t>Jeremiah</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>After Aurora</t>
+          <t>@ Store, Equip</t>
         </is>
       </c>
       <c r="X22" t="inlineStr"/>
@@ -1628,21 +1548,13 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
@@ -1651,7 +1563,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1663,36 +1575,41 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Supv Rx</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Carlie</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>After Aurora</t>
+          <t>Driver,
+Optima</t>
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
@@ -1703,22 +1620,13 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>@ Store,
-Help Kim</t>
-        </is>
-      </c>
+          <t>AURORA OUTPATIENT RX #1222, CEDAR GROVE</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
@@ -1727,14 +1635,10 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
@@ -1743,38 +1647,39 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Mai</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Driver,
+Altima</t>
+        </is>
+      </c>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
     </row>
@@ -1783,21 +1688,13 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>313 SOUTH MAIN ST</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
@@ -1806,12 +1703,14 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Ashley P</t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Driver,
+Red Van,
+Rx</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -1829,35 +1728,27 @@
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Heather</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>@ Store, Until 1:15</t>
-        </is>
-      </c>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
     </row>
@@ -1866,21 +1757,13 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/Z3osjsSq666QtkPNA</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
@@ -1889,7 +1772,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Brianna</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1912,12 +1795,12 @@
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Brianna</t>
+          <t>Ashley P</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -1928,19 +1811,15 @@
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Jeremiah</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>@ Store, Until 1:15</t>
-        </is>
-      </c>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
     </row>
@@ -1949,21 +1828,13 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>PARK ON STREET</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
@@ -1972,7 +1843,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Elijah</t>
+          <t>Anisha</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1995,7 +1866,7 @@
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2011,19 +1882,15 @@
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Marcia</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>@ Store, Until 1:15</t>
-        </is>
-      </c>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
     </row>
@@ -2032,21 +1899,9 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Makeda</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>@ Store, work w/ Michael</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
@@ -2055,7 +1910,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Elijah</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2071,7 +1926,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Ashley P</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2082,35 +1937,32 @@
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Eva</t>
+          <t>Qiana</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store,
+Supv Rx</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Nagui</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>@ Store, Until 1:15</t>
-        </is>
-      </c>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
     </row>
@@ -2121,17 +1973,18 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Michael N</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>@ Store, Trainer</t>
+          <t>Driver,
+Sante Fe, Equip</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -2142,7 +1995,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Makeda</t>
+          <t>Eva</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2158,7 +2011,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Evelin</t>
+          <t>Anisha</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2167,24 +2020,20 @@
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Monica</t>
+        </is>
+      </c>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
@@ -2196,19 +2045,15 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Qiana</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
@@ -2217,7 +2062,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Michael N</t>
+          <t>Evelin</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2233,34 +2078,35 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Ashley P</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
+          <t>@ Store,
+Rx</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>Makeda</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
     </row>
@@ -2269,21 +2115,9 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>15)</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>@ Store, work w/ Michael</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
@@ -2292,7 +2126,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Qiana</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2301,34 +2135,45 @@
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>15)</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15) </t>
-        </is>
-      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Michael N</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>@ Store,
-Rx</t>
-        </is>
-      </c>
+          <t>5:30 AM MEET COLLEGE (SOUTHWEST)</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>5:15 AM MEET BAYSHORE</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr"/>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
     </row>
@@ -2341,37 +2186,61 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>17)</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Justin</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>16)</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16) </t>
-        </is>
-      </c>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
+          <t>6:00 AM START</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Qiana</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
     </row>
@@ -2381,45 +2250,55 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>8:30 AM MEET COLLEGE (SOUTHWEST)</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>18)</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Makeda</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>17)</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>6:30 AM RACINE COURT 
-(HWY 43 &amp; Y)</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr"/>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17) </t>
-        </is>
-      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Qiana</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>@ Store,
-Supv Rx</t>
-        </is>
-      </c>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
@@ -2432,49 +2311,54 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>5:30 AM MEET WATERTOWN PLANK</t>
+          <t>9:00 AM START</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>19)</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>5:15 AM OFFICE LEAVE TIME</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>Michael N</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>18)</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr"/>
+          <t>Makeda</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>18)</t>
-        </is>
-      </c>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>PICK #891 +RX, RACINE - 
+MT PLEASANT - SOUTH</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>AURORA OUTPATIENT RX #1227, PLYMOUTH</t>
-        </is>
-      </c>
+      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
@@ -2487,35 +2371,43 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>EXCEL FINANCIAL</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>20)</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>EXCEL FINANCIAL</t>
-        </is>
-      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>2820 S GREEN BAY ROAD</t>
+        </is>
+      </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2600 KILEY WAY, SUITE 100</t>
+          <t>5:15 AM OFFICE LEAVE TIME</t>
         </is>
       </c>
       <c r="W35" t="inlineStr"/>
@@ -2530,35 +2422,31 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
+          <t>SMOKE WORLD VAPE, TOB &amp; VAPE OUTLET PLUS, RACINE</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>KANSASVILLE CITGO QUICK MART</t>
-        </is>
-      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/82wgqsh41W62</t>
+        </is>
+      </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/oK3no3iSD5kXaRa59</t>
+          <t>7:00 AM START</t>
         </is>
       </c>
       <c r="W36" t="inlineStr"/>
@@ -2573,23 +2461,19 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>KOHN'S FILLING STATION, KEWASKUM</t>
+          <t>6100 WASHINGTON AVE</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>AURORA OUTPATIENT RX #1102, HARTFORD</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>23010 DURAND AVE</t>
+          <t>5:00 AM START</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
@@ -2597,13 +2481,17 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
-          <t>5:30 AM REQUIRED MEET AT GARFIELD AVE PICK N SAVE</t>
+          <t>SET UP ON REG #5</t>
         </is>
       </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
@@ -2616,7 +2504,7 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>890 FOND DU LAC AVE</t>
+          <t>https://goo.gl/maps/cHN9ujzpR19oH6AF9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -2624,7 +2512,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>1640 E SUMNER ST, SUITE 100</t>
+          <t>7:00 AM START</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2632,35 +2520,22 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/QZs8ZSjv9eL2</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>Pick n Save address is:
-1100 E Garfield Ave</t>
-        </is>
-      </c>
+      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+          <t>CONDON OIL #270, POY SIPPI</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
     </row>
@@ -2670,17 +2545,13 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/CJnRNDyortw</t>
-        </is>
-      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/umuyQZyC8FT2</t>
+          <t>(7AM - 3PM)</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2688,30 +2559,38 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>ASCENSION ELMBROOK HOSPITAL RX #1104</t>
         </is>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>5:45 AM START</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr"/>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr"/>
+          <t>239 MAIN ST</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>C-STORE ONLY</t>
+        </is>
+      </c>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
     </row>
@@ -2720,50 +2599,62 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">TO FOLLOW </t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van, Equip</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>PAID VIRTUAL SEMINAR - LEADERSHIP, TEAM-BUILDING</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
+          <t>19333 W NORTH AVE  SUITE 390</t>
         </is>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr"/>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>After Aurora</t>
+        </is>
+      </c>
       <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>Driver,
-Optima</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/Nz84R23bat22</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
     </row>
@@ -2772,48 +2663,56 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+          <t>Casey</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Train w/ Lashaun</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Camry, Equip</t>
-        </is>
-      </c>
+          <t>BROOKFIELD OFFICE</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>TWIN LAKES CITGO, TWIN LAKES</t>
+          <t>https://goo.gl/maps/HnZswssC8QL2</t>
         </is>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>ASCENSION IP CSMM COLUMBIA ST MARY'S WOMEN'S MEDICAL CENTER</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
@@ -2823,10 +2722,14 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>KOHN'S FILLING STATION 259, CAMPBELLSPORT</t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -2838,22 +2741,40 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>410 N LAKE AVE</t>
+          <t>GO IN THROUGH EMERGENCY ENTRANCE</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2323 N LAKE DR</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Driver,
+Sante Fe,
+Supv Rx</t>
+        </is>
+      </c>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>C-STORE ONLY</t>
+        </is>
+      </c>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
     </row>
@@ -2862,38 +2783,63 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>259 N FOND DU LAC AVE</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>@ Store,
+Until 12:30</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Ashley P</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/k9s2GwpMbH32</t>
+          <t>TO FOLLOW</t>
         </is>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/86sUJVyjHnUKr7tv8</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr"/>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>After Aurora</t>
+        </is>
+      </c>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>CONDON OIL #135, OMRO</t>
         </is>
       </c>
       <c r="W43" t="inlineStr"/>
@@ -2906,29 +2852,37 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/WCsZpx5SMsA2</t>
-        </is>
-      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>6:15 AM OFFICE LEAVE TIME</t>
+          <t>Brianna</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>In order for everyone to get to the site efficiently and avoid anyone</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="S44" t="inlineStr"/>
@@ -2936,7 +2890,7 @@
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>163 E MAIN ST</t>
         </is>
       </c>
       <c r="W44" t="inlineStr"/>
@@ -2952,43 +2906,46 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
+          <t>DJ</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>Driver,
-Altima, Equip</t>
-        </is>
-      </c>
+          <t>ASCENSION ST JOSEPH-MAYFAIR RX #1106, TOSA</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>getting confused on where to go, all must use the meet above</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr"/>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
-          <t>PICK #416, WAUWATOSA - WALNUT</t>
+          <t>https://goo.gl/maps/w6KtjB6H4g72</t>
         </is>
       </c>
       <c r="W45" t="inlineStr"/>
@@ -3000,54 +2957,50 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Katherine</t>
+          <t>201 N MAYFAIR RD</t>
         </is>
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>DJ to drop off the Altima at Lutters in AM.  Use Camry until after Fri</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr"/>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
-          <t>1717 N MAYFAIR RD</t>
+          <t>**Also will need to bring DC5 cards**</t>
         </is>
       </c>
       <c r="W46" t="inlineStr"/>
@@ -3059,45 +3012,48 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Driver,
-Altima</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1750 ELKHORN</t>
+          <t>Jake S</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/efsuGG591Ms</t>
+        </is>
+      </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Jeri</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/96AWc1YH6do</t>
-        </is>
-      </c>
+      <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
@@ -3111,10 +3067,14 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>201 E MORRISSEY DRIVE, SUITE 100</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3125,27 +3085,35 @@
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
+          <t>10)</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr">
+        <is>
           <t>1)</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
-          <t>SET UP ON REG #5</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr"/>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
     </row>
@@ -3158,37 +3126,66 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/xYN7FT5gMzQk78dv6</t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>5:15 AM OFFICE LEAVE TIME</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Camry available, Equip</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr">
+        <is>
           <t>2)</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>Curt</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sante Fe, Bring ALL Equip, 
+help Michelle</t>
+        </is>
+      </c>
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
     </row>
@@ -3198,55 +3195,62 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>6:30 AM MEET OFFICE</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Lincoln</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
+          <t>DJ</t>
         </is>
       </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>Makeda</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>Driver,
-Camry</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>Brianna</t>
+          <t>Jacqui</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>@ Store, Equip</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="X50" t="inlineStr"/>
@@ -3258,69 +3262,45 @@
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>7:00 AM START</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Sante Fe, Equip</t>
-        </is>
-      </c>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Michael N</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>Driver,
-Optima</t>
+          <t>@ Store,
+Rx</t>
         </is>
       </c>
       <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Aaron</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Until 12:00</t>
-        </is>
-      </c>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
     </row>
@@ -3330,51 +3310,43 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>CONDON OIL #120, PRINCETON</t>
-        </is>
-      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Lori</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>@ Garfield meet too!</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Curt</t>
-        </is>
-      </c>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
@@ -3385,56 +3357,52 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>GAUGERT'S BUSS STOP, SULLIVAN</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Nick</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>811 OLD GREEN LAKE RD</t>
+          <t>9:00 AM START</t>
         </is>
       </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>Mai</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>Until 12:00</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>After Aurora</t>
-        </is>
-      </c>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
     </row>
@@ -3444,17 +3412,17 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>141 MAIN ST</t>
-        </is>
-      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>6:30 AM MEET OFFICE</t>
+          <t>Palmer</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3462,31 +3430,19 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/b9UWz2Uc4DF9epFR8</t>
+          <t>EXCEL FINANCIAL</t>
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>Monica</t>
-        </is>
-      </c>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="W54" t="inlineStr"/>
@@ -3499,17 +3455,17 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/TEUfEX2J1AE2</t>
-        </is>
-      </c>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
+          <t>Qiana</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3517,33 +3473,18 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>SMOKE WORLD VAPE, 
+OAK CREEK</t>
         </is>
       </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>Sue</t>
-        </is>
-      </c>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Sonia</t>
-        </is>
-      </c>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
@@ -3554,48 +3495,32 @@
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>APPROX 10:00/11:00 AM START</t>
-        </is>
-      </c>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>EXCEL FINANCIAL</t>
-        </is>
-      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>CONDON OIL #220, GREEN LAKE</t>
+          <t>8809 S HOWELL AVE</t>
         </is>
       </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>5:15 AM MEET AT THE OFFICE</t>
+        </is>
+      </c>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>Until 10:00</t>
-        </is>
-      </c>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
     </row>
@@ -3605,48 +3530,32 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>CONCORD GENERAL STORE, OCONOMOWOC</t>
-        </is>
-      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>514 MILL ST</t>
+          <t>https://goo.gl/maps/1fZ4T4q9WR1Hexjb7</t>
         </is>
       </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
     </row>
@@ -3656,25 +3565,17 @@
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>RON'S MARKET, HELENVILLE</t>
-        </is>
-      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>N6485 COUNTY RD F</t>
-        </is>
-      </c>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/9KFU2mUvQ1KBEVvg9</t>
+          <t>PARK ACROSS THE STREET AT PICK N SAVE AND RIDE TOGETHER STORE HAS SMALL PARKING LOT</t>
         </is>
       </c>
       <c r="O58" t="inlineStr"/>
@@ -3682,26 +3583,14 @@
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
     </row>
@@ -3711,19 +3600,11 @@
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>W3094 HWY 18</t>
-        </is>
-      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/X4xEoL3zCRA2</t>
-        </is>
-      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
@@ -3733,26 +3614,14 @@
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>AURORA OUTPATIENT RX #1433, MT PLEASANT</t>
         </is>
       </c>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>Elijah</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
     </row>
@@ -3762,19 +3631,11 @@
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/pyYX7wkpwom</t>
-        </is>
-      </c>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>APPROX 10:00/10:30 AM START</t>
-        </is>
-      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
@@ -3784,35 +3645,26 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Michelle</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>@ Store, 
-PC Box</t>
+          <t>Sante Fe available, Equip</t>
         </is>
       </c>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>13250 WASHINGTON AVE, SUITE 1A0043</t>
+        </is>
+      </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
     </row>
@@ -3826,11 +3678,7 @@
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
@@ -3840,34 +3688,22 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Courtney</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Curt</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/hWixpCQuYhJ3PMrB9</t>
+        </is>
+      </c>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr"/>
     </row>
@@ -3876,29 +3712,12 @@
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Driver,
-Optima, Equip</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>CONDON OIL #195, THERESA</t>
-        </is>
-      </c>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
@@ -3908,36 +3727,18 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>Optima
-Help Michelle,
-Take DC5's</t>
-        </is>
-      </c>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
     </row>
@@ -3946,49 +3747,45 @@
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>213 N MILWAUKEE</t>
-        </is>
-      </c>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
       <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr"/>
     </row>
@@ -4002,381 +3799,35 @@
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/dBrycqMgUwF2</t>
-        </is>
-      </c>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Driver,
+Optima</t>
+        </is>
+      </c>
       <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>15)</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
       <c r="X64" t="inlineStr"/>
       <c r="Y64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>16)</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr"/>
-      <c r="Y65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Driver,
-Optima, Equip</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr"/>
-      <c r="X66" t="inlineStr"/>
-      <c r="Y66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr"/>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr"/>
-      <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr"/>
-      <c r="X67" t="inlineStr"/>
-      <c r="Y67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr"/>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
-      <c r="T68" t="inlineStr"/>
-      <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr"/>
-      <c r="X68" t="inlineStr"/>
-      <c r="Y68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr"/>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr"/>
-      <c r="U69" t="inlineStr"/>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr"/>
-      <c r="X69" t="inlineStr"/>
-      <c r="Y69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr"/>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
-      <c r="T70" t="inlineStr"/>
-      <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>AURORA OUTPATIENT RX #1017, WAUWATOSA</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr"/>
-      <c r="X70" t="inlineStr"/>
-      <c r="Y70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr"/>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr"/>
-      <c r="T71" t="inlineStr"/>
-      <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>1220 DEWEY AVENUE</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr"/>
-      <c r="X71" t="inlineStr"/>
-      <c r="Y71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr"/>
-      <c r="B72" t="inlineStr"/>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
-      <c r="S72" t="inlineStr"/>
-      <c r="T72" t="inlineStr"/>
-      <c r="U72" t="inlineStr"/>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/9FX8iZxiZbN2</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr"/>
-      <c r="X72" t="inlineStr"/>
-      <c r="Y72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr"/>
-      <c r="B73" t="inlineStr"/>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="inlineStr"/>
-      <c r="T73" t="inlineStr"/>
-      <c r="U73" t="inlineStr"/>
-      <c r="V73" t="inlineStr"/>
-      <c r="W73" t="inlineStr"/>
-      <c r="X73" t="inlineStr"/>
-      <c r="Y73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr"/>
-      <c r="B74" t="inlineStr"/>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr"/>
-      <c r="T74" t="inlineStr"/>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>Sante Fe available, Equip</t>
-        </is>
-      </c>
-      <c r="X74" t="inlineStr"/>
-      <c r="Y74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Week1.xlsx
+++ b/Week1.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y64"/>
+  <dimension ref="A1:AA67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sun, May 5</t>
+          <t>Sun, May 12</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -427,7 +427,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Mon, May 6</t>
+          <t>Mon, May 13</t>
         </is>
       </c>
       <c r="F1" t="inlineStr"/>
@@ -435,7 +435,7 @@
       <c r="H1" t="inlineStr"/>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Tue, May 7</t>
+          <t>Tue, May 14</t>
         </is>
       </c>
       <c r="J1" t="inlineStr"/>
@@ -443,7 +443,7 @@
       <c r="L1" t="inlineStr"/>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Wed, May 8</t>
+          <t>Wed, May 15</t>
         </is>
       </c>
       <c r="N1" t="inlineStr"/>
@@ -451,7 +451,7 @@
       <c r="P1" t="inlineStr"/>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Thu, May 9</t>
+          <t>Thu, May 16</t>
         </is>
       </c>
       <c r="R1" t="inlineStr"/>
@@ -459,7 +459,7 @@
       <c r="T1" t="inlineStr"/>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Fri, May 10</t>
+          <t>Fri, May 17</t>
         </is>
       </c>
       <c r="V1" t="inlineStr"/>
@@ -467,9 +467,11 @@
       <c r="X1" t="inlineStr"/>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Sat, May 11</t>
-        </is>
-      </c>
+          <t>Sat, May 18</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr"/>
+      <c r="AA1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -497,6 +499,8 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -524,6 +528,8 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -535,66 +541,28 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Katherine </t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Bag 5, SB 11</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jeremiah </t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Bags 1-4</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Katherine </t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Bag 5, SB 11</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DJ </t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Bags 1-3</t>
-        </is>
-      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Bags 5,6</t>
-        </is>
-      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -606,16 +574,8 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kim </t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Bag 8, SB 10</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -626,22 +586,16 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kim </t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>Bag 8, SB 11</t>
-        </is>
-      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -665,7 +619,11 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Red Van oil change this day</t>
+        </is>
+      </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
@@ -673,6 +631,8 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -704,10 +664,16 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MOTHER'S DAY</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
@@ -717,7 +683,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
+          <t>4:45 AM REQUIRED MEET AT WATERTOWN PLANK PnR</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -725,7 +691,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4:30 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>5:00 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -733,7 +699,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>5:00 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>4:30 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -741,7 +707,7 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>5:15 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -749,22 +715,32 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>THEY NOW HAVE SIGNS UP NO STREET PARKING</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>ENTER THRU MATERNITY (3RD LEVEL) VISITOR ENTRANCE.  RX IS IN THE LOBBY</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -788,7 +764,7 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
@@ -796,22 +772,32 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>11:45 AM REQUIRED MEET AT TIPP ST PARK N RIDE</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ASCENSION IP CSMO COLUMBIA ST MARY'S HOSP OZAUKEE CAMPUS, MEQUON</t>
+          <t>5:00 AM START</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -835,7 +821,7 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>METRO #371 +RX, MILWAUKEE</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
@@ -843,13 +829,18 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>ADDRESS TO THE MEET:
-W156N9277 TIPP ST, MENOMONEE FALLS</t>
+          <t>PICK #374, PEWAUKEE - CAPITOL DR</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>PIGGLY WIGGLY #200, MEQUON</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -859,7 +850,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>13111 N PORT WASHINGTON RD</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -867,7 +858,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>MARIANO'S #515 +RX, CHICAGO, RAVENSWOOD</t>
+          <t>MARIANO'S #524 +RX, NORTHFIELD</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -875,8 +866,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>MARIANO'S #541 +FC-RX, 
-DES PLAINES</t>
+          <t>MARIANO'S #537 +RX, NAPERVILLE</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -884,7 +874,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>MARIANO'S #523 +RX, GURNEE</t>
+          <t>1123 N VAN BUREN STREET</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -892,12 +882,18 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>12:00 PM START</t>
+          <t>1405 CAPITOL DRIVE</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>6111 W MEQUON RD</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -907,7 +903,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/h68MdySxd6QHKPLu5</t>
+          <t>ASCENSION ST JOSEPH RX-CHAMBERS #1103, MILW</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -915,7 +911,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1800 WEST LAWRENCE AVE</t>
+          <t>1822 WILLOW RD</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -923,7 +919,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>10 E GOLF RD</t>
+          <t>1300 S NAPER BLVD</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -931,7 +927,7 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>6655 GRAND AVE</t>
+          <t>https://goo.gl/maps/P9qm8u7dxgH2</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -939,12 +935,18 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>MODAS</t>
+          <t>https://goo.gl/maps/fM2WtjtDye32</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/vQEGbDwowNJ7UTyo7</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -954,7 +956,7 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Need 2 supvs here and for each to bring a box</t>
+          <t>5000 W CHAMBERS  ROOM 1801</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -962,7 +964,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/fhp2WWuMFCQ2</t>
+          <t>https://goo.gl/maps/jdSWvCFJ2cU2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -970,28 +972,26 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/igRLR2wEyh22</t>
+          <t>https://goo.gl/maps/zEFY7puewEn</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/SV1CeAGfq1s</t>
-        </is>
-      </c>
+      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1119, MENOM FALLS</t>
+          <t>SET UP ON REG #5</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -999,13 +999,17 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/gRgCFNfwBUy</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>SET UP ON REG #7</t>
+          <t>SET UP ON REG #5</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1013,89 +1017,109 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>SET UP ON REG #3</t>
+          <t>SET UP ON REG #1</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>RESET-REMAPPED</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t xml:space="preserve">N93 W14575 WHITTAKER WAY </t>
+          <t>LIQUOR RESET-REMAPPED</t>
         </is>
       </c>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Camry available, Equip</t>
-        </is>
-      </c>
+          <t xml:space="preserve">TO FOLLOW   </t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>RESET-REMAPPED</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Carlie</t>
+        </is>
+      </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/CLqauUgd2u12</t>
-        </is>
-      </c>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1107,7 +1131,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Jeremiah</t>
+          <t>Nate</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1116,57 +1140,75 @@
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>@ Store,
+Sante Fe, Equip</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Curt</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
           <t>1)</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>@ Store,
-Equip</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Area tickets are used here, supervisor will need to arrive early to post them.</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr"/>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sante Fe available, Equip</t>
+        </is>
+      </c>
       <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>PC Box</t>
-        </is>
-      </c>
+          <t>ASCENSION ST FRANCIS RX #1107, MILWAUKEE</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
@@ -1175,62 +1217,78 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Nate</t>
+          <t>Carlie</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>@ Store, Equip</t>
+          <t>Driver,
+Optima,
+Rx</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Make sure to bring folders for both sites - *notes* - Items over $1,000 count as tenths - Count big dollar sections 1st for auditing. </t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>3237 S 16TH ST    ROOM 121</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1242,54 +1300,72 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>Driver,
-Sante Fe</t>
+Red Van,
+Rx</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Driver,
-Optima</t>
-        </is>
-      </c>
+          <t>Curt</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
         <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Rx</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
           <t>3)</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>Curt</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Make sure to tag each location when completed. Try to start large Drawer sections early - they take a lot of time.</t>
+          <t>Carlie</t>
         </is>
       </c>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
@@ -1297,7 +1373,11 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/ckXW882eGXp</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
@@ -1307,26 +1387,26 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1336,15 +1416,33 @@
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Meet in order to avoid parking issues at the location</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
@@ -1352,7 +1450,11 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
@@ -1362,26 +1464,32 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Jerry D</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van,
+Supv Rx</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1391,15 +1499,33 @@
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Only Milwwaukee crew will be at this meet up</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
@@ -1409,7 +1535,7 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>6:00 AM MEET AT THE OFFICE</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -1421,18 +1547,14 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Supv Rx</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1444,26 +1566,43 @@
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
           <t>6)</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>Driver,
-Camry</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
@@ -1473,7 +1612,7 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
+          <t>ASCENSION RX #1105, FRANKLIN-27TH ST</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1485,31 +1624,30 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -1519,29 +1657,25 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Driver,
-Red Van,
-Rx</t>
+          <t>Supv Rx</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Jeremiah</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>Jerry D</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
@@ -1551,7 +1685,7 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>10101 S 27TH ST    ROOM 1005</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1563,57 +1697,59 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>@ Store,
+Supv Rx</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Supv Rx</t>
-        </is>
-      </c>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr"/>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Until 12:00</t>
+        </is>
+      </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Driver,
-Optima</t>
-        </is>
-      </c>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
@@ -1623,7 +1759,7 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1222, CEDAR GROVE</t>
+          <t>https://goo.gl/maps/fQ4V9q61NUS2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -1635,53 +1771,54 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Driver,
-Altima</t>
-        </is>
-      </c>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
@@ -1691,7 +1828,7 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>313 SOUTH MAIN ST</t>
+          <t>TO FOLLOW</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1703,54 +1840,54 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Sue</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Driver,
-Red Van,
-Rx</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>Stephanie</t>
         </is>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Sue</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Katherine</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
@@ -1760,7 +1897,7 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/Z3osjsSq666QtkPNA</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -1772,7 +1909,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Angela</t>
+          <t>Makeda</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1783,24 +1920,24 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Stephanie</t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Ashley P</t>
+          <t>Brianna</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -1811,17 +1948,19 @@
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
@@ -1831,7 +1970,7 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PARK ON STREET</t>
+          <t>ASCENSION AMG RAWSON AVE RX #1116, FRANKLIN</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -1843,7 +1982,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Anisha</t>
+          <t>Qiana</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1854,19 +1993,23 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -1882,17 +2025,23 @@
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr"/>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Until 10:00</t>
+        </is>
+      </c>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
@@ -1900,7 +2049,11 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>7400 W RAWSON AVE, SUITE 140</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
@@ -1910,7 +2063,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Elijah</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1921,12 +2074,12 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Angela</t>
+          <t>Ashley P</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -1937,81 +2090,65 @@
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Qiana</t>
+          <t>Evelin</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>@ Store,
-Supv Rx</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Mai</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr"/>
+          <t>Jerry S</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>@ Store, Until 1:00</t>
+        </is>
+      </c>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Driver,
-Sante Fe, Equip</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/JDSt1uteEWoVQ3wg8</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Anisha</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2026,65 +2163,50 @@
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr"/>
+          <t>Kirsten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>@ Store, Until 1:00</t>
+        </is>
+      </c>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Sue</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>15)</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Ashley P</t>
+          <t>Makeda</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>@ Store,
-Rx</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
@@ -2094,7 +2216,7 @@
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -2109,310 +2231,302 @@
       </c>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>16)</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>5:30 AM MEET COLLEGE (SOUTHWEST)</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>15)</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
-          <t>5:30 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>16)</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>Nate</t>
+          <t>Marcia</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store, Until 1:00</t>
         </is>
       </c>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Carlie</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>17)</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Justin</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>16)</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>17)</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Qiana</t>
+          <t>Nagui</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store, Until 1:00</t>
         </is>
       </c>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>8:30 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>18)</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Makeda</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>17)</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>7:00 AM START</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>PICK #846 +RX, WEST ALLIS - 108TH ST</t>
         </is>
       </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>18)</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>9:00 AM START</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>19)</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Michael N</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>PICK #378, RACINE - CALEDONIA</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>18)</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Makeda</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
-          <t>PICK #891 +RX, RACINE - 
-MT PLEASANT - SOUTH</t>
+          <t>2625 S 108TH ST</t>
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>19)</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>20)</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>5111 DOUGLAS AVENUE</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>AURORA OUTPATIENT RX #1264, PORT WASHINGTON</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2820 S GREEN BAY ROAD</t>
+          <t>https://goo.gl/maps/BUUQissbQNk</t>
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>5:15 AM OFFICE LEAVE TIME</t>
-        </is>
-      </c>
+      <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
@@ -2420,38 +2534,36 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>SMOKE WORLD VAPE, TOB &amp; VAPE OUTLET PLUS, RACINE</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/b5CYjdz3kAC2</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>1475 GRAND AVE</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/82wgqsh41W62</t>
-        </is>
-      </c>
+      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>7:00 AM START</t>
-        </is>
-      </c>
+      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
@@ -2459,42 +2571,52 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>6100 WASHINGTON AVE</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>SMALL RESET-REMAPPED</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>5:00 AM START</t>
+          <t>https://goo.gl/maps/eMESBveZrkcjkpYJ8</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>SET UP ON REG #5</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr"/>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>6:15 AM MEET AT THE OFFICE</t>
         </is>
       </c>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
@@ -2504,40 +2626,42 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/cHN9ujzpR19oH6AF9</t>
+          <t>7:00 AM START</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>7:00 AM START</t>
-        </is>
-      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
-          <t>CONDON OIL #270, POY SIPPI</t>
+          <t>7:00 AM START</t>
         </is>
       </c>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
@@ -2545,269 +2669,271 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>(7AM - 3PM)</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>@ Store,
+Equip</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>ASCENSION ELMBROOK HOSPITAL RX #1104</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Camry, Equip</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
-          <t>239 MAIN ST</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>C-STORE ONLY</t>
-        </is>
-      </c>
+          <t>EXCEL FINANCIAL</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
+          <t>AURORA OUTPATIENT RX #1230, HOWARDS GROVE</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
         <is>
           <t>Driver,
-Red Van, Equip</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>PAID VIRTUAL SEMINAR - LEADERSHIP, TEAM-BUILDING</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+Optima</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>19333 W NORTH AVE  SUITE 390</t>
-        </is>
-      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>Stephanie</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>After Aurora</t>
+          <t>Until 11:00</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/Nz84R23bat22</t>
+          <t>OPEN PANTRY #493, RACINE</t>
         </is>
       </c>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Casey</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Train w/ Lashaun</t>
-        </is>
-      </c>
+          <t>620 S WISCONSIN DR</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>BROOKFIELD OFFICE</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/HnZswssC8QL2</t>
-        </is>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr"/>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Rx</t>
+        </is>
+      </c>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>3441 SPRING ST</t>
         </is>
       </c>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>https://maps.app.goo.gl/m32L8HYJsFkLkhxb9</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>After Aurora</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>GO IN THROUGH EMERGENCY ENTRANCE</t>
+          <t>5:00 MEET AT THE OFFICE</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>Anisha</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>Driver,
-Sante Fe,
-Supv Rx</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>C-STORE ONLY</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/8i7XHemjTpL2</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>@ Store,
-Until 12:30</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Ashley P</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -2815,54 +2941,68 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Annette</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>After Aurora</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
-          <t>CONDON OIL #135, OMRO</t>
+          <t>TO FOLLOW</t>
         </is>
       </c>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Brianna</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -2877,25 +3017,31 @@
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr"/>
+          <t>Courtney</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
-          <t>163 E MAIN ST</t>
+          <t xml:space="preserve">EXCEL FINANCIAL </t>
         </is>
       </c>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
@@ -2908,32 +3054,36 @@
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>After Aurora</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
-          <t>ASCENSION ST JOSEPH-MAYFAIR RX #1106, TOSA</t>
+          <t>ASCENSION COMMUNITY RX #1100-WISC, RACINE</t>
         </is>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Anisha</t>
+          <t>Eva</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -2945,12 +3095,14 @@
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/w6KtjB6H4g72</t>
+          <t>OPEN PANTRY #9570, RACINE</t>
         </is>
       </c>
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
@@ -2963,32 +3115,36 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>201 N MAYFAIR RD</t>
+          <t>1244 WISCONSIN AVE</t>
         </is>
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>Eva</t>
+          <t>Heather</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -3000,12 +3156,14 @@
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
-          <t>**Also will need to bring DC5 cards**</t>
+          <t>2731 DURAND AVE</t>
         </is>
       </c>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
@@ -3013,37 +3171,45 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>PARK IN PARKING STRUCTURE.  ENTER THRU MAIN ENTRANCE</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Jake S</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/efsuGG591Ms</t>
+          <t>https://goo.gl/maps/tu42wujVwN92</t>
         </is>
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Jeri</t>
+          <t>Jerry S</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -3053,10 +3219,16 @@
       </c>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/boUkpED44a62</t>
+        </is>
+      </c>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
@@ -3064,20 +3236,28 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
@@ -3085,7 +3265,7 @@
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -3099,23 +3279,13 @@
         </is>
       </c>
       <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Michelle</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
@@ -3123,20 +3293,28 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>Josie</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
@@ -3145,49 +3323,52 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Katherine</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Camry available, Equip</t>
+          <t>Driver,
+Corolla,
+Equip</t>
         </is>
       </c>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Lori</t>
+          <t>Katie</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store, Until 12:45</t>
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>Katherine</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Sante Fe, Bring ALL Equip, 
-help Michelle</t>
+          <t>Equip</t>
         </is>
       </c>
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
@@ -3195,20 +3376,28 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>AURORA OUTPATIENT RX #1085 MILWAUKEE</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
@@ -3217,44 +3406,47 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Makeda</t>
+          <t>Kirsten</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store, Until 12:45, 1st DC5 Scan, work w/ Marcia</t>
         </is>
       </c>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>Jacqui</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Driver,
+Camry</t>
         </is>
       </c>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
@@ -3262,20 +3454,28 @@
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>945 N 12TH ST</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Michelle</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+          <t>Savannah</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
@@ -3283,18 +3483,17 @@
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Michael N</t>
+          <t>Lori</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>@ Store,
-Rx</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T51" t="inlineStr"/>
@@ -3303,6 +3502,8 @@
       <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
@@ -3310,20 +3511,28 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/ocvCohDG8tChEG7r9</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
@@ -3331,12 +3540,12 @@
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>16)</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Makeda</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -3350,6 +3559,8 @@
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
@@ -3357,54 +3568,52 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>*Reminder need a different scanner setup for this site!</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Nick</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>9:00 AM START</t>
+          <t>5:30 AM LEAVE TIME FROM OFFICE</t>
         </is>
       </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>15)</t>
+          <t>17)</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Marcia</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store, work w/ Kirsten</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Madison Office</t>
         </is>
       </c>
       <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
@@ -3415,57 +3624,71 @@
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Palmer</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
+          <t>7:00 AM START</t>
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>18)</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Michael N</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Sante Fe, Equip</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Qiana</t>
+          <t>5:15 AM MEET AT THE OFFICE</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3473,56 +3696,92 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>SMOKE WORLD VAPE, 
-OAK CREEK</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>19)</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
       <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>8809 S HOWELL AVE</t>
+          <t>CONDON OIL #175, RANDOLPH</t>
         </is>
       </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>20)</t>
+        </is>
+      </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>5:15 AM MEET AT THE OFFICE</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr"/>
+          <t>Qiana</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>@ Store,
+Supv Rx</t>
+        </is>
+      </c>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
@@ -3534,30 +3793,44 @@
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/1fZ4T4q9WR1Hexjb7</t>
+          <t>154 E KIENOW DR</t>
         </is>
       </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>21)</t>
+        </is>
+      </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr"/>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
@@ -3569,23 +3842,23 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>AURORA OUTPATIENT RX #1070, RACINE</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>PARK ACROSS THE STREET AT PICK N SAVE AND RIDE TOGETHER STORE HAS SMALL PARKING LOT</t>
+          <t>https://goo.gl/maps/gLRK63LNv182</t>
         </is>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
@@ -3593,6 +3866,8 @@
       <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
@@ -3604,19 +3879,23 @@
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>8400 WASHINGTON AVENUE</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>AURORA OUTPATIENT RX #1433, MT PLEASANT</t>
-        </is>
-      </c>
+      <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
@@ -3624,6 +3903,8 @@
       <c r="W59" t="inlineStr"/>
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
@@ -3635,31 +3916,23 @@
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/WsqKM5J2Bo42</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>Sante Fe available, Equip</t>
-        </is>
-      </c>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>13250 WASHINGTON AVE, SUITE 1A0043</t>
-        </is>
-      </c>
+      <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
@@ -3667,6 +3940,8 @@
       <c r="W60" t="inlineStr"/>
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
@@ -3681,24 +3956,16 @@
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Curt</t>
+          <t>CONDON OIL #190, WAUPUN</t>
         </is>
       </c>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/hWixpCQuYhJ3PMrB9</t>
-        </is>
-      </c>
+      <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
@@ -3706,6 +3973,8 @@
       <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
@@ -3716,18 +3985,26 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>612 E MAIN ST</t>
         </is>
       </c>
       <c r="O62" t="inlineStr"/>
@@ -3741,6 +4018,8 @@
       <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
@@ -3751,43 +4030,42 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Driver,
+Camry</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>https://goo.gl/maps/JDEB8kGCMzC2</t>
         </is>
       </c>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
       <c r="V63" t="inlineStr"/>
       <c r="W63" t="inlineStr"/>
       <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
@@ -3806,28 +4084,137 @@
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>Driver,
-Optima</t>
-        </is>
-      </c>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr"/>
       <c r="W64" t="inlineStr"/>
       <c r="X64" t="inlineStr"/>
       <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>@ Store,
+Equip</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr"/>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Courtney</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr"/>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr"/>
+      <c r="X67" t="inlineStr"/>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Week1.xlsx
+++ b/Week1.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA67"/>
+  <dimension ref="A1:Y81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sun, May 12</t>
+          <t>Sun, May 19</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -427,7 +427,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Mon, May 13</t>
+          <t>Mon, May 20</t>
         </is>
       </c>
       <c r="F1" t="inlineStr"/>
@@ -435,7 +435,7 @@
       <c r="H1" t="inlineStr"/>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Tue, May 14</t>
+          <t>Tue, May 21</t>
         </is>
       </c>
       <c r="J1" t="inlineStr"/>
@@ -443,7 +443,7 @@
       <c r="L1" t="inlineStr"/>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Wed, May 15</t>
+          <t>Wed, May 22</t>
         </is>
       </c>
       <c r="N1" t="inlineStr"/>
@@ -451,7 +451,7 @@
       <c r="P1" t="inlineStr"/>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Thu, May 16</t>
+          <t>Thu, May 23</t>
         </is>
       </c>
       <c r="R1" t="inlineStr"/>
@@ -459,7 +459,7 @@
       <c r="T1" t="inlineStr"/>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Fri, May 17</t>
+          <t>Fri, May 24</t>
         </is>
       </c>
       <c r="V1" t="inlineStr"/>
@@ -467,11 +467,9 @@
       <c r="X1" t="inlineStr"/>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Sat, May 18</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr"/>
-      <c r="AA1" t="inlineStr"/>
+          <t>Sat, May 25</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -499,8 +497,6 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -528,8 +524,6 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -541,28 +535,66 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DJ </t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Bags 1-2</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ian </t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Bag 7, I-CALS</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DJ </t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Bag 1, SB 11</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DJ </t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Bag 1, SB 11</t>
+        </is>
+      </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kim </t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bags 5-7</t>
+        </is>
+      </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -574,28 +606,58 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bag 7, SB 11</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ian </t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Bag 8</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kim </t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Bavs 5,6</t>
+        </is>
+      </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lincoln </t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>ICALS</t>
+        </is>
+      </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -607,8 +669,16 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kim </t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bags 5,6</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -621,18 +691,28 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Red Van oil change this day</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr"/>
+          <t xml:space="preserve">Lincoln </t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>ICALS</t>
+        </is>
+      </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Katherine </t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bag 8</t>
+        </is>
+      </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -644,8 +724,16 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ian </t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bag 8, SB 10</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
@@ -656,91 +744,63 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ian </t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Bag 8</t>
+        </is>
+      </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>MOTHER'S DAY</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>4:45 AM REQUIRED MEET AT WATERTOWN PLANK PnR</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>5:00 AM MEET COLLEGE (SOUTHWEST)</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>4:30 AM MEET COLLEGE (SOUTHWEST)</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5:15 AM MEET AT S RACINE COURT (HWYS 43 &amp; Y) </t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ENTER THRU MATERNITY (3RD LEVEL) VISITOR ENTRANCE.  RX IS IN THE LOBBY</t>
+          <t>5:00 AM MEET BAYSHORE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -748,7 +808,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>4:45 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -756,7 +816,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>4:45 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -764,7 +824,7 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
@@ -772,32 +832,26 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>5:00 AM START</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5:00 AM START</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -805,7 +859,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -813,7 +867,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -821,7 +875,7 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>METRO #371 +RX, MILWAUKEE</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
@@ -829,28 +883,26 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>PICK #374, PEWAUKEE - CAPITOL DR</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>PIGGLY WIGGLY #200, MEQUON</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -858,7 +910,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>MARIANO'S #524 +RX, NORTHFIELD</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -866,7 +918,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>MARIANO'S #537 +RX, NAPERVILLE</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -874,7 +926,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1123 N VAN BUREN STREET</t>
+          <t>AURORA OUTPATIENT RX #1110, MILWAUKEE</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -882,28 +934,26 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>1405 CAPITOL DRIVE</t>
+          <t>ALBRECHT'S DELAFIELD MARKET</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>6111 W MEQUON RD</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PIGGLY WIGGLY #221, PALMYRA</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASCENSION ST JOSEPH RX-CHAMBERS #1103, MILW</t>
+          <t>TIETZ'S PIGGLY WIGGLY #336, PLYMOUTH</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -911,7 +961,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1822 WILLOW RD</t>
+          <t>MARIANO'S #531 +RX, SKOKIE</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -919,7 +969,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1300 S NAPER BLVD</t>
+          <t>MARIANO'S #506 +FC +RX, HOFFMAN ESTATES</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -927,7 +977,7 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/P9qm8u7dxgH2</t>
+          <t>1575 N RIVERCENTER DRIVE</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -935,28 +985,26 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/fM2WtjtDye32</t>
+          <t>3255 GOLF RD</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/vQEGbDwowNJ7UTyo7</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>117 W TAFT</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>5000 W CHAMBERS  ROOM 1801</t>
+          <t>1411 EASTERN AVE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -964,7 +1012,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/jdSWvCFJ2cU2</t>
+          <t>3358 W TOUHY AVE</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -972,36 +1020,42 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/zEFY7puewEn</t>
+          <t>2575 GOLF ROAD</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/rULfaGpqQPG2</t>
+        </is>
+      </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>SET UP ON REG #5</t>
+          <t>https://goo.gl/maps/UZh6uE9Zs2H2</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/VvUw29M3hE72</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/gRgCFNfwBUy</t>
+          <t>https://goo.gl/maps/H1oQiRvmvRp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1009,7 +1063,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>SET UP ON REG #5</t>
+          <t>https://goo.gl/maps/Dybn9qjgpUN2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1017,50 +1071,20 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>SET UP ON REG #1</t>
+          <t>https://goo.gl/maps/xDy3YHxAU3P2</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>LIQUOR RESET-REMAPPED</t>
-        </is>
-      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
@@ -1068,15 +1092,15 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TO FOLLOW   </t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>SET UP ON REG #1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
@@ -1085,60 +1109,76 @@
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Red Van available, Equip</t>
+        </is>
+      </c>
       <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Driver,
+Camry, Equip</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Driver,
+Altima, Equip</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
@@ -1147,80 +1187,85 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Brianna</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>@ Store,
-Sante Fe, Equip</t>
+          <t>@ Store, Equip</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Curt</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr"/>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Until noon</t>
+        </is>
+      </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Sante Fe available, Equip</t>
-        </is>
-      </c>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Y16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>Paul</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ASCENSION ST FRANCIS RX #1107, MILWAUKEE</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Casey</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
@@ -1235,79 +1280,59 @@
       <c r="O17" t="inlineStr">
         <is>
           <t>Driver,
-Optima,
-Rx</t>
+Optima</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Y17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>3237 S 16TH ST    ROOM 121</t>
+          <t>Jerry D</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>Carlie</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>Driver,
-Red Van,
-Rx</t>
+Optima</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -1318,76 +1343,54 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Curt</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>Rx</t>
-        </is>
-      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>DJ</t>
         </is>
       </c>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Y18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/ckXW882eGXp</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1404,67 +1407,61 @@
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Jerry D</t>
+          <t>2 AT ST LUKES, 6 AT ST MARY'S (NEED MINI POST IT NOTES)</t>
         </is>
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>Jerry D</t>
         </is>
       </c>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Y19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Jerry D</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1476,162 +1473,150 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>ENTER THRU SURGICAL CENTER</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>6:30 AM MEET COLLEGE (SOUTHWEST)</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Until 10:00</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PIGGLY WIGGLY #201, CEDARBURG</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>Driver,
 Red Van,
 Supv Rx</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Sarah</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>ASCENSION RX #1105, FRANKLIN-27TH ST</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
@@ -1640,72 +1625,69 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>Stephanie</t>
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>Supv Rx</t>
-        </is>
-      </c>
+          <t>7:00 AM START</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Jerry D</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>W61 N286 WASHINGTON AVE</t>
+        </is>
+      </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>10101 S 27TH ST    ROOM 1005</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>@ Store,
-Supv Rx</t>
-        </is>
-      </c>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
@@ -1714,71 +1696,74 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Driver,
+Sante Fe</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Mai</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>Until 12:00</t>
-        </is>
-      </c>
+          <t xml:space="preserve">DC5-ITEM LEVEL   </t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Mai</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/QamMdWSr16N2</t>
+        </is>
+      </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/fQ4V9q61NUS2</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>Makeda</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Elijah</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
@@ -1787,67 +1772,65 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>ASCENSION ALL SAINTS HOSP WI AVE CAMPUS (ST LUKE'S), RACINE</t>
         </is>
       </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr"/>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>FEW GROC AISLES RESET-REMAPPED</t>
+        </is>
+      </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>TO FOLLOW</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
@@ -1856,38 +1839,40 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>1320 WISCONSIN AVE</t>
         </is>
       </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr"/>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
@@ -1895,21 +1880,17 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Makeda</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1925,64 +1906,74 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/raiuDa4wRko</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr"/>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Sante Fe available, Equip</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ASCENSION AMG RAWSON AVE RX #1116, FRANKLIN</t>
+          <t>5:30 AM MEET BAYSHORE</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Qiana</t>
+          <t>Anisha</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1998,7 +1989,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Anisha</t>
+          <t>Eva</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2007,63 +1998,61 @@
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Elijah</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t xml:space="preserve">DC5-ITEM LEVEL </t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Stephanie</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Until 10:00</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Curt</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>7400 W RAWSON AVE, SUITE 140</t>
+          <t>7:00 AM START</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Ashley P</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2079,67 +2068,78 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Ashley P</t>
+          <t>Evelin</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store,
+Rx</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>15)</t>
-        </is>
-      </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>ASCENSION ALL SAINTS HOSP SPRING ST CAMPUS (ST MARY'S), RACINE</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Jerry S</t>
+          <t>Makeda</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>@ Store, Until 1:00</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/JDSt1uteEWoVQ3wg8</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
@@ -2158,41 +2158,71 @@
       </c>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>3801 SPRING ST</t>
+        </is>
+      </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Kirsten</t>
+          <t>Nate</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>@ Store, Until 1:00</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Jerry S</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>@ Store, Until 10:30</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>AURORA OUTPATIENT RX #1169 GREEN BAY</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
@@ -2211,207 +2241,229 @@
       </c>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/PjumoiJbqD62</t>
+        </is>
+      </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>15)</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+          <t>2845 GREENBRIER RD</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>15)</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>5:30 AM MEET COLLEGE (SOUTHWEST)</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>16)</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Michael N</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>THE ASCENSIONS HAVE BEEN RESCHEDULED!</t>
         </is>
       </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>16)</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Marcia</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>@ Store, Until 1:00</t>
-        </is>
-      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Marcia</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>@ Store, Until 10:30</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>https://goo.gl/maps/rneu9EfJWkGa7fvJ7</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>16)</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>Makeda</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>17)</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>17)</t>
-        </is>
-      </c>
+      <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Nagui</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>@ Store, Until 1:00</t>
-        </is>
-      </c>
+          <t>9:00 AM START</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Nagui</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>@ Store, Until 10:30</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>17)</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>Michael N</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>@ Store,
+Rx</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>18)</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr"/>
+          <t>Qiana</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>@ Store,
+Supv Rx</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>PICK #846 +RX, WEST ALLIS - 108TH ST</t>
-        </is>
-      </c>
+      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>18)</t>
-        </is>
-      </c>
+      <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Sarah</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>EXCEL FINANCIAL</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
@@ -2420,7 +2472,7 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2431,53 +2483,55 @@
       <c r="G34" t="inlineStr">
         <is>
           <t>Driver,
-Red Van</t>
+Red Van, Equip</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>18)</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>PICK #378, RACINE - CALEDONIA</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>19)</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr"/>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>2625 S 108TH ST</t>
-        </is>
-      </c>
+      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>19)</t>
-        </is>
-      </c>
+      <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>SMOKE WORLD VAPE, BROOKFIELD</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
@@ -2486,7 +2540,7 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2497,36 +2551,30 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>5111 DOUGLAS AVENUE</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>AURORA OUTPATIENT RX #1264, PORT WASHINGTON</t>
-        </is>
-      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/BUUQissbQNk</t>
+          <t>9:00 AM START</t>
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>17115 W BLUEMOUND RD</t>
+        </is>
+      </c>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
@@ -2538,32 +2586,30 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/b5CYjdz3kAC2</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>1475 GRAND AVE</t>
-        </is>
-      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>EXCEL FINANCIAL</t>
+        </is>
+      </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/o6BySGmshE5c9am29</t>
+        </is>
+      </c>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
@@ -2577,7 +2623,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>SMALL RESET-REMAPPED</t>
+          <t>5:30 AM START</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2585,38 +2631,24 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/eMESBveZrkcjkpYJ8</t>
+          <t>THEY NOW HAVE SIGNS UP NO STREET PARKING</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>SMOKE WORLD VAPE, WAUKESHA</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>6:15 AM MEET AT THE OFFICE</t>
-        </is>
-      </c>
+      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
@@ -2626,42 +2658,52 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
+          <t>5:30 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>12:00 PM START</t>
+        </is>
+      </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>530 W SUNSET DRIVE</t>
         </is>
       </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr"/>
+          <t>Lincoln</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sante Fe available, Equip</t>
+        </is>
+      </c>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
@@ -2671,67 +2713,48 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>@ Store,
-Equip</t>
-        </is>
-      </c>
+          <t>ROTE OIL #6 HUBERTUS</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Camry, Equip</t>
-        </is>
-      </c>
+          <t>AURORA OUTPATIENT RX #1143 MENOM FALLS</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>https://goo.gl/maps/aogDHj45t6GWbbYP8</t>
         </is>
       </c>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
@@ -2741,59 +2764,44 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1230, HOWARDS GROVE</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Driver,
-Optima</t>
-        </is>
-      </c>
+          <t>1306 HWY 175</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>N93 W14575 WHITTAKER WAY</t>
+        </is>
+      </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>Until 11:00</t>
-        </is>
-      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>OPEN PANTRY #493, RACINE</t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
@@ -2803,54 +2811,48 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>620 S WISCONSIN DR</t>
+          <t>ASCENSION COMMUNITY RX #1102-ATRIUM, RACINE</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>https://goo.gl/maps/SZRuQ4FHA1cX2ZmC8</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/AJgcVD6yx75Kq3yS6</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Sue</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>Rx</t>
+          <t>Sante Fe available, Equip</t>
         </is>
       </c>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>3441 SPRING ST</t>
-        </is>
-      </c>
+      <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
@@ -2860,62 +2862,40 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/m32L8HYJsFkLkhxb9</t>
+          <t>3811 SPRING ST</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>After Aurora</t>
-        </is>
-      </c>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>5:00 MEET AT THE OFFICE</t>
-        </is>
-      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/8i7XHemjTpL2</t>
-        </is>
-      </c>
+      <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
@@ -2923,37 +2903,45 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/HCpmGJRX9sG2</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Annette</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
@@ -2965,83 +2953,59 @@
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>5:00 AM OFFICE LEAVE TIME</t>
         </is>
       </c>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>ROTE OIL #7 MILWAUKEE</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>Courtney</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
-          <t xml:space="preserve">EXCEL FINANCIAL </t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
@@ -3049,60 +3013,38 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>After Aurora</t>
-        </is>
-      </c>
+          <t>5931 N 91ST ST</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>ASCENSION COMMUNITY RX #1100-WISC, RACINE</t>
-        </is>
-      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
-          <t>OPEN PANTRY #9570, RACINE</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
-      <c r="Z45" t="inlineStr"/>
-      <c r="AA45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
@@ -3110,60 +3052,42 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>ASCENSION COMMUNITY RX #1101-SPRING ST, RACINE</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/cw58s7atAhTAGHNd7</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>1244 WISCONSIN AVE</t>
-        </is>
-      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
+      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr">
         <is>
-          <t>Heather</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>5:00 AM OFFICE LEAVE TIME</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2731 DURAND AVE</t>
+          <t>ROTE OIL #14 TREVOR (CITGO)</t>
         </is>
       </c>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr"/>
-      <c r="AA46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
@@ -3173,62 +3097,44 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>PARK IN PARKING STRUCTURE.  ENTER THRU MAIN ENTRANCE</t>
+          <t>3807 SPRING ST</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/tu42wujVwN92</t>
+          <t xml:space="preserve">5:30 AM START </t>
         </is>
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Jerry S</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/boUkpED44a62</t>
+          <t>12617 ANTIOCH RD</t>
         </is>
       </c>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr"/>
-      <c r="AA47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
@@ -3238,54 +3144,44 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>https://goo.gl/maps/345cLtjsHsD2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>EXCEL FINANCIAL</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
+      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t xml:space="preserve">DC5-FINANCIAL </t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/xA9YMzPGc6Vhxi5r8</t>
+        </is>
+      </c>
       <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr"/>
-      <c r="AA48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
@@ -3293,327 +3189,251 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Josie</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>ROTE OIL #8 ELM GROVE</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>Driver,
-Corolla,
-Equip</t>
-        </is>
-      </c>
+          <t>ROTE OIL #10 MUKWONAGO - ROCHESTER</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
+      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Katie</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>@ Store, Until 12:45</t>
-        </is>
-      </c>
+          <t>ROTE OIL #1 PADDOCK LAKE- BRASS BALL</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
-      <c r="Z49" t="inlineStr"/>
-      <c r="AA49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1085 MILWAUKEE</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Driver,
+Sante Fe, Equip</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>13395 WATERTOWN PLANK RD</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>1060 N ROCHESTER ST</t>
         </is>
       </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
+      <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Kirsten</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>@ Store, Until 12:45, 1st DC5 Scan, work w/ Marcia</t>
-        </is>
-      </c>
+          <t>25406 75TH ST</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>Driver,
-Camry</t>
-        </is>
-      </c>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr"/>
-      <c r="AA50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>945 N 12TH ST</t>
+          <t>Curt</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Savannah</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/5zXAKpcRHDmA17UK9</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/dmvR5bTHLs1Cbjcr5</t>
+        </is>
+      </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>15)</t>
-        </is>
-      </c>
+      <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/LTa4ckcczx5qc8269</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>ROTE OIL #13 TREVOR (BP)</t>
+        </is>
+      </c>
       <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr"/>
-      <c r="AA51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/ocvCohDG8tChEG7r9</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Victoria</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TO FOLLOW   </t>
+        </is>
+      </c>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>16)</t>
-        </is>
-      </c>
+      <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Makeda</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>12511 ANTIOCH RD</t>
+        </is>
+      </c>
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr"/>
-      <c r="AA52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>*Reminder need a different scanner setup for this site!</t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>5:30 AM LEAVE TIME FROM OFFICE</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>17)</t>
-        </is>
-      </c>
+      <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr">
         <is>
-          <t>Marcia</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>@ Store, work w/ Kirsten</t>
-        </is>
-      </c>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
       <c r="V53" t="inlineStr">
         <is>
-          <t>Madison Office</t>
+          <t>https://goo.gl/maps/iu3xzNwgJ32esP5RA</t>
         </is>
       </c>
       <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr"/>
-      <c r="AA53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
@@ -3625,70 +3445,48 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>ROTE OIL #09 GREENFIELD</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
+          <t>ROTE OIL #12 MUKWONAGO - (AMOCO) GREENWALD</t>
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>18)</t>
-        </is>
-      </c>
+      <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr">
         <is>
-          <t>Michael N</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>ROTE OIL #2 PADDOCK LAKE- 75TH ST</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
+      <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr"/>
-      <c r="AA54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Sante Fe, Equip</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>5:15 AM MEET AT THE OFFICE</t>
+          <t>12345 W LAYTON AVE</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3696,34 +3494,37 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>909 GREENWALD CT</t>
         </is>
       </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>19)</t>
-        </is>
-      </c>
+      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr">
         <is>
-          <t>Michelle</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>25555 75TH ST</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>@ Store,
+Camry, Equip</t>
+        </is>
+      </c>
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
-      <c r="AA55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
@@ -3732,12 +3533,12 @@
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>5:00 AM OFFICE LEAVE TIME</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -3745,7 +3546,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>https://goo.gl/maps/TSgMUriHbJPX9hGE7</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3753,84 +3554,75 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>CONDON OIL #175, RANDOLPH</t>
+          <t>https://goo.gl/maps/ejQSLoz2D8EmzKVq6</t>
         </is>
       </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>20)</t>
-        </is>
-      </c>
+      <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr">
         <is>
-          <t>Qiana</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>@ Store,
-Supv Rx</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/5UyWWXXbzXMaVnv99</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr"/>
-      <c r="AA56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>154 E KIENOW DR</t>
+          <t xml:space="preserve">TO FOLLOW   </t>
         </is>
       </c>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>21)</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>Sarah</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
-      <c r="AA57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
@@ -3838,36 +3630,58 @@
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1070, RACINE</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Camry available, Equip</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/gLRK63LNv182</t>
+          <t>ROTE OIL  #11 MUKWONAGO - (BP) ARROWHEAD</t>
         </is>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Camry, Equip</t>
+        </is>
+      </c>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr"/>
       <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr"/>
-      <c r="AA58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
@@ -3875,13 +3689,21 @@
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>ROTE OIL #03 TWIN LAKES</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>8400 WASHINGTON AVENUE</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -3889,22 +3711,32 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>122 ARROWHEAD DR</t>
         </is>
       </c>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr"/>
       <c r="W59" t="inlineStr"/>
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="inlineStr"/>
-      <c r="AA59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
@@ -3912,13 +3744,21 @@
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>475 N LAKE AVE</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/WsqKM5J2Bo42</t>
+          <t>DJ</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -3926,7 +3766,7 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>https://goo.gl/maps/7XkTFZtDFDgGBctz7</t>
         </is>
       </c>
       <c r="O60" t="inlineStr"/>
@@ -3940,8 +3780,6 @@
       <c r="W60" t="inlineStr"/>
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
-      <c r="Z60" t="inlineStr"/>
-      <c r="AA60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
@@ -3949,7 +3787,11 @@
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/jNgJR8hii6jJGZQP7</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
@@ -3957,11 +3799,7 @@
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>CONDON OIL #190, WAUPUN</t>
-        </is>
-      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
@@ -3973,8 +3811,6 @@
       <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr"/>
-      <c r="AA61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
@@ -3982,35 +3818,27 @@
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TO FOLLOW   </t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>612 E MAIN ST</t>
-        </is>
-      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
@@ -4018,8 +3846,6 @@
       <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr"/>
-      <c r="AA62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
@@ -4027,36 +3853,43 @@
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Driver,
-Camry</t>
-        </is>
-      </c>
+          <t>5:00 AM OFFICE LEAVE TIME</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/JDEB8kGCMzC2</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Camry available, Equip</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
@@ -4064,8 +3897,6 @@
       <c r="W63" t="inlineStr"/>
       <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr"/>
-      <c r="Z63" t="inlineStr"/>
-      <c r="AA63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
@@ -4073,15 +3904,31 @@
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>ROTE OIL #04 GENOA CITY</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
@@ -4093,8 +3940,6 @@
       <c r="W64" t="inlineStr"/>
       <c r="X64" t="inlineStr"/>
       <c r="Y64" t="inlineStr"/>
-      <c r="Z64" t="inlineStr"/>
-      <c r="AA64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
@@ -4102,29 +3947,24 @@
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100 ELIZABETH LANE    </t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>@ Store,
-Equip</t>
-        </is>
-      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
@@ -4135,8 +3975,6 @@
       <c r="W65" t="inlineStr"/>
       <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr"/>
-      <c r="Z65" t="inlineStr"/>
-      <c r="AA65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
@@ -4144,32 +3982,24 @@
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/DitGJzEvTVhJPxkJ8</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>FOX BROS PIGGLY WIGGLY #088, SAUKVILLE</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>Courtney</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
@@ -4180,8 +4010,6 @@
       <c r="W66" t="inlineStr"/>
       <c r="X66" t="inlineStr"/>
       <c r="Y66" t="inlineStr"/>
-      <c r="Z66" t="inlineStr"/>
-      <c r="AA66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
@@ -4189,19 +4017,27 @@
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TO FOLLOW   </t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>810 E GREEN BAY AVE</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr"/>
@@ -4213,8 +4049,580 @@
       <c r="W67" t="inlineStr"/>
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr"/>
-      <c r="Z67" t="inlineStr"/>
-      <c r="AA67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/eiMeyhHbpT82</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Until 2:00</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr"/>
+      <c r="X68" t="inlineStr"/>
+      <c r="Y68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>ROTE OIL #05  LAKE GENEVA</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr"/>
+      <c r="X69" t="inlineStr"/>
+      <c r="Y69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>300 PELLER RD</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Jerry S</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr"/>
+      <c r="X70" t="inlineStr"/>
+      <c r="Y70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/6fegzT1PbyY5VkDR6</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Sante Fe</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr"/>
+      <c r="X71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Ethan</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr"/>
+      <c r="X72" t="inlineStr"/>
+      <c r="Y72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Camry, Equip</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Heather</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr"/>
+      <c r="X73" t="inlineStr"/>
+      <c r="Y73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Jeremiah</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr"/>
+      <c r="X74" t="inlineStr"/>
+      <c r="Y74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Jeri</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr"/>
+      <c r="X75" t="inlineStr"/>
+      <c r="Y75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Katie</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>@ Store, Until 12:45</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr"/>
+      <c r="X76" t="inlineStr"/>
+      <c r="Y76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Kirsten</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>@ Store, Until 12:45</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr"/>
+      <c r="X77" t="inlineStr"/>
+      <c r="Y77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Marcia</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr"/>
+      <c r="X78" t="inlineStr"/>
+      <c r="Y78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Nagui</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>@ Store, Until 12:45</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr"/>
+      <c r="X79" t="inlineStr"/>
+      <c r="Y79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Savannah</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Week1.xlsx
+++ b/Week1.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y81"/>
+  <dimension ref="A1:Y73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sun, May 19</t>
+          <t>Sun, May 26</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -427,7 +427,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Mon, May 20</t>
+          <t>Mon, May 27</t>
         </is>
       </c>
       <c r="F1" t="inlineStr"/>
@@ -435,7 +435,7 @@
       <c r="H1" t="inlineStr"/>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Tue, May 21</t>
+          <t>Tue, May 28</t>
         </is>
       </c>
       <c r="J1" t="inlineStr"/>
@@ -443,7 +443,7 @@
       <c r="L1" t="inlineStr"/>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Wed, May 22</t>
+          <t>Wed, May 29</t>
         </is>
       </c>
       <c r="N1" t="inlineStr"/>
@@ -451,7 +451,7 @@
       <c r="P1" t="inlineStr"/>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Thu, May 23</t>
+          <t>Thu, May 30</t>
         </is>
       </c>
       <c r="R1" t="inlineStr"/>
@@ -459,7 +459,7 @@
       <c r="T1" t="inlineStr"/>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Fri, May 24</t>
+          <t>Fri, May 31</t>
         </is>
       </c>
       <c r="V1" t="inlineStr"/>
@@ -467,7 +467,7 @@
       <c r="X1" t="inlineStr"/>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Sat, May 25</t>
+          <t>Sat, Jun 1</t>
         </is>
       </c>
     </row>
@@ -530,43 +530,31 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DJ </t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Bags 1-2</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ian </t>
+          <t xml:space="preserve">Katherine </t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Bag 7, I-CALS</t>
+          <t>ICALS</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DJ </t>
+          <t xml:space="preserve">Katherine </t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Bag 1, SB 11</t>
+          <t>Bag 8</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -578,7 +566,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Bag 1, SB 11</t>
+          <t>ICALS</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -590,7 +578,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Bags 5-7</t>
+          <t>Bags 1-4</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -601,59 +589,39 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Bag 7, SB 11</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DJ </t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ICALS</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ian </t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Bag 8</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kim </t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>Bavs 5,6</t>
-        </is>
-      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lincoln </t>
+          <t xml:space="preserve">Katherine </t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>ICALS</t>
+          <t>Bag 5, SB 11</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
@@ -661,7 +629,11 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Tuesday is a slow day due to Memorial day on Monday</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
@@ -669,16 +641,8 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kim </t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Bags 5,6</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -689,26 +653,18 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lincoln </t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>ICALS</t>
-        </is>
-      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katherine </t>
+          <t xml:space="preserve">Lashaun </t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Bag 8</t>
+          <t>Bag 6</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
@@ -724,16 +680,8 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ian </t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Bag 8, SB 10</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
@@ -744,16 +692,8 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ian </t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>Bag 8</t>
-        </is>
-      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
@@ -766,49 +706,65 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>*MEMORIAL DAY</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>5:15 AM MEET OFFICE MEET</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>4:15 AM MEET COLLEGE (SOUTHWEST)</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4:15 AM MEET COLLEGE (SOUTHWEST) </t>
+        </is>
+      </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5:15 AM MEET AT S RACINE COURT (HWYS 43 &amp; Y) </t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>5:00 AM MEET BAYSHORE</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4:45 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -816,7 +772,7 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>4:45 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -832,7 +788,7 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>5:00 AM START</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
@@ -841,25 +797,17 @@
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>EXCEL FINANCIAL</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -867,7 +815,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -883,7 +831,7 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>PICK #845 +RX, MILWAUKEE-LOOMIS</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
@@ -892,25 +840,17 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>KOHN'S FILLING STATION, KEWASKUM</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -918,7 +858,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>MARIANO'S #526 +RX, SHOREWOOD</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -926,7 +866,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1110, MILWAUKEE</t>
+          <t>MARIANO'S #539 +RX, BRONZEVILLE</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -934,7 +874,7 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>ALBRECHT'S DELAFIELD MARKET</t>
+          <t>3701 S 27TH ST</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
@@ -943,25 +883,17 @@
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>PIGGLY WIGGLY #221, PALMYRA</t>
-        </is>
-      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>TIETZ'S PIGGLY WIGGLY #336, PLYMOUTH</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>MARIANO'S #531 +RX, SKOKIE</t>
+          <t>890 FOND DU LAC AVE</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -969,7 +901,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>MARIANO'S #506 +FC +RX, HOFFMAN ESTATES</t>
+          <t>950 BROOK FOREST AVE</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -977,7 +909,7 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1575 N RIVERCENTER DRIVE</t>
+          <t>3857 S MARTIN LUTHER KING</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -985,7 +917,7 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>3255 GOLF RD</t>
+          <t>https://goo.gl/maps/BLy8vMxXBsA2</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
@@ -994,25 +926,17 @@
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>117 W TAFT</t>
-        </is>
-      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>1411 EASTERN AVE</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3358 W TOUHY AVE</t>
+          <t>https://goo.gl/maps/CJnRNDyortw</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1020,7 +944,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2575 GOLF ROAD</t>
+          <t>https://goo.gl/maps/ieT41cP6AP42</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -1028,42 +952,30 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/rULfaGpqQPG2</t>
+          <t>https://goo.gl/maps/xtUgo2RcwVm</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/UZh6uE9Zs2H2</t>
-        </is>
-      </c>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/VvUw29M3hE72</t>
-        </is>
-      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/H1oQiRvmvRp</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/Dybn9qjgpUN2</t>
+          <t>TO FOLLOW</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1071,18 +983,34 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/xDy3YHxAU3P2</t>
+          <t>SET UP ON REG #1</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>LIQUOR RESET-REMAPPED</t>
+        </is>
+      </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sante Fe available, Equip</t>
+        </is>
+      </c>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
     </row>
@@ -1098,7 +1026,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>SET UP ON REG #1</t>
+          <t>EXCEL FINANCIAL</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1107,77 +1035,43 @@
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Red Van available, Equip</t>
+          <t>Until 12:00</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Driver,
-Camry, Equip</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Driver,
-Altima, Equip</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>KOHN'S FILLING STATION 259, CAMPBELLSPORT</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
@@ -1198,28 +1092,28 @@
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Mai</t>
+          <t>Nate</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>Until noon</t>
+          <t>@ Store, Equip</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="W16" t="inlineStr"/>
@@ -1227,45 +1121,21 @@
       <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>259 N FOND DU LAC AVE</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
@@ -1274,23 +1144,30 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
+          <t>Casey</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
           <t>Carlie</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Driver,
-Optima</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Rx</t>
+        </is>
+      </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -1307,34 +1184,17 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Driver,
-Optima</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/WCsZpx5SMsA2</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
@@ -1343,26 +1203,38 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Cynthia</t>
+        </is>
+      </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Supv Rx</t>
+        </is>
+      </c>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
     </row>
@@ -1371,28 +1243,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Sonia</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
@@ -1402,22 +1258,26 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>Curt</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2 AT ST LUKES, 6 AT ST MARY'S (NEED MINI POST IT NOTES)</t>
+          <t>Jerry D</t>
         </is>
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -1431,40 +1291,28 @@
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
@@ -1473,22 +1321,35 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Driver,
+Altima</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>ENTER THRU SURGICAL CENTER</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Supv Rx</t>
+        </is>
+      </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -1502,40 +1363,29 @@
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>Casey</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Driver,
+Camry</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
@@ -1544,79 +1394,54 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>Jerry D</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>6:30 AM MEET COLLEGE (SOUTHWEST)</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr"/>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Until 10:00</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>PIGGLY WIGGLY #201, CEDARBURG</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Elijah</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van,
-Supv Rx</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
@@ -1625,68 +1450,57 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr"/>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>W61 N286 WASHINGTON AVE</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
@@ -1696,71 +1510,54 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Driver,
-Sante Fe</t>
-        </is>
-      </c>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC5-ITEM LEVEL   </t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr"/>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/QamMdWSr16N2</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Makeda</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1772,31 +1569,31 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>ASCENSION ALL SAINTS HOSP WI AVE CAMPUS (ST LUKE'S), RACINE</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Anisha</t>
+          <t>Elijah</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -1809,25 +1606,17 @@
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>FEW GROC AISLES RESET-REMAPPED</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Sue</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1839,7 +1628,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Anisha</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -1848,22 +1637,31 @@
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1320 WISCONSIN AVE</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr"/>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Driver,
+Camry</t>
+        </is>
+      </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Ashley P</t>
+          <t>Eva</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -1883,21 +1681,13 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>AURORA OUTPATIENT RX #1224, SHEBOYGAN</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
@@ -1906,7 +1696,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Ashley P</t>
+          <t>Anisha</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -1915,22 +1705,30 @@
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/raiuDa4wRko</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr"/>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Elijah</t>
+          <t>Evelin</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
@@ -1942,45 +1740,21 @@
       <c r="Y26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Sante Fe available, Equip</t>
-        </is>
-      </c>
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>5:30 AM MEET BAYSHORE</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>3400 UNION AVE, SUITE 1C-1006</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
@@ -1998,22 +1772,30 @@
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC5-ITEM LEVEL </t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr"/>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Justin</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -2025,41 +1807,21 @@
       <c r="Y27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Curt</t>
-        </is>
-      </c>
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>7:00 AM START</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/oh7TcXwsTBYkDsmw5</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
@@ -2073,73 +1835,57 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>15)</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
           <t>@ Store,
 Rx</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>ASCENSION ALL SAINTS HOSP SPRING ST CAMPUS (ST MARY'S), RACINE</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Makeda</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Elijah</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
@@ -2157,22 +1903,30 @@
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>3801 SPRING ST</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr"/>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
-          <t>15)</t>
+          <t>16)</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Nate</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -2184,43 +1938,27 @@
       <c r="Y29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Jerry S</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>@ Store, Until 10:30</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>AURORA OUTPATIENT RX #1169 GREEN BAY</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Eva</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store, Equip</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -2240,13 +1978,21 @@
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>15)</t>
+        </is>
+      </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/PjumoiJbqD62</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr"/>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
@@ -2255,38 +2001,22 @@
       <c r="Y30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2845 GREENBRIER RD</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>15)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Evelin</t>
+          <t>Carlie</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2307,17 +2037,26 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
+          <t>@ Store,
+Rx</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>16)</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>THE ASCENSIONS HAVE BEEN RESCHEDULED!</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
@@ -2326,45 +2065,17 @@
       <c r="Y31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Marcia</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>@ Store, Until 10:30</t>
-        </is>
-      </c>
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/rneu9EfJWkGa7fvJ7</t>
-        </is>
-      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>16)</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Makeda</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
@@ -2382,14 +2093,26 @@
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>17)</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Makeda</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
-          <t>9:00 AM START</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="W32" t="inlineStr"/>
@@ -2397,42 +2120,17 @@
       <c r="Y32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Nagui</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>@ Store, Until 10:30</t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>17)</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Michael N</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>@ Store,
-Rx</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
@@ -2451,14 +2149,26 @@
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18) </t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Michael N</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="W33" t="inlineStr"/>
@@ -2470,63 +2180,42 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van, Equip</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>18)</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
+          <t>7:00 AM START</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19) </t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
           <t>Taylor</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>19)</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
-          <t>SMOKE WORLD VAPE, BROOKFIELD</t>
+          <t>AURORA OUTPATIENT RX #1262, MILWAUKEE</t>
         </is>
       </c>
       <c r="W34" t="inlineStr"/>
@@ -2538,20 +2227,16 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Sue</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>EXCEL FINANCIAL</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
@@ -2559,17 +2244,13 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>9:00 AM START</t>
-        </is>
-      </c>
+      <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="inlineStr">
         <is>
-          <t>17115 W BLUEMOUND RD</t>
+          <t>3003 W GOOD HOPE RD, SUITE 1129</t>
         </is>
       </c>
       <c r="W35" t="inlineStr"/>
@@ -2586,25 +2267,29 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>CONCORD GENERAL STORE, OCONOMOWOC</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>6:30 AM START</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>EXCEL FINANCIAL</t>
-        </is>
-      </c>
+      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/o6BySGmshE5c9am29</t>
+          <t>https://goo.gl/maps/55ZX8sbcB762</t>
         </is>
       </c>
       <c r="W36" t="inlineStr"/>
@@ -2623,7 +2308,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>5:30 AM START</t>
+          <t>N6485 COUNTY RD F</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2631,7 +2316,7 @@
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
-          <t>THEY NOW HAVE SIGNS UP NO STREET PARKING</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
@@ -2639,7 +2324,7 @@
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
-          <t>SMOKE WORLD VAPE, WAUKESHA</t>
+          <t>7:00 AM START</t>
         </is>
       </c>
       <c r="S37" t="inlineStr"/>
@@ -2656,17 +2341,13 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>5:30 AM MEET COLLEGE (SOUTHWEST)</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>https://goo.gl/maps/X4xEoL3zCRA2</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2674,7 +2355,7 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>12:00 PM START</t>
+          <t>ASCENSION SETON RX #1112, MILWAUKEE</t>
         </is>
       </c>
       <c r="O38" t="inlineStr"/>
@@ -2682,7 +2363,7 @@
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
-          <t>530 W SUNSET DRIVE</t>
+          <t>COCA-COLA, MILWAUKEE</t>
         </is>
       </c>
       <c r="S38" t="inlineStr"/>
@@ -2694,12 +2375,12 @@
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Katherine</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Sante Fe available, Equip</t>
+          <t>Camry available, Equip</t>
         </is>
       </c>
       <c r="X38" t="inlineStr"/>
@@ -2711,25 +2392,17 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>ROTE OIL #6 HUBERTUS</t>
-        </is>
-      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1143 MENOM FALLS</t>
+          <t>2301 N LAKE DR</t>
         </is>
       </c>
       <c r="O39" t="inlineStr"/>
@@ -2737,7 +2410,7 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/aogDHj45t6GWbbYP8</t>
+          <t>11800 W BROWN DEER RD</t>
         </is>
       </c>
       <c r="S39" t="inlineStr"/>
@@ -2749,7 +2422,7 @@
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>Carlie</t>
         </is>
       </c>
       <c r="W39" t="inlineStr"/>
@@ -2762,31 +2435,39 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>1306 HWY 175</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>N93 W14575 WHITTAKER WAY</t>
+          <t>https://goo.gl/maps/fovW5S1B5ZD2</t>
         </is>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/3qRtjQQ4gbR2</t>
+        </is>
+      </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr">
@@ -2796,7 +2477,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="W40" t="inlineStr"/>
@@ -2809,44 +2490,24 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>ASCENSION COMMUNITY RX #1102-ATRIUM, RACINE</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/SZRuQ4FHA1cX2ZmC8</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/AJgcVD6yx75Kq3yS6</t>
+          <t>TO FOLLOW</t>
         </is>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>Lincoln</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>Sante Fe available, Equip</t>
-        </is>
-      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="inlineStr"/>
@@ -2860,36 +2521,36 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>3811 SPRING ST</t>
-        </is>
-      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>TO FOLLOW</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Sante Fe available, Equip</t>
+        </is>
+      </c>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="inlineStr"/>
@@ -2903,57 +2564,33 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/HCpmGJRX9sG2</t>
-        </is>
-      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>7:00 AM START</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+          <t>ASCENSION CSM OZAUKEE RETAIL RX #1109, MEQUON</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>Sarah</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
-          <t>5:00 AM OFFICE LEAVE TIME</t>
+          <t>7:00 AM START</t>
         </is>
       </c>
       <c r="W43" t="inlineStr"/>
@@ -2966,29 +2603,21 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>TO FOLLOW</t>
-        </is>
-      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>ROTE OIL #7 MILWAUKEE</t>
+          <t>COCA-COLA, MILWAUKEE</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>13133 N PORT WASHINGTON RD,  SUITE G1</t>
         </is>
       </c>
       <c r="O44" t="inlineStr"/>
@@ -3000,7 +2629,7 @@
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="W44" t="inlineStr"/>
@@ -3013,33 +2642,37 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>5931 N 91ST ST</t>
+          <t>11800 W BROWN DEER RD</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/ZV1UXpiCr4u</t>
+        </is>
+      </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>9:00 AM START</t>
+        </is>
+      </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>VILLARD SHOP RITE, MILWAUKEE</t>
         </is>
       </c>
       <c r="W45" t="inlineStr"/>
@@ -3052,17 +2685,13 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>ASCENSION COMMUNITY RX #1101-SPRING ST, RACINE</t>
-        </is>
-      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/cw58s7atAhTAGHNd7</t>
+          <t>https://goo.gl/maps/3qRtjQQ4gbR2</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3074,7 +2703,7 @@
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr">
         <is>
-          <t>5:00 AM OFFICE LEAVE TIME</t>
+          <t>EXCEL FINANCIAL</t>
         </is>
       </c>
       <c r="S46" t="inlineStr"/>
@@ -3082,7 +2711,7 @@
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="inlineStr">
         <is>
-          <t>ROTE OIL #14 TREVOR (CITGO)</t>
+          <t>5123 W VILLARD AVE</t>
         </is>
       </c>
       <c r="W46" t="inlineStr"/>
@@ -3095,33 +2724,33 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>3807 SPRING ST</t>
-        </is>
-      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>TO FOLLOW</t>
-        </is>
-      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t xml:space="preserve">5:30 AM START </t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr"/>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>SMOKE WORLD VAPE, MILW-BRADY</t>
         </is>
       </c>
       <c r="S47" t="inlineStr"/>
@@ -3129,7 +2758,7 @@
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="inlineStr">
         <is>
-          <t>12617 ANTIOCH RD</t>
+          <t>https://maps.app.goo.gl/e7gLkJnEfEdEK8D98</t>
         </is>
       </c>
       <c r="W47" t="inlineStr"/>
@@ -3142,43 +2771,51 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/345cLtjsHsD2</t>
-        </is>
-      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Sante Fe available, Equip</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr"/>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC5-FINANCIAL </t>
+          <t>1422 E BRADY ST</t>
         </is>
       </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/xA9YMzPGc6Vhxi5r8</t>
-        </is>
-      </c>
+      <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
@@ -3192,37 +2829,57 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>ROTE OIL #8 ELM GROVE</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>ROTE OIL #10 MUKWONAGO - ROCHESTER</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr"/>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
-          <t>ROTE OIL #1 PADDOCK LAKE- BRASS BALL</t>
+          <t>https://goo.gl/maps/stP5CiWnmcaw4sMA7</t>
         </is>
       </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr"/>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Red Van available, Equip</t>
+        </is>
+      </c>
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
     </row>
@@ -3231,51 +2888,34 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Driver,
-Sante Fe, Equip</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>13395 WATERTOWN PLANK RD</t>
-        </is>
-      </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>1060 N ROCHESTER ST</t>
-        </is>
-      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr">
         <is>
-          <t>25406 75TH ST</t>
+          <t>TO FOLLOW</t>
         </is>
       </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>Curt</t>
         </is>
       </c>
       <c r="W50" t="inlineStr"/>
@@ -3287,46 +2927,34 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Curt</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/5zXAKpcRHDmA17UK9</t>
-        </is>
-      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/dmvR5bTHLs1Cbjcr5</t>
-        </is>
-      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/LTa4ckcczx5qc8269</t>
+          <t>EXCEL FINANCIAL</t>
         </is>
       </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>ROTE OIL #13 TREVOR (BP)</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="W51" t="inlineStr"/>
@@ -3338,22 +2966,14 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>8:15 AM MEET OFFICE</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3361,7 +2981,7 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t xml:space="preserve">TO FOLLOW   </t>
+          <t>7:00 AM START</t>
         </is>
       </c>
       <c r="O52" t="inlineStr"/>
@@ -3369,17 +2989,13 @@
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>SMOKE WORLD VAPE, PUFF N UP, MILW-CAPITOL</t>
         </is>
       </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>12511 ANTIOCH RD</t>
-        </is>
-      </c>
+      <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
@@ -3389,22 +3005,14 @@
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>9:00 AM START</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3412,7 +3020,7 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>COCA-COLA, MILWAUKEE</t>
         </is>
       </c>
       <c r="O53" t="inlineStr"/>
@@ -3420,17 +3028,13 @@
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>6900 W CAPITOL DR</t>
         </is>
       </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/iu3xzNwgJ32esP5RA</t>
-        </is>
-      </c>
+      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
@@ -3447,7 +3051,7 @@
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>ROTE OIL #09 GREENFIELD</t>
+          <t>EXCEL FINANCIAL</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3455,7 +3059,7 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>ROTE OIL #12 MUKWONAGO - (AMOCO) GREENWALD</t>
+          <t>11800 W BROWN DEER RD</t>
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
@@ -3463,7 +3067,7 @@
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr">
         <is>
-          <t>ROTE OIL #2 PADDOCK LAKE- 75TH ST</t>
+          <t>https://goo.gl/maps/vDKLCtsWm3wvSBNj7</t>
         </is>
       </c>
       <c r="S54" t="inlineStr"/>
@@ -3486,7 +3090,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>12345 W LAYTON AVE</t>
+          <t>SMOKE WORLD VAPE, WATERTOWN</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3494,35 +3098,18 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>909 GREENWALD CT</t>
+          <t>https://goo.gl/maps/3qRtjQQ4gbR2</t>
         </is>
       </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>25555 75TH ST</t>
-        </is>
-      </c>
+      <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>@ Store,
-Camry, Equip</t>
-        </is>
-      </c>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
     </row>
@@ -3531,57 +3118,41 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>5:00 AM OFFICE LEAVE TIME</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/TSgMUriHbJPX9hGE7</t>
+          <t>1907 MARKET WAY</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/ejQSLoz2D8EmzKVq6</t>
-        </is>
-      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/5UyWWXXbzXMaVnv99</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
     </row>
@@ -3590,32 +3161,44 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/wQQEXdVvpg4wrmb56</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t xml:space="preserve">TO FOLLOW   </t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Sante Fe available, Equip</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Casey</t>
+        </is>
+      </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr"/>
@@ -3630,52 +3213,36 @@
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>Camry available, Equip</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>ROTE OIL  #11 MUKWONAGO - (BP) ARROWHEAD</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>Camry, Equip</t>
-        </is>
-      </c>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="inlineStr"/>
@@ -3689,48 +3256,32 @@
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>ROTE OIL #03 TWIN LAKES</t>
-        </is>
-      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>122 ARROWHEAD DR</t>
-        </is>
-      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
       <c r="V59" t="inlineStr"/>
@@ -3744,31 +3295,27 @@
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>475 N LAKE AVE</t>
-        </is>
-      </c>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Red Van</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/7XkTFZtDFDgGBctz7</t>
-        </is>
-      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
@@ -3787,19 +3334,31 @@
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/jNgJR8hii6jJGZQP7</t>
-        </is>
-      </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>6:30 AM MEET OFFICE</t>
+        </is>
+      </c>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
@@ -3818,27 +3377,35 @@
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TO FOLLOW   </t>
-        </is>
-      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>7:00 AM START</t>
+        </is>
+      </c>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
+      <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
@@ -3853,43 +3420,23 @@
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>5:00 AM OFFICE LEAVE TIME</t>
-        </is>
-      </c>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>Camry available, Equip</t>
-        </is>
-      </c>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>Kim</t>
-        </is>
-      </c>
+      <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
@@ -3904,29 +3451,17 @@
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>ROTE OIL #04 GENOA CITY</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>GAUGERT'S BUSS STOP, SULLIVAN</t>
         </is>
       </c>
       <c r="O64" t="inlineStr"/>
@@ -3947,23 +3482,23 @@
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100 ELIZABETH LANE    </t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>Office</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>141 MAIN ST</t>
+        </is>
+      </c>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
@@ -3982,23 +3517,23 @@
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/DitGJzEvTVhJPxkJ8</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>FOX BROS PIGGLY WIGGLY #088, SAUKVILLE</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/TEUfEX2J1AE2</t>
+        </is>
+      </c>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
@@ -4017,27 +3552,15 @@
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TO FOLLOW   </t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>810 E GREEN BAY AVE</t>
-        </is>
-      </c>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>Office</t>
-        </is>
-      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr"/>
@@ -4056,30 +3579,26 @@
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/eiMeyhHbpT82</t>
-        </is>
-      </c>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>Katherine</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Until 2:00</t>
+          <t>Equip</t>
         </is>
       </c>
       <c r="P68" t="inlineStr"/>
@@ -4099,20 +3618,29 @@
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>ROTE OIL #05  LAKE GENEVA</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Driver,
+Camry</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
@@ -4130,28 +3658,12 @@
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>300 PELLER RD</t>
-        </is>
-      </c>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>Jerry S</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
@@ -4173,28 +3685,12 @@
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/6fegzT1PbyY5VkDR6</t>
-        </is>
-      </c>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Sante Fe</t>
-        </is>
-      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
@@ -4219,24 +3715,16 @@
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>Ethan</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Madison Office</t>
+        </is>
+      </c>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
@@ -4254,40 +3742,20 @@
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Camry, Equip</t>
-        </is>
-      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>Heather</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
@@ -4300,330 +3768,6 @@
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr"/>
-      <c r="B74" t="inlineStr"/>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>Jeremiah</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr"/>
-      <c r="T74" t="inlineStr"/>
-      <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr"/>
-      <c r="W74" t="inlineStr"/>
-      <c r="X74" t="inlineStr"/>
-      <c r="Y74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr"/>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>Jeri</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr"/>
-      <c r="T75" t="inlineStr"/>
-      <c r="U75" t="inlineStr"/>
-      <c r="V75" t="inlineStr"/>
-      <c r="W75" t="inlineStr"/>
-      <c r="X75" t="inlineStr"/>
-      <c r="Y75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr"/>
-      <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>Katie</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>@ Store, Until 12:45</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr"/>
-      <c r="U76" t="inlineStr"/>
-      <c r="V76" t="inlineStr"/>
-      <c r="W76" t="inlineStr"/>
-      <c r="X76" t="inlineStr"/>
-      <c r="Y76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr"/>
-      <c r="B77" t="inlineStr"/>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>Kirsten</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>@ Store, Until 12:45</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr"/>
-      <c r="T77" t="inlineStr"/>
-      <c r="U77" t="inlineStr"/>
-      <c r="V77" t="inlineStr"/>
-      <c r="W77" t="inlineStr"/>
-      <c r="X77" t="inlineStr"/>
-      <c r="Y77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr"/>
-      <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>Marcia</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="inlineStr"/>
-      <c r="T78" t="inlineStr"/>
-      <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr"/>
-      <c r="W78" t="inlineStr"/>
-      <c r="X78" t="inlineStr"/>
-      <c r="Y78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr"/>
-      <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>Nagui</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>@ Store, Until 12:45</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="inlineStr"/>
-      <c r="T79" t="inlineStr"/>
-      <c r="U79" t="inlineStr"/>
-      <c r="V79" t="inlineStr"/>
-      <c r="W79" t="inlineStr"/>
-      <c r="X79" t="inlineStr"/>
-      <c r="Y79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr"/>
-      <c r="B80" t="inlineStr"/>
-      <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>Sarah</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr"/>
-      <c r="T80" t="inlineStr"/>
-      <c r="U80" t="inlineStr"/>
-      <c r="V80" t="inlineStr"/>
-      <c r="W80" t="inlineStr"/>
-      <c r="X80" t="inlineStr"/>
-      <c r="Y80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>Savannah</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="inlineStr"/>
-      <c r="T81" t="inlineStr"/>
-      <c r="U81" t="inlineStr"/>
-      <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr"/>
-      <c r="X81" t="inlineStr"/>
-      <c r="Y81" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Week1.xlsx
+++ b/Week1.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y73"/>
+  <dimension ref="A1:Y75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sun, May 26</t>
+          <t>Sun, Jun 2</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -427,7 +427,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Mon, May 27</t>
+          <t>Mon, Jun 3</t>
         </is>
       </c>
       <c r="F1" t="inlineStr"/>
@@ -435,7 +435,7 @@
       <c r="H1" t="inlineStr"/>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Tue, May 28</t>
+          <t>Tue, Jun 4</t>
         </is>
       </c>
       <c r="J1" t="inlineStr"/>
@@ -443,7 +443,7 @@
       <c r="L1" t="inlineStr"/>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Wed, May 29</t>
+          <t>Wed, Jun 5</t>
         </is>
       </c>
       <c r="N1" t="inlineStr"/>
@@ -451,7 +451,7 @@
       <c r="P1" t="inlineStr"/>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Thu, May 30</t>
+          <t>Thu, Jun 6</t>
         </is>
       </c>
       <c r="R1" t="inlineStr"/>
@@ -459,7 +459,7 @@
       <c r="T1" t="inlineStr"/>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Fri, May 31</t>
+          <t>Fri, Jun 7</t>
         </is>
       </c>
       <c r="V1" t="inlineStr"/>
@@ -467,7 +467,7 @@
       <c r="X1" t="inlineStr"/>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Sat, Jun 1</t>
+          <t>Sat, Jun 8</t>
         </is>
       </c>
     </row>
@@ -530,33 +530,37 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kim </t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Bags 5-7</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katherine </t>
+          <t xml:space="preserve">DJ </t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>ICALS</t>
+          <t>Bags 1,2</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Katherine </t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Bag 8</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -566,19 +570,19 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>ICALS</t>
+          <t>Bags 1-3</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim </t>
+          <t xml:space="preserve">Ian </t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Bags 1-4</t>
+          <t>Bags 5-8, Scanners</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -590,28 +594,36 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DJ </t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bags 1,2</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DJ </t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>ICALS</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kim </t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Bags 5,6</t>
+        </is>
+      </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
@@ -621,7 +633,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Bag 5, SB 11</t>
+          <t>Bag 4, SB 11</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
@@ -629,20 +641,20 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Tuesday is a slow day due to Memorial day on Monday</t>
-        </is>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ian </t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bag 8, SB 11</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -659,12 +671,12 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lashaun </t>
+          <t>DJ</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Bag 6</t>
+          <t>Bags 1-3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
@@ -675,11 +687,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -703,7 +711,11 @@
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5:00 AM MEET WATERTOWN PLANK</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
@@ -713,7 +725,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>*MEMORIAL DAY</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -721,7 +733,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5:15 AM MEET OFFICE MEET</t>
+          <t>4:00 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -729,7 +741,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4:15 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>4:45 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -737,7 +749,7 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4:15 AM MEET COLLEGE (SOUTHWEST) </t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -745,7 +757,7 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>5:00 AM MEET WATERTOWN PLANK</t>
         </is>
       </c>
       <c r="W8" t="inlineStr"/>
@@ -754,11 +766,19 @@
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -780,7 +800,7 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
@@ -788,7 +808,7 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
@@ -797,17 +817,25 @@
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>FOX BROS PIGGLY WIGGLY #093, OCONOMOWOC</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -823,7 +851,7 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>PICK #381, MUSKEGO</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
@@ -831,7 +859,7 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>PICK #845 +RX, MILWAUKEE-LOOMIS</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
@@ -840,17 +868,25 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>*SALE INVENTORY - FOX BROS BUYING</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1300 BROWN ST</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>KOHN'S FILLING STATION, KEWASKUM</t>
+          <t>MARIANO'S #509 +RX, FRANKFORT</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -858,7 +894,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>MARIANO'S #526 +RX, SHOREWOOD</t>
+          <t>MARIANO'S #501 +RX +OFFSITE RX, ARLINGTON HEIGHTS</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -866,7 +902,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>MARIANO'S #539 +RX, BRONZEVILLE</t>
+          <t>S74 W17005 JANESVILLE ROAD</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -874,7 +910,7 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>3701 S 27TH ST</t>
+          <t>PICK #472 +RX, FOND DU LAC-PIONEER</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
@@ -883,17 +919,25 @@
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PIGGLY WIGGLY #082, MAYVILLE</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/2K5yALCcUdM2</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>890 FOND DU LAC AVE</t>
+          <t>21001 S LAGRANGE RD</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -901,7 +945,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>950 BROOK FOREST AVE</t>
+          <t>802 E NORTHWEST HWY</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -909,7 +953,7 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>3857 S MARTIN LUTHER KING</t>
+          <t>https://goo.gl/maps/H8srKt8FVUp</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -917,7 +961,7 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/BLy8vMxXBsA2</t>
+          <t>55 W PIONEER RD</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
@@ -926,17 +970,25 @@
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1440 HORICON ST</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>5:00 am meet at Grafton Park n Ride (Carlie/Trevor)</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/CJnRNDyortw</t>
+          <t>https://goo.gl/maps/GfpVE3eArJM2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -944,7 +996,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/ieT41cP6AP42</t>
+          <t>https://goo.gl/maps/ZNjAYKcq8772</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -952,20 +1004,28 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/xtUgo2RcwVm</t>
+          <t>5:15 am meet at Grafton Park n Ride (Carlie/Trevor)</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/Cccqh1Wg8xs</t>
+        </is>
+      </c>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/3nJCWDd6bxMw9Df6A</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
@@ -975,42 +1035,34 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>SET UP ON REG #6 OR 7</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>SET UP ON REG #1</t>
+          <t>**OFFSITE RX, ARLINGTON HEIGHTS</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>LIQUOR RESET-REMAPPED</t>
-        </is>
-      </c>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Sante Fe available, Equip</t>
-        </is>
-      </c>
+          <t>SET UP ON REG #1</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
     </row>
@@ -1019,198 +1071,287 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>@ Store,
+Sante Fe, Equip</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>EXCEL FINANCIAL</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1250 VILLAGE DR</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Aaron</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Until 12:00</t>
-        </is>
-      </c>
+          <t>5:00 am meet at Grafton Park n Ride (Carlie/Trevor)</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Jerry S</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>@ Store, (Driver)
+Trainer, work w/ Eva G</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>KOHN'S FILLING STATION 259, CAMPBELLSPORT</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>*</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Brianna</t>
+          <t>https://maps.app.goo.gl/vthwUcrXyYaj6dDj9</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>@ Store, Equip</t>
+          <t>LINK FOR RX ONLY</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Nate</t>
+          <t>Carlie</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>@ Store, Equip</t>
+          <t>(Driver)</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Casey</t>
-        </is>
-      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Curt</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Trevor</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>@ Store,
+(w/ Carlie)</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>259 N FOND DU LAC AVE</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>SET UP ON REG #1</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>Rx</t>
-        </is>
-      </c>
+          <t>Casey</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr"/>
+          <t>Jeremiah</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>@ Store,
+White Camry,
+Until 12:00</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Annette</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/WCsZpx5SMsA2</t>
+          <t>Katherine</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1222,67 +1363,111 @@
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>Carlie</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Supv Rx</t>
+          <t>@ Store,
+(Grafton),
+Trainer</t>
         </is>
       </c>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ethan</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Curt</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Jerry D</t>
+          <t>Ian</t>
         </is>
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Jerry D</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="W19" t="inlineStr"/>
@@ -1290,585 +1475,812 @@
       <c r="Y19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Eva G</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>@ Store,
+1st Day, work w/ Carlie</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t>Carlie</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
           <t>Driver,
-Altima</t>
+Optima</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Supv Rx</t>
-        </is>
-      </c>
+          <t>Jerry D</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Mai</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Driver, Equip
+Red Van,
+Supv Rx</t>
+        </is>
+      </c>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Jeremiah</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Casey</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Driver,
-Camry</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Jerry D</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>@ Store,
+After Aurora
+if needed</t>
+        </is>
+      </c>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Annette</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Katie</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>@ Store,
+Until 1:00</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Sue</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+          <t>Cynthia</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr"/>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Until 12:00</t>
+        </is>
+      </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Angela</t>
+          <t>Mai</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Rx</t>
         </is>
       </c>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Josie</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>@ Store, Until 11:45</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Driver,
+Altima</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Kay</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Louisa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>@ Store,
+Work w/ Marcia</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>Jerry D</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Elijah</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>@ Store, Until 11:45</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Marcia</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>@ Store,
+Trainer</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Angela</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Driver,
+Sante Fe</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Sue</t>
+          <t>Stephanie</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Driver,
-Camry</t>
+          <t>Until 11:00</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Eva</t>
+          <t>Trevor</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store,
+(Grafton)</t>
         </is>
       </c>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Nagui</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>@ Store,
+Until 1:00</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1224, SHEBOYGAN</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Anisha</t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Rx</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Evelin</t>
+          <t>Annette</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store, Until 1:30</t>
         </is>
       </c>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Nagui</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>12)</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>3400 UNION AVE, SUITE 1C-1006</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Brianna</t>
+          <t>Trevor</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>w/ Carlie</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>Eva G</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store, 1st DC5 Scan, work w/ Carlie</t>
         </is>
       </c>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/oh7TcXwsTBYkDsmw5</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>Elijah</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
-          <t>15)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Nate</t>
+          <t>Heather</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>@ Store,
-Rx</t>
+          <t xml:space="preserve">@ Store  </t>
         </is>
       </c>
       <c r="X28" t="inlineStr"/>
@@ -1883,55 +2295,51 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr">
         <is>
-          <t>16)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Jerry S</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t xml:space="preserve">@ Store  </t>
         </is>
       </c>
       <c r="X29" t="inlineStr"/>
@@ -1943,60 +2351,64 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Justin</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>@ Store, Equip</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>15)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Makeda</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>15)</t>
-        </is>
-      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Kirsten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>@ Store, Until 1:30</t>
+        </is>
+      </c>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
     </row>
@@ -2006,61 +2418,65 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>16)</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>Michael N</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store,
+Rx</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>16)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Michael N</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>@ Store,
-Rx</t>
-        </is>
-      </c>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>16)</t>
-        </is>
-      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>15)</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
     </row>
@@ -2070,21 +2486,38 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>MALICKI'S PIGGLY WIGGLY #342, OAK CREEK</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>17)</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Qiana</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>@ Store,
+Supv Rx</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>17)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Nate</t>
+          <t>Anisha</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2093,29 +2526,29 @@
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>17)</t>
-        </is>
-      </c>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
-          <t>Makeda</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>FOX BROS PIGGLY WIGGLY #083, BEAVER DAM</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>16)</t>
+        </is>
+      </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr"/>
+          <t>Marcia</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@ Store  </t>
+        </is>
+      </c>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
     </row>
@@ -2125,21 +2558,37 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2201 E RAWSON AVE</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>18)</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>18)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Qiana</t>
+          <t>Ashley P</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2149,29 +2598,29 @@
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18) </t>
-        </is>
-      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Michael N</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>810 PARK AVE</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>17)</t>
+        </is>
+      </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr"/>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
     </row>
@@ -2181,44 +2630,56 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/r6Lve1UzasE2</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>7:00 AM START</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>16)</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19) </t>
-        </is>
-      </c>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/y8AoS99KUVU2</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>18)</t>
+        </is>
+      </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1262, MILWAUKEE</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr"/>
+          <t>Nagui</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>@ Store, Until 1:30</t>
+        </is>
+      </c>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
     </row>
@@ -2232,28 +2693,44 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>EXCEL FINANCIAL</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>17)</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Makeda</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>19)</t>
+        </is>
+      </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>3003 W GOOD HOPE RD, SUITE 1129</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr"/>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
     </row>
@@ -2262,36 +2739,65 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>CONCORD GENERAL STORE, OCONOMOWOC</t>
+          <t xml:space="preserve">6:00 AM START   </t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>18)</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>6:30 AM START</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr"/>
+          <t>Michael N</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>@ Store,
+Rx</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/55ZX8sbcB762</t>
-        </is>
-      </c>
+      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
@@ -2301,33 +2807,45 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Curt</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>N6485 COUNTY RD F</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>DC5-ITEM LEVEL</t>
-        </is>
-      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr"/>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="inlineStr"/>
@@ -2340,49 +2858,53 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Cynthia</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/X4xEoL3zCRA2</t>
+          <t>FOX BROS PIGGLY WIGGLY #091, SLINGER</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>ASCENSION SETON RX #1112, MILWAUKEE</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>COCA-COLA, MILWAUKEE</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr"/>
+          <t>Anisha</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Camry available, Equip</t>
-        </is>
-      </c>
+          <t>4:45 AM OFFICE LEAVE TIME</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
     </row>
@@ -2391,38 +2913,54 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1100 E COMMERCE BLVD</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2301 N LAKE DR</t>
+          <t>7:00 AM START</t>
         </is>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>11800 W BROWN DEER RD</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr"/>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="W39" t="inlineStr"/>
@@ -2434,50 +2972,54 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Monica</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/WgMCr1tJCE12</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/fovW5S1B5ZD2</t>
+          <t>EXCEL FINANCIAL</t>
         </is>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/3qRtjQQ4gbR2</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr"/>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="W40" t="inlineStr"/>
@@ -2489,28 +3031,56 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>5:30 am meet at Grafton Park n Ride (Carlie/Trevor)</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>DAYBREAK, DELAFIELD</t>
         </is>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>AURORA OUTPATIENT RX #1032 FOND DU LAC</t>
+        </is>
+      </c>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
@@ -2520,8 +3090,16 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Sonia</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
@@ -2531,29 +3109,33 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>622 GENESEE ST</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>Justin</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>Sante Fe available, Equip</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>210 WISCONSIN AMERICAN DR,  SUITE 24</t>
+        </is>
+      </c>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
@@ -2567,30 +3149,50 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
+          <t>Jeremiah</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>ASCENSION CSM OZAUKEE RETAIL RX #1109, MEQUON</t>
+          <t>https://goo.gl/maps/dNtyDnuiw6J2</t>
         </is>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
+          <t>https://maps.app.goo.gl/7eYhgLDismavDcYj6</t>
         </is>
       </c>
       <c r="W43" t="inlineStr"/>
@@ -2603,35 +3205,52 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>5:00 AM MEET OFFICE</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>COCA-COLA, MILWAUKEE</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>@ Store,
+Driver</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>13133 N PORT WASHINGTON RD,  SUITE G1</t>
-        </is>
-      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Makeda</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
@@ -2642,40 +3261,77 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>6:00 AMSTART</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>11800 W BROWN DEER RD</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>Trevor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>@ Store,
+(w/ Carlie)</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/ZV1UXpiCr4u</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Red Van available, Equip</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>9:00 AM START</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr"/>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>VILLARD SHOP RITE, MILWAUKEE</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr"/>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>White Camry, Equip</t>
+        </is>
+      </c>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
     </row>
@@ -2685,35 +3341,47 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/3qRtjQQ4gbR2</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>Annette</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Paul</t>
+        </is>
+      </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>EXCEL FINANCIAL</t>
-        </is>
-      </c>
+      <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>5123 W VILLARD AVE</t>
-        </is>
-      </c>
+      <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
@@ -2724,43 +3392,39 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>AURORA OUTPATIENT RX #1072 TWIN LAKES</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Ethan</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>Sarah</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>SMOKE WORLD VAPE, MILW-BRADY</t>
-        </is>
-      </c>
+      <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>https://maps.app.goo.gl/e7gLkJnEfEdEK8D98</t>
-        </is>
-      </c>
+      <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
@@ -2771,51 +3435,47 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>700 NORTH LAKE AVENUE SUITE 101</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>Heather</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Sante Fe available, Equip</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1422 E BRADY ST</t>
+          <t>5:15 AM MEET WATERTOWN PLANK</t>
         </is>
       </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>5:30 AM MEET BAYSHORE</t>
+        </is>
+      </c>
       <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
@@ -2826,60 +3486,52 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/EJCh7QYTfkz4egwc8</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>Jerry S</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/stP5CiWnmcaw4sMA7</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>Red Van available, Equip</t>
-        </is>
-      </c>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
     </row>
@@ -2892,30 +3544,43 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Katie</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>@ Store,
+Until 1:00</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr">
         <is>
-          <t>TO FOLLOW</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
-          <t>Curt</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="W50" t="inlineStr"/>
@@ -2927,34 +3592,60 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van, Equip</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Kirsten</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>@ Store,
+Until 1:00</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>SULLIVAN'S FOODS #242, MARENGO</t>
+        </is>
+      </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
+          <t>FOX BROS PIGGLY WIGGLY #084, WEST BEND</t>
         </is>
       </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="U51" t="inlineStr"/>
       <c r="V51" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>FOX BROS PIGGLY WIGGLY #086, PORT WASHINGTON</t>
         </is>
       </c>
       <c r="W51" t="inlineStr"/>
@@ -2966,22 +3657,39 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Sue</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>8:15 AM MEET OFFICE</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>Louisa</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>@ Store,
+Work w/ Marcia</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>7:00 AM START</t>
+          <t>202 LINDOW LANE</t>
         </is>
       </c>
       <c r="O52" t="inlineStr"/>
@@ -2989,13 +3697,17 @@
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr">
         <is>
-          <t>SMOKE WORLD VAPE, PUFF N UP, MILW-CAPITOL</t>
+          <t>2575 E WASHINGTON ST</t>
         </is>
       </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>101 W SEVEN HILLS RD</t>
+        </is>
+      </c>
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
@@ -3009,18 +3721,27 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>11)</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>9:00 AM START</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+          <t>Marcia</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>@ Store,
+Trainer</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>COCA-COLA, MILWAUKEE</t>
+          <t>https://goo.gl/maps/GrPtfaDKMT2RotRb9</t>
         </is>
       </c>
       <c r="O53" t="inlineStr"/>
@@ -3028,13 +3749,17 @@
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr">
         <is>
-          <t>6900 W CAPITOL DR</t>
+          <t>https://goo.gl/maps/v6j5Md5UXg82</t>
         </is>
       </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/bDTjbGTBftHbSSuh9</t>
+        </is>
+      </c>
       <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
@@ -3049,27 +3774,15 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>EXCEL FINANCIAL</t>
-        </is>
-      </c>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>11800 W BROWN DEER RD</t>
-        </is>
-      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/vDKLCtsWm3wvSBNj7</t>
-        </is>
-      </c>
+      <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
@@ -3088,28 +3801,58 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>SMOKE WORLD VAPE, WATERTOWN</t>
-        </is>
-      </c>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/3qRtjQQ4gbR2</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr"/>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Driver,
+Sante Fe, Equip</t>
+        </is>
+      </c>
       <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Driver,
+Altima, Equip</t>
+        </is>
+      </c>
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
     </row>
@@ -3125,34 +3868,56 @@
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>1907 MARKET WAY</t>
+          <t xml:space="preserve">5:30 AM MEET WATERTOWN PLANK </t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>@ Store,
+White Camry</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Aaron</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>@ Store,
+Until 12:00</t>
+        </is>
+      </c>
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
     </row>
@@ -3168,41 +3933,49 @@
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/wQQEXdVvpg4wrmb56</t>
+          <t xml:space="preserve">6:00 AM START </t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>Nick</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Sante Fe available, Equip</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Cynthia</t>
+        </is>
+      </c>
       <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
@@ -3217,36 +3990,62 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC5-FINANCIAL </t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr"/>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr"/>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Driver,
+Sante Fe
+Until 9:00</t>
+        </is>
+      </c>
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
     </row>
@@ -3259,33 +4058,62 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>FOX BROS PIGGLY WIGGLY #090, JACKSON</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T59" t="inlineStr"/>
-      <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>w/ Kim
+Until 9:00</t>
+        </is>
+      </c>
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
     </row>
@@ -3298,33 +4126,61 @@
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>Red Van</t>
-        </is>
-      </c>
+          <t>W194 N16774 EAGLE DR</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Michael N</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
     </row>
@@ -3337,37 +4193,61 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/8bY4qRuqZNT2</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>6:30 AM MEET OFFICE</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr"/>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr"/>
     </row>
@@ -3380,37 +4260,33 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>7:00 AM START</t>
-        </is>
-      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Eva</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
     </row>
@@ -3423,25 +4299,46 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Driver,
+Altima, Equip</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr"/>
     </row>
@@ -3454,25 +4351,41 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Cynthia</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>GAUGERT'S BUSS STOP, SULLIVAN</t>
-        </is>
-      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr"/>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>10)</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Justin</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X64" t="inlineStr"/>
       <c r="Y64" t="inlineStr"/>
     </row>
@@ -3485,20 +4398,20 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Jerry D</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>141 MAIN ST</t>
-        </is>
-      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
@@ -3520,20 +4433,26 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>@ Store,
+White Camry,
+Until 10:30</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/TEUfEX2J1AE2</t>
-        </is>
-      </c>
+      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
@@ -3555,9 +4474,21 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Jeri</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
@@ -3568,7 +4499,11 @@
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr"/>
-      <c r="V67" t="inlineStr"/>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Madison Office</t>
+        </is>
+      </c>
       <c r="W67" t="inlineStr"/>
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr"/>
@@ -3582,32 +4517,36 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Josie</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr"/>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
       <c r="W68" t="inlineStr"/>
       <c r="X68" t="inlineStr"/>
       <c r="Y68" t="inlineStr"/>
@@ -3621,26 +4560,25 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>Driver,
-Camry</t>
-        </is>
-      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
@@ -3661,9 +4599,21 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
@@ -3688,9 +4638,21 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Savannah</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
@@ -3720,11 +4682,7 @@
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>Madison Office</t>
-        </is>
-      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
@@ -3751,11 +4709,7 @@
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
@@ -3768,6 +4722,68 @@
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr"/>
+      <c r="X74" t="inlineStr"/>
+      <c r="Y74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr"/>
+      <c r="X75" t="inlineStr"/>
+      <c r="Y75" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Week1.xlsx
+++ b/Week1.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y75"/>
+  <dimension ref="A1:Y95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Sun, Jun 2</t>
+          <t>Sun, Jun 9</t>
         </is>
       </c>
       <c r="B1" t="inlineStr"/>
@@ -427,7 +427,7 @@
       <c r="D1" t="inlineStr"/>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Mon, Jun 3</t>
+          <t>Mon, Jun 10</t>
         </is>
       </c>
       <c r="F1" t="inlineStr"/>
@@ -435,7 +435,7 @@
       <c r="H1" t="inlineStr"/>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Tue, Jun 4</t>
+          <t>Tue, Jun 11</t>
         </is>
       </c>
       <c r="J1" t="inlineStr"/>
@@ -443,7 +443,7 @@
       <c r="L1" t="inlineStr"/>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Wed, Jun 5</t>
+          <t>Wed, Jun 12</t>
         </is>
       </c>
       <c r="N1" t="inlineStr"/>
@@ -451,7 +451,7 @@
       <c r="P1" t="inlineStr"/>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Thu, Jun 6</t>
+          <t>Thu, Jun 13</t>
         </is>
       </c>
       <c r="R1" t="inlineStr"/>
@@ -459,7 +459,7 @@
       <c r="T1" t="inlineStr"/>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Fri, Jun 7</t>
+          <t>Fri, Jun 14</t>
         </is>
       </c>
       <c r="V1" t="inlineStr"/>
@@ -467,7 +467,7 @@
       <c r="X1" t="inlineStr"/>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Sat, Jun 8</t>
+          <t>Sat, Jun 15</t>
         </is>
       </c>
     </row>
@@ -537,12 +537,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim </t>
+          <t xml:space="preserve">DJ </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bags 5-7</t>
+          <t xml:space="preserve">Bags 1,2 </t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -554,13 +554,21 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Bags 1,2</t>
+          <t>Bags 1-3</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Katherine </t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Bag 8</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -570,7 +578,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Bags 1-3</t>
+          <t>Bags 1-4</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -582,7 +590,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Bags 5-8, Scanners</t>
+          <t>Bag 5, SB 11</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -593,47 +601,51 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DJ </t>
+          <t xml:space="preserve">Kim </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bags 1,2</t>
+          <t>Bags 5-7</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Katherine </t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Bag 8</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kim </t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>Bags 5,6</t>
-        </is>
-      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katherine </t>
+          <t xml:space="preserve">DJ </t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Bag 4, SB 11</t>
+          <t>Bag 1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
@@ -644,17 +656,13 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ian </t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Bag 8, SB 11</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -671,12 +679,12 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>DJ</t>
+          <t xml:space="preserve">Katherine </t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Bags 1-3</t>
+          <t>Bags 7,8</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
@@ -687,7 +695,11 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -713,7 +725,7 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5:00 AM MEET WATERTOWN PLANK</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -733,7 +745,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4:00 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>4:30 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -741,7 +753,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4:45 AM MEET COLLEGE (SOUTHWEST)</t>
+          <t>5:00 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
@@ -749,7 +761,7 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>5:00 AM MEET COLLEGE (SOUTHWEST)</t>
         </is>
       </c>
       <c r="S8" t="inlineStr"/>
@@ -757,7 +769,7 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr">
         <is>
-          <t>5:00 AM MEET WATERTOWN PLANK</t>
+          <t xml:space="preserve">5:30 AM MEET AT S RACINE COURT </t>
         </is>
       </c>
       <c r="W8" t="inlineStr"/>
@@ -768,7 +780,7 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -800,7 +812,7 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="S9" t="inlineStr"/>
@@ -819,7 +831,7 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>PIGGLY WIGGLY #220, MUSKEGO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -827,7 +839,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FOX BROS PIGGLY WIGGLY #093, OCONOMOWOC</t>
+          <t>PIGGLY WIGGLY #070, WEST ALLIS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -851,7 +863,7 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>PICK #381, MUSKEGO</t>
+          <t>DC5-ITEM LEVEL</t>
         </is>
       </c>
       <c r="S10" t="inlineStr"/>
@@ -870,7 +882,7 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>*SALE INVENTORY - FOX BROS BUYING</t>
+          <t>W189 S7847 RACINE AVE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -878,7 +890,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1300 BROWN ST</t>
+          <t>10282 W NATIONAL</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -886,7 +898,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>MARIANO'S #509 +RX, FRANKFORT</t>
+          <t>MARIANO'S #513 +RX, WHEATON</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -894,7 +906,8 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>MARIANO'S #501 +RX +OFFSITE RX, ARLINGTON HEIGHTS</t>
+          <t>MARIANO'S #502 +RX, 
+VERNON HILLS</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -902,7 +915,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>S74 W17005 JANESVILLE ROAD</t>
+          <t>MARIANO'S #518 +RX, GLENVIEW</t>
         </is>
       </c>
       <c r="S11" t="inlineStr"/>
@@ -910,7 +923,7 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr">
         <is>
-          <t>PICK #472 +RX, FOND DU LAC-PIONEER</t>
+          <t>AURORA OUTPATIENT RX #1145 ELKHORN</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
@@ -921,7 +934,7 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PIGGLY WIGGLY #082, MAYVILLE</t>
+          <t>https://goo.gl/maps/3aRXzfmExPr</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
@@ -929,7 +942,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/2K5yALCcUdM2</t>
+          <t>https://goo.gl/maps/zGMZZJVxurK2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -937,7 +950,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>21001 S LAGRANGE RD</t>
+          <t>625 S MAIN ST</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -945,7 +958,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>802 E NORTHWEST HWY</t>
+          <t>1720 N MILWAUKEE AVENUE</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -953,7 +966,7 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/H8srKt8FVUp</t>
+          <t>25 WAUKEGAN RD</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -961,7 +974,7 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>55 W PIONEER RD</t>
+          <t>W3985 COUNTY ROAD NN</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
@@ -970,17 +983,13 @@
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1440 HORICON ST</t>
-        </is>
-      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>5:00 am meet at Grafton Park n Ride (Carlie/Trevor)</t>
+          <t>5:30 am meet for Carlie/Trevor at Grafton Park n Ride</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -988,7 +997,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/GfpVE3eArJM2</t>
+          <t>https://maps.app.goo.gl/vYhjkFWiTisqXoRN9</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -996,7 +1005,7 @@
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/ZNjAYKcq8772</t>
+          <t>https://goo.gl/maps/ynVVx558fS22</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -1004,7 +1013,7 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>5:15 am meet at Grafton Park n Ride (Carlie/Trevor)</t>
+          <t>https://goo.gl/maps/E7YkRP2q2272</t>
         </is>
       </c>
       <c r="S13" t="inlineStr"/>
@@ -1012,7 +1021,7 @@
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/Cccqh1Wg8xs</t>
+          <t>https://goo.gl/maps/DNeRzd2PfnuGBCUo6</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
@@ -1020,13 +1029,21 @@
       <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/3nJCWDd6bxMw9Df6A</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Sante Fe available, Equip</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
@@ -1035,40 +1052,44 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>SET UP ON REG #6 OR 7</t>
+          <t>SET UP ON REG #1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
-          <t>**OFFSITE RX, ARLINGTON HEIGHTS</t>
+          <t xml:space="preserve">SET UP ON LAST REG </t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>4:15 am meet for Carlie/Trevor at Grafton Park n Ride</t>
+        </is>
+      </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>SET UP ON REG #1</t>
-        </is>
-      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
@@ -1078,13 +1099,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>DJ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>@ Store,
-Sante Fe, Equip</t>
+          <t>Equip</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1092,60 +1112,50 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>1250 VILLAGE DR</t>
+          <t>4:15 am meet for Carlie/Trevor at Grafton Park n Ride</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
         <is>
           <t>1)</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr">
         <is>
-          <t>5:00 am meet at Grafton Park n Ride (Carlie/Trevor)</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Driver,
+Sante Fe,
+Equip</t>
+        </is>
+      </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jerry S</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
@@ -1159,8 +1169,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>@ Store, (Driver)
-Trainer, work w/ Eva G</t>
+          <t>(Driver)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1171,7 +1180,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Nate</t>
+          <t>Brianna</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1180,40 +1189,36 @@
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>https://maps.app.goo.gl/vthwUcrXyYaj6dDj9</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>LINK FOR RX ONLY</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
           <t>2)</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>(Driver)</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Monica</t>
+        </is>
+      </c>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
@@ -1221,12 +1226,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Curt</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -1238,15 +1243,10 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trevor</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>@ Store,
-(w/ Carlie)</t>
-        </is>
-      </c>
+          <t>Cynthia</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
@@ -1258,62 +1258,67 @@
           <t>Casey</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Driver,
+Sante Fe</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>SET UP ON REG #1</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Casey</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr"/>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Driver,
+Optima,
+Trainer</t>
+        </is>
+      </c>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Jeremiah</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Katherine</t>
+          <t>Brianna</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>@ Store,
-White Camry,
-Until 12:00</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1324,14 +1329,10 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Annette</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
@@ -1340,18 +1341,37 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Driver,
+Gold Camry</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Driver,
+Optima,
+Trainer</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1361,41 +1381,26 @@
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>@ Store,
-(Grafton),
-Trainer</t>
-        </is>
-      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>Nate</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Driver,
-Red Van</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1406,14 +1411,10 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ethan</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Nick</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
@@ -1422,35 +1423,31 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van</t>
-        </is>
-      </c>
+          <t>Jerry D</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Brianna</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>@ Store, Equip</t>
+          <t>Driver,
+Sante Fe</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1458,16 +1455,18 @@
           <t>Ian</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van,
+Supv Rx</t>
+        </is>
+      </c>
       <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Casey</t>
+          <t>4:30 AM OFFICE LEAVE TIME</t>
         </is>
       </c>
       <c r="W19" t="inlineStr"/>
@@ -1477,15 +1476,19 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mai</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>Qiana</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
@@ -1494,15 +1497,10 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Eva G</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>@ Store,
-1st Day, work w/ Carlie</t>
-        </is>
-      </c>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
@@ -1511,31 +1509,35 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Monica</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Supv Rx</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Carlie</t>
+          <t>DJ</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
           <t>Driver,
-Optima</t>
+Altima</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1545,37 +1547,19 @@
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Driver, Equip
-Red Van,
-Supv Rx</t>
-        </is>
-      </c>
+          <t>7:00 AM START</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
@@ -1585,12 +1569,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jeremiah</t>
+          <t>Trevor</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>(w/ Carlie)</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -1601,26 +1585,30 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Casey</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
+          <t>Greg</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2nd Day (work w/ Carlie)</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -1630,59 +1618,24 @@
       </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>@ Store,
-After Aurora
-if needed</t>
-        </is>
-      </c>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Annette</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Katie</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>@ Store,
-Until 1:00</t>
-        </is>
-      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
@@ -1691,89 +1644,63 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Sue</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Mai</t>
+          <t>Lashaun</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Until 12:00</t>
+          <t>Driver,
+Gold Camry</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Mai</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Rx</t>
-        </is>
-      </c>
+          <t>AURORA OUTPATIENT RX #1157, STURGEON BAY</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Josie</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>@ Store, Until 11:45</t>
-        </is>
-      </c>
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
@@ -1782,52 +1709,39 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>Sue</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Driver,
-Altima</t>
-        </is>
-      </c>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>Mai</t>
         </is>
       </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
+      <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>1910 ALABAMA ST</t>
         </is>
       </c>
       <c r="W23" t="inlineStr"/>
@@ -1835,38 +1749,17 @@
       <c r="Y23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Kay</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Louisa</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>@ Store,
-Work w/ Marcia</t>
-        </is>
-      </c>
+          <t>4:30 AM MEET AT THE OFFICE</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
@@ -1875,47 +1768,49 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Ashley P</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store,
+Rx
+(Train w/ Lashaun)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Supv Rx</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Monica</t>
         </is>
       </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>8)</t>
-        </is>
-      </c>
+      <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>https://goo.gl/maps/PT62tX3aqSWcCC5G6</t>
         </is>
       </c>
       <c r="W24" t="inlineStr"/>
@@ -1923,38 +1818,17 @@
       <c r="Y24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>10)</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>@ Store, Until 11:45</t>
-        </is>
-      </c>
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Marcia</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>@ Store,
-Trainer</t>
-        </is>
-      </c>
+          <t>7:00 AM START</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
@@ -1963,7 +1837,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Brianna</t>
+          <t>Anisha</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1974,89 +1848,46 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Driver,
-Sante Fe</t>
-        </is>
-      </c>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Stephanie</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>Until 11:00</t>
-        </is>
-      </c>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>9)</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Trevor</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>@ Store,
-(Grafton)</t>
-        </is>
-      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Michelle</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nagui</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>@ Store,
-Until 1:00</t>
-        </is>
-      </c>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
@@ -2065,7 +1896,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Elijah</t>
+          <t>Ashley P</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2076,82 +1907,62 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Rx</t>
-        </is>
-      </c>
+          <t>Paul</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr"/>
+          <t>Robyn</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>3rd Day (work w/ Carlie)</t>
+        </is>
+      </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>Annette</t>
+          <t>DJ</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>@ Store, Until 1:30</t>
+          <t>Equip</t>
         </is>
       </c>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Nagui</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sarah</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>PIGGLY WIGGLY #406, LANCASTER</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
@@ -2160,7 +1971,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Eva</t>
+          <t>Elijah</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2171,69 +1982,49 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Mai</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
+          <t>Robyn</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2nd Day (work w/ Michael)</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Trevor</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>w/ Carlie</t>
-        </is>
-      </c>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>11)</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Eva G</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>@ Store, 1st DC5 Scan, work w/ Carlie</t>
-        </is>
-      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Sarah</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>158 N WASHINGTON</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
@@ -2254,35 +2045,31 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>13)</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Stephanie</t>
+        </is>
+      </c>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>12)</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Heather</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">@ Store  </t>
-        </is>
-      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
     </row>
@@ -2292,7 +2079,11 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/jFeseMTzfS32</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
@@ -2313,35 +2104,35 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>Stephanie</t>
         </is>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Sue</t>
+        </is>
+      </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>13)</t>
-        </is>
-      </c>
+      <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr">
         <is>
-          <t>Jerry S</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">@ Store  </t>
-        </is>
-      </c>
+          <t>5:00 AM MEET AT THE OFFICE</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
     </row>
@@ -2351,11 +2142,7 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
@@ -2365,7 +2152,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>Nate</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2376,39 +2163,39 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>12)</t>
+          <t>14)</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Stephanie</t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>15)</t>
+        </is>
+      </c>
       <c r="R30" t="inlineStr">
         <is>
+          <t>Trevor</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>(w/ Carlie)</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
+        <is>
           <t>6:00 AM START</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>14)</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Kirsten</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>@ Store, Until 1:30</t>
-        </is>
-      </c>
+      <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
     </row>
@@ -2417,66 +2204,66 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Driver,
+Sante Fe, Equip</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>16)</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Michael N</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>@ Store,
-Rx</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>13)</t>
+          <t>15)</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Sue</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr"/>
+          <t>Trevor</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>(w/ Carlie)</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>16)</t>
+        </is>
+      </c>
       <c r="R31" t="inlineStr">
         <is>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
           <t>DC5-FINANCIAL</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>15)</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Lori</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
     </row>
@@ -2485,34 +2272,25 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MALICKI'S PIGGLY WIGGLY #342, OAK CREEK</t>
+          <t>Casey</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>17)</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Qiana</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>@ Store,
-Supv Rx</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>14)</t>
+          <t>16)</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2526,29 +2304,30 @@
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>17)</t>
+        </is>
+      </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>FOX BROS PIGGLY WIGGLY #083, BEAVER DAM</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr"/>
+          <t>Evelin</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>@ Store,
+Rx</t>
+        </is>
+      </c>
       <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>16)</t>
-        </is>
-      </c>
+      <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Marcia</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">@ Store  </t>
-        </is>
-      </c>
+          <t>PIGGLY WIGGLY #169, COTTAGE GROVE</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
     </row>
@@ -2557,70 +2336,72 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2201 E RAWSON AVE</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>Ian</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>18)</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>15)</t>
+          <t>17)</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Ashley P</t>
+          <t>Eva</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
           <t>@ Store,
-Supv Rx</t>
+Rx
+(Train w/ Lashaun)</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>18)</t>
+        </is>
+      </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>810 PARK AVE</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr"/>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>17)</t>
-        </is>
-      </c>
+      <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Michelle</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>421 W COTTAGE GROVE RD</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
     </row>
@@ -2629,26 +2410,34 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/r6Lve1UzasE2</t>
+          <t>Jerry D</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>DC5-ITEM LEVEL</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>16)</t>
+          <t>18)</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Joseph</t>
+          <t>Evelin</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -2657,29 +2446,29 @@
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>19)</t>
+        </is>
+      </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/y8AoS99KUVU2</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr"/>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>18)</t>
-        </is>
-      </c>
+      <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr">
         <is>
-          <t>Nagui</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>@ Store, Until 1:30</t>
-        </is>
-      </c>
+          <t>https://goo.gl/maps/ysP4kdWtU542</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
     </row>
@@ -2688,22 +2477,34 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>PICK #357 +RX, GERMANTOWN</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>17)</t>
+          <t>19)</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Makeda</t>
+          <t>Joseph</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -2716,21 +2517,9 @@
       <c r="R35" t="inlineStr"/>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>19)</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Sarah</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
     </row>
@@ -2741,31 +2530,27 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Equip</t>
-        </is>
-      </c>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">6:00 AM START   </t>
+          <t>N112 W16200 MEQUON RD</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>18)</t>
+          <t>20)</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2776,29 +2561,29 @@
       <c r="O36" t="inlineStr">
         <is>
           <t>@ Store,
-Rx</t>
+Trainer</t>
         </is>
       </c>
       <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr">
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
         <is>
           <t>1)</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
         <is>
           <t>@ Store, Equip</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
     </row>
@@ -2809,12 +2594,12 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Curt</t>
+          <t>Mai</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -2822,7 +2607,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>https://goo.gl/maps/EHNPxYdtCp82</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2831,25 +2616,29 @@
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr">
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
         <is>
           <t>2)</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Aaron</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>@ Store, Until 12:00</t>
+        </is>
+      </c>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
     </row>
@@ -2860,12 +2649,12 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -2873,7 +2662,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>FOX BROS PIGGLY WIGGLY #091, SLINGER</t>
+          <t>SET UP ON REG CLOSEST TOWARDS SERVICE COUNTER</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2882,29 +2671,30 @@
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr">
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
         <is>
           <t>3)</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>Anisha</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
-          <t>4:45 AM OFFICE LEAVE TIME</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr"/>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Driver,
+Optima</t>
+        </is>
+      </c>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
     </row>
@@ -2915,12 +2705,12 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mai</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -2928,7 +2718,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>1100 E COMMERCE BLVD</t>
+          <t>5:30 am meet for Carlie/Trevor at Grafton Park n Ride</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2941,26 +2731,22 @@
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr">
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>FOX BROS PIGGLY WIGGLY #087, HARTFORD</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
         <is>
           <t>4)</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>Ashley P</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
       <c r="V39" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="W39" t="inlineStr"/>
@@ -2974,52 +2760,44 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Monica</t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>https://goo.gl/maps/WgMCr1tJCE12</t>
-        </is>
-      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
-          <t>EXCEL FINANCIAL</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr">
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1566 E SUMNER ST</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
         <is>
           <t>5)</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
       <c r="V40" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="W40" t="inlineStr"/>
@@ -3031,57 +2809,57 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Paul</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>5:30 am meet at Grafton Park n Ride (Carlie/Trevor)</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>DJ</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
-          <t>DAYBREAK, DELAFIELD</t>
+          <t>PIGGLY WIGGLY #170, WATERLOO</t>
         </is>
       </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr">
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/aDpuMeDEHSz</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
         <is>
           <t>6)</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>Joseph</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jeri</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>AURORA OUTPATIENT RX #1032 FOND DU LAC</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
     </row>
@@ -3090,53 +2868,54 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Sonia</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Carlie</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>(Driver),
+Trainer</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>622 GENESEE ST</t>
+          <t>810 N MONROE ST</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr">
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
         <is>
           <t>7)</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>Justin</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Nick</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
         <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>210 WISCONSIN AMERICAN DR,  SUITE 24</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
     </row>
@@ -3146,55 +2925,51 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6:00 AM START </t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Jeremiah</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t>Curt</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/dNtyDnuiw6J2</t>
+          <t>https://goo.gl/maps/nBV5CGccWtE2</t>
         </is>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Lori</t>
+          <t>Jeremiah</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store, Equip</t>
         </is>
       </c>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>https://maps.app.goo.gl/7eYhgLDismavDcYj6</t>
-        </is>
-      </c>
+      <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
@@ -3207,27 +2982,22 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>5:00 AM MEET OFFICE</t>
+          <t xml:space="preserve">DC5-FINANCIAL       </t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Carlie</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>@ Store,
-Driver</t>
-        </is>
-      </c>
+          <t>Cynthia</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
@@ -3235,17 +3005,17 @@
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Makeda</t>
+          <t>Annette</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t xml:space="preserve">@ Store  </t>
         </is>
       </c>
       <c r="T44" t="inlineStr"/>
@@ -3263,25 +3033,24 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>6:00 AMSTART</t>
+          <t>LAKHBIR WG MOBIL #8, MADISON</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Trevor</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>@ Store,
-(w/ Carlie)</t>
+          <t>1st Day (work w/ Carlie)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -3292,46 +3061,38 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Red Van available, Equip</t>
+          <t>@ Store, Equip</t>
         </is>
       </c>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>David</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t xml:space="preserve">@ Store  </t>
         </is>
       </c>
       <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>White Camry, Equip</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4:30 AM MEET AT S RACINE COURT </t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
     </row>
@@ -3343,24 +3104,24 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>DC5-ITEM LEVEL</t>
+          <t>699 S WHITNEY WAY</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Annette</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>Supv Rx</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -3371,17 +3132,37 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Paul</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr"/>
+          <t>Jeri</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Jerry S</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>@ Store, after Condon</t>
+        </is>
+      </c>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
@@ -3394,37 +3175,65 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AURORA OUTPATIENT RX #1072 TWIN LAKES</t>
+          <t>https://maps.app.goo.gl/dDkZaUKMLA3ANdv96</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Rx</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
+        <is>
           <t>5)</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Ethan</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Katie</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@ Store  </t>
+        </is>
+      </c>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC5-FINANCIAL </t>
+        </is>
+      </c>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
@@ -3437,43 +3246,59 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>700 NORTH LAKE AVENUE SUITE 101</t>
+          <t xml:space="preserve">TO FOLLOW </t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
+          <t>8)</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Monica</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Nick</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
+        <is>
           <t>6)</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Heather</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
-          <t>5:15 AM MEET WATERTOWN PLANK</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr"/>
+          <t>Marcia</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@ Store  </t>
+        </is>
+      </c>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="inlineStr">
         <is>
-          <t>5:30 AM MEET BAYSHORE</t>
+          <t>SULLIVAN'S FOODS #295 +ACE, WINNEBAGO</t>
         </is>
       </c>
       <c r="W48" t="inlineStr"/>
@@ -3488,47 +3313,59 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/EJCh7QYTfkz4egwc8</t>
+          <t xml:space="preserve">DC5-FINANCIAL </t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
+          <t>9)</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Nick</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Ron</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
+        <is>
           <t>7)</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Jerry S</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr"/>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>@ Store, after Condon</t>
+        </is>
+      </c>
       <c r="T49" t="inlineStr"/>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="inlineStr">
         <is>
-          <t>6:00 AM START</t>
+          <t>703 N ELIDA STREET</t>
         </is>
       </c>
       <c r="W49" t="inlineStr"/>
@@ -3541,46 +3378,65 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>LAKHBIR CP SYENE #16, FITCHBURG</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
+          <t>10)</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Robyn</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>1st Day (work w/ Michael)</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Savannah</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
+        <is>
           <t>8)</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Katie</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>@ Store,
-Until 1:00</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr"/>
+          <t>Ron</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="inlineStr">
         <is>
-          <t>DC5-FINANCIAL</t>
+          <t>https://goo.gl/maps/XJm8iLALryeWSpAZ6</t>
         </is>
       </c>
       <c r="W50" t="inlineStr"/>
@@ -3592,62 +3448,36 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ian</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Driver,
-Red Van, Equip</t>
-        </is>
-      </c>
+          <t>2770 S SYENE RD</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Kirsten</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>@ Store,
-Until 1:00</t>
-        </is>
-      </c>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>SULLIVAN'S FOODS #242, MARENGO</t>
-        </is>
-      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>FOX BROS PIGGLY WIGGLY #084, WEST BEND</t>
-        </is>
-      </c>
+      <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>FOX BROS PIGGLY WIGGLY #086, PORT WASHINGTON</t>
-        </is>
-      </c>
+      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
@@ -3657,58 +3487,54 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sue</t>
+          <t>https://maps.app.goo.gl/BGAVED5UHCh9zoeo8</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Louisa</t>
+          <t>Trevor</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>@ Store,
-Work w/ Marcia</t>
+          <t>(w/ Carlie)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>202 LINDOW LANE</t>
-        </is>
-      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>2575 E WASHINGTON ST</t>
-        </is>
-      </c>
+      <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>101 W SEVEN HILLS RD</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr"/>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>@ Store, Equip,
+(Groc Supv)</t>
+        </is>
+      </c>
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
     </row>
@@ -3718,30 +3544,33 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>11)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Marcia</t>
+          <t>Eva</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>@ Store,
-Trainer</t>
+          <t>@ Store</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/GrPtfaDKMT2RotRb9</t>
+          <t>4:45 AM OFFICE LEAVE TIME</t>
         </is>
       </c>
       <c r="O53" t="inlineStr"/>
@@ -3749,18 +3578,27 @@
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/v6j5Md5UXg82</t>
+          <t>7:00 AM START</t>
         </is>
       </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>https://maps.app.goo.gl/bDTjbGTBftHbSSuh9</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr"/>
+          <t>Casey</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Driver,
+Red Van</t>
+        </is>
+      </c>
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
     </row>
@@ -3770,24 +3608,62 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC5-FINANCIAL   </t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Michael N</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>@ Store,
+Trainer</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6:00 AM START </t>
+        </is>
+      </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Greg</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>1st Financial
+work w/ Angela</t>
+        </is>
+      </c>
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
     </row>
@@ -3797,62 +3673,56 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>LAKHBIR CP MART SOUTH #1, MADISON</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>15)</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Nate</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>@ Store, Equip</t>
-        </is>
-      </c>
+          <t xml:space="preserve">DC5-FINANCIAL </t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
+      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>Driver,
-Sante Fe, Equip</t>
-        </is>
-      </c>
+          <t>PIGGLY WIGGLY #168, EDGERTON</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr">
         <is>
-          <t>1)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>Driver,
-Altima, Equip</t>
-        </is>
-      </c>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
     </row>
@@ -3862,60 +3732,46 @@
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2570 RIMROCK RD</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5:30 AM MEET WATERTOWN PLANK </t>
-        </is>
-      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Katherine</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>@ Store,
-White Camry</t>
-        </is>
-      </c>
+          <t>LAKHBIR BP MOHAWK #7, MADISON</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>2)</t>
-        </is>
-      </c>
+      <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr">
         <is>
-          <t>Lashaun</t>
+          <t>1211 N MAIN ST</t>
         </is>
       </c>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>@ Store,
-Until 12:00</t>
+          <t>Ace Side</t>
         </is>
       </c>
       <c r="X56" t="inlineStr"/>
@@ -3927,53 +3783,41 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/AeMqZ4iM1Pf323zs8</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6:00 AM START </t>
-        </is>
-      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Nick</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>4325 MOHAWK DR</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>3)</t>
-        </is>
-      </c>
+      <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr">
         <is>
-          <t>Sonia</t>
+          <t>https://goo.gl/maps/9YbLUf3aGUH2</t>
         </is>
       </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>Sonia</t>
         </is>
       </c>
       <c r="W57" t="inlineStr"/>
@@ -3992,60 +3836,34 @@
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC5-FINANCIAL </t>
+          <t>6:00 AM START</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Angela</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>https://maps.app.goo.gl/PLqtoJ6NWQs5uGjt6</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>4)</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>Brianna</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>Driver,
-Sante Fe
-Until 9:00</t>
-        </is>
-      </c>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
     </row>
@@ -4054,64 +3872,68 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
-          <t>FOX BROS PIGGLY WIGGLY #090, JACKSON</t>
+          <t>DC5-FINANCIAL</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>5)</t>
-        </is>
-      </c>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Eva</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t xml:space="preserve">TO FOLLOW </t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>Evelin</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store, Equip</t>
         </is>
       </c>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>Stephanie</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>w/ Kim
-Until 9:00</t>
+          <t>@ Store,
+Trainer</t>
         </is>
       </c>
       <c r="X59" t="inlineStr"/>
@@ -4122,42 +3944,46 @@
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Palmer</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>W194 N16774 EAGLE DR</t>
+          <t>FOX BROS PIGGLY WIGGLY #089, HUBERTUS</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>6)</t>
-        </is>
-      </c>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Evelin</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t xml:space="preserve">DC5-FINANCIAL  </t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Michael N</t>
+          <t>Anisha</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -4168,12 +3994,12 @@
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>9)</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>Brianna</t>
+          <t>Anisha</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
@@ -4189,42 +4015,46 @@
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Qiana</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>https://goo.gl/maps/8bY4qRuqZNT2</t>
+          <t>1234 HWY 175</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>7)</t>
-        </is>
-      </c>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Taylor</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>@ Store</t>
-        </is>
-      </c>
+          <t>LAKHBIR CG MOBIL #5, MADISON</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Jeri</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
@@ -4235,12 +4065,12 @@
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>10)</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>Elijah</t>
+          <t>Ashley P</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -4261,25 +4091,45 @@
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>https://goo.gl/maps/k8v61779c9p</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>605 COTTAGE GROVE RD</t>
+        </is>
+      </c>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>11)</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>Eva</t>
+          <t>Elijah</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
@@ -4299,44 +4149,48 @@
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1)</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>DJ</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Driver,
-Altima, Equip</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/bmHVowFwiUmQqnQ86</t>
+        </is>
+      </c>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>5)</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>12)</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>Evelin</t>
+          <t>Eva</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store,
+Ace Side</t>
         </is>
       </c>
       <c r="X63" t="inlineStr"/>
@@ -4353,37 +4207,58 @@
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2)</t>
+          <t>1)</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Cynthia</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
+          <t>Jeremiah</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>6)</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Michael N</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr">
         <is>
-          <t>10)</t>
+          <t>13)</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>Evelin</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t>@ Store,
+Ace Side</t>
         </is>
       </c>
       <c r="X64" t="inlineStr"/>
@@ -4400,27 +4275,59 @@
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>3)</t>
+          <t>2)</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Jerry D</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
+          <t>David</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">@ Store  </t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC5-FINANCIAL   </t>
+        </is>
+      </c>
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>7)</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Nick</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr"/>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>14)</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr"/>
     </row>
@@ -4435,33 +4342,48 @@
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>4)</t>
+          <t>3)</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Ian</t>
+          <t>Heather</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>@ Store,
-White Camry,
-Until 10:30</t>
+          <t xml:space="preserve">@ Store  </t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>LAKHBIR CP MART AW #14, MADISON</t>
+        </is>
+      </c>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr"/>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>15)</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Justin</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>@ Store,
+Ace Side</t>
+        </is>
+      </c>
       <c r="X66" t="inlineStr"/>
       <c r="Y66" t="inlineStr"/>
     </row>
@@ -4476,35 +4398,48 @@
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>5)</t>
+          <t>4)</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Jeri</t>
+          <t>Jerry S</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t xml:space="preserve">@ Store  </t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>4601 COTTAGE GROVE RD</t>
+        </is>
+      </c>
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr"/>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>16)</t>
+        </is>
+      </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>Madison Office</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr"/>
+          <t>Nate</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>@ Store,
+Ace Supv</t>
+        </is>
+      </c>
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr"/>
     </row>
@@ -4519,35 +4454,52 @@
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>6)</t>
+          <t>5)</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Josie</t>
+          <t>Katie</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t xml:space="preserve">@ Store  </t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/bjwT7M9WA23hoXd88</t>
+        </is>
+      </c>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>4:30 AM OFFICE LEAVE TIME</t>
+        </is>
+      </c>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
-      <c r="U68" t="inlineStr"/>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>17)</t>
+        </is>
+      </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>Lashaun</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr"/>
+          <t>Taylor</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>@ Store,
+Ace Side</t>
+        </is>
+      </c>
       <c r="X68" t="inlineStr"/>
       <c r="Y68" t="inlineStr"/>
     </row>
@@ -4562,17 +4514,17 @@
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>7)</t>
+          <t>6)</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Lori</t>
+          <t>Kirsten</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t xml:space="preserve">@ Store  </t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
@@ -4581,7 +4533,11 @@
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
       <c r="U69" t="inlineStr"/>
@@ -4601,26 +4557,43 @@
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>8)</t>
+          <t>7)</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Marcia</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>@ Store</t>
+          <t xml:space="preserve">@ Store  </t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>White Camry
+Equip</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr"/>
@@ -4640,30 +4613,50 @@
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>9)</t>
+          <t>8)</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Savannah</t>
+          <t>Michelle</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
+          <t>@ Store, Until 10:30</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
           <t>@ Store</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>LAKHBIR CP WEST #11, MADISON</t>
+        </is>
+      </c>
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr"/>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>4:45 AM MEET AT THE OFFICE</t>
+        </is>
+      </c>
       <c r="W71" t="inlineStr"/>
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
@@ -4681,16 +4674,36 @@
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>6702 MINERAL POINT RD</t>
+        </is>
+      </c>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr"/>
-      <c r="V72" t="inlineStr"/>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>6:00 AM START</t>
+        </is>
+      </c>
       <c r="W72" t="inlineStr"/>
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
@@ -4713,11 +4726,19 @@
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/u6JziHHvPAFDhbCTA</t>
+        </is>
+      </c>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr"/>
-      <c r="V73" t="inlineStr"/>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="W73" t="inlineStr"/>
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
@@ -4734,7 +4755,7 @@
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>4:45 AM OFFICE LEAVE TIME</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4744,11 +4765,19 @@
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TO FOLLOW   </t>
+        </is>
+      </c>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr"/>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>LAKHBIR CP MART SOUTH #1, MADISON</t>
+        </is>
+      </c>
       <c r="W74" t="inlineStr"/>
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
@@ -4765,7 +4794,7 @@
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t xml:space="preserve">6:00 AM START </t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -4775,14 +4804,800 @@
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr"/>
-      <c r="V75" t="inlineStr"/>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2570 RIMROCK RD</t>
+        </is>
+      </c>
       <c r="W75" t="inlineStr"/>
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC5-FINANCIAL </t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>LAKHBIR GAMMON BP #12, MADISON</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/AeMqZ4iM1Pf323zs8</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr"/>
+      <c r="X76" t="inlineStr"/>
+      <c r="Y76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>LAKHBIR NP MOBIL #9, MADISON</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>699 S GAMMON RD</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr"/>
+      <c r="X77" t="inlineStr"/>
+      <c r="Y77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>3101 N SHERMAN AVE</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/xn9rk4qzwpnZm3Jj9</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr"/>
+      <c r="X78" t="inlineStr"/>
+      <c r="Y78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/SNnQrwGgZvMobqnQ9</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TO FOLLOW   </t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>LAKHBIR MS MOBIL #4, MADISON</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr"/>
+      <c r="X79" t="inlineStr"/>
+      <c r="Y79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>TO FOLLOW</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>3019 E WASHINGTON AVE</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>DC5-FINANCIAL</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>LAKHBIR VR MOBIL #6, MADISON</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/Kpi5RsNj91eBCKx88</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>LAKHBIR CP MART NE #15, MADISON</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>4601 VERONA RD</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TO FOLLOW </t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="inlineStr"/>
+      <c r="Y82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>4901 COMMERCIAL AVE</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/R5BjsCpnN3fE746N9</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DC5-FINANCIAL  </t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr"/>
+      <c r="X83" t="inlineStr"/>
+      <c r="Y83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/iYBAaHXs8ZRaWucF9</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr"/>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>LAKHBIR BP EAST #2, MADISON</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr"/>
+      <c r="X84" t="inlineStr"/>
+      <c r="Y84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>Brianna</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>@ Store, Equip</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>2702 E WASHINGTON AVE</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr"/>
+      <c r="X85" t="inlineStr"/>
+      <c r="Y85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>White Camry
+Equip</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>Ashley P</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>https://maps.app.goo.gl/eD1oEYfBoN2jg6bP8</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr"/>
+      <c r="X86" t="inlineStr"/>
+      <c r="Y86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Palmer</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>Sante Fe</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
+      <c r="W87" t="inlineStr"/>
+      <c r="X87" t="inlineStr"/>
+      <c r="Y87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Ron</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>@ Store</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>1)</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Katherine</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr"/>
+      <c r="Y88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>2)</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Curt</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr"/>
+      <c r="X89" t="inlineStr"/>
+      <c r="Y89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="inlineStr"/>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>3)</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Lashaun</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Driver,
+White Camry</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr"/>
+      <c r="Y90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="inlineStr"/>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>4)</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Lori</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>@ Store (After c-store if needed)</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr"/>
+      <c r="Y91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="inlineStr"/>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr"/>
+      <c r="W92" t="inlineStr"/>
+      <c r="X92" t="inlineStr"/>
+      <c r="Y92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="inlineStr"/>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr"/>
+      <c r="W93" t="inlineStr"/>
+      <c r="X93" t="inlineStr"/>
+      <c r="Y93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="inlineStr"/>
+      <c r="T94" t="inlineStr"/>
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr"/>
+      <c r="X94" t="inlineStr"/>
+      <c r="Y94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr"/>
+      <c r="T95" t="inlineStr"/>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Nick</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr"/>
+      <c r="X95" t="inlineStr"/>
+      <c r="Y95" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
